--- a/数据/黄平文献粗读汇总表_精进版.xlsx
+++ b/数据/黄平文献粗读汇总表_精进版.xlsx
@@ -678,44 +678,36 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Integrated analysis of restraint stress in rat serum using ATR-FTIR and Raman spectroscopy with Machine learning</t>
+          <t>FTIR spectroscopy imaging coupled with machine learning reveals biochemical changes in the brains of diabetic mice</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>ATR-FTIR和拉曼光谱结合机器学习综合分析大鼠血清约束应激</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>使用ATR-FTIR和拉曼光谱结合机器学习联合识别大鼠血清中约束应激的新方法。</t>
-        </is>
-      </c>
+          <t>FTIR光谱成像结合机器学习揭示糖尿病小鼠脑生化改变</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr"/>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>应激</t>
+          <t>糖尿病脑病</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>AI/机器学习;光谱</t>
+          <t>AI/机器学习; 光谱</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>死亡方式</t>
+          <t>死因</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>2025-11</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>复旦大学基础医学院法医学系</t>
-        </is>
-      </c>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr"/>
       <c r="J3" s="3" t="inlineStr">
         <is>
           <t>4.8</t>
@@ -723,48 +715,31 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>可牵引「应激相关死亡（约束/体位性窒息）的生化和光谱学死后诊断」综述：从『约束应激缺乏特异性形态学改变的鉴定困境』切入，梳理ATR-FTIR与拉曼在血清生化指纹层面的证据，讨论光谱分类模型用于区分死亡方式（约束致死 vs 自然疾病）的价值，并与传统尸检所见（瘀点、擦伤、内脏淤血）及应激激素生化指标形成互补证据链，可进一步扩展为『生物体液光谱组学在死亡方式判定中的应用』综述。</t>
+          <t>可牵引一篇『FTIR光谱成像在脑组织区域生化分析中的应用』综述：以糖尿病脑病区域特异性代谢改变为范例，系统梳理FTIRM在皮层、海马、丘脑等不同脑区的脂质与蛋白质二级结构光谱特征，结合机器学习分类方法，按『样本制备—光谱采集与区域定位—峰归属生化注释—分类建模—与生化金标准验证』框架组织；对法医学可延伸至脑缺血、创伤等病理性损伤的分子诊断应用前景。</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>基于大鼠约束应激模型，约束方式、时长与强度同人类法医案例中的真实约束情形差异较大，种属外推性有限；血清光谱易受死后变化、溶血、采血部位及保存条件干扰，摘要未报告样本量、建模细节及独立验证；缺乏与皮质酮等应激相关生化指标的相关性对照，光谱差异的分子解释深度不足。</t>
+          <t>基于db/db小鼠模型，与人类糖尿病脑病存在物种差异，向人体转化需谨慎；区域间光谱差异的生物学注释主要依靠峰归属推断，缺乏与免疫组化、质谱等生化金标准的定量验证。摘要未报告样本量、死后延迟及固定处理对光谱的影响，研究为描述性分析，区域特异性标志物的稳健性与判别效能证据不足。</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">In forensic practice, accurately determining whether an individual has been subjected to prolonged restraint or assessing injuries resulting from restraint can be challenging. To address this, we explored a novel approach using attenuated total reflection Fourier transform infrared (ATR-FTIR) spectroscopy and Raman spectroscopy combined with machine learning to jointly identify restraint stress. We randomly assigned rats into three experimental groups: a restraint stress group (subjected to fasting and water deprivation), a control group (subjected to fasting and water deprivation without restraint), and a normal group. After collecting the serum spectra of the animals, a principal component analysis (PCA) model was established to explore the separation trends among the groups and to identify relevant characteristic peaks. Subsequently, a random forest (RF) model was established to compare the restraint stress group with the other two groups. The analysis identified key substances that indicated the presence of restraint stress: 1161 cm−1, 1167 cm−1 (anti-symmetric C-O-C stretch) and 980 cm−1, 976 cm−1, 974 cm−1 (−N+(CH3)3, antisymmetric stretch). And the RF model was used to compare the restraint stress groups at different time points, revealing substances that may help determine the duration of restraint stress: 1747 cm−1 (ester carbonyl band), 1626 cm−1 (β-pleated sheet), 1211 cm−1 (Amide III, −N+(CH3)3, antisymmetric stretch), 1180 cm−1 (phosphodiester), 1128 cm−1 (−C–C-), 1024 cm−1 (C-O stretching coupled with C-O bending) and 1389 cm−1, 1335 cm−1, 1321 cm−1 (Trp, α helix, phospholipids), 710 cm−1 (Polysaccharides), 1266 cm−1 (Amide Ⅲ), 1015 cm−1 (β-carotene). These findings suggest that ATR-FTIR and Raman spectroscopy together, when combined with machine learning, has significant potential as a powerful tool for analyzing and characterizing restraint stress, offering new insights and directions for future research in this area.
-</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>动物实验，大鼠血清样本，ATR-FTIR+拉曼光谱+机器学习</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>ATR-FTIR和拉曼光谱联合使用具有分析和表征约束应激的强大潜力。</t>
-        </is>
-      </c>
-      <c r="P3" s="3" t="inlineStr">
-        <is>
-          <t>首次联合ATR-FTIR和拉曼光谱分析约束应激</t>
-        </is>
-      </c>
-      <c r="Q3" s="3" t="inlineStr">
-        <is>
-          <t>ATR-FTIR;拉曼光谱;约束应激;机器学习</t>
-        </is>
-      </c>
+          <t>Diabetic encephalopathy is a progressive complication of type 2 diabetes, yet its region-specific biochemical changes remain unclear. In this study, we applied Fourier Transform Infrared Microspectroscopy (FTIRM) to assess metabolic alterations in the anatomical structures of the brains of db/db mice. Spectral data from five anatomically defined regions, cerebral cortex, hippocampus, thalamus, hypothalamus, and striatum, were analyzed in both 12-week and 21-week wild-type and diabetic groups. Marked changes were observed in the spectral regions of glucose, phospholipids, esterified lipids, amide, and nucleic acids across these brain regions. As diabetes progress, the hippocampus exhibited progressive molecular deterioration, while the hypothalamus showed disruptions followed by partial restoration at 21 weeks. Partial least square discriminant analysis (PLS-DA) models based on second-derivative spectra achieved high classification accuracy (area under the curve (AUC) &gt; 0.99), reliably distinguishing between healthy, early (12 weeks), and late (21 weeks) diabetic stages. These results demonstrate the capacity of FTIRM combined with machine learning to reveal region-specific biochemical signatures of diabetic encephalopathy and offer potential for early diagnosis and staging.</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr"/>
+      <c r="O3" s="3" t="inlineStr"/>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" s="3" t="inlineStr"/>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>Spectrochimica Acta Part A: Molecular and Biomolecular Spectroscopy</t>
+          <t>Spectrochimica Acta. Part A, Molecular and Biomolecular Spectroscopy</t>
         </is>
       </c>
       <c r="S3" s="3" t="inlineStr">
         <is>
-          <t>10.1016/j.saa.2025.126379</t>
+          <t>10.1016/j.saa.2025.126835</t>
         </is>
       </c>
     </row>
@@ -774,27 +749,27 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>A simple optical microscopy-based diatom classification approach for forensic drowning site inference: a pilot study</t>
+          <t>Integrated analysis of restraint stress in rat serum using ATR-FTIR and Raman spectroscopy with Machine learning</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>基于普通光学显微镜的硅藻分类方法用于法医溺死地点推断：初步研究</t>
+          <t>ATR-FTIR和拉曼光谱结合机器学习综合分析大鼠血清约束应激</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>基于普通光学显微镜的简单硅藻分类方法，用于法医案例中溺死地点推断。</t>
+          <t>使用ATR-FTIR和拉曼光谱结合机器学习联合识别大鼠血清中约束应激的新方法。</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>硅藻</t>
+          <t>应激</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>形态学</t>
+          <t>AI/机器学习;光谱</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -804,62 +779,63 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>复旦大学基础医学院法医学系/司法鉴定科学研究院</t>
+          <t>复旦大学基础医学院法医学系</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>可牵引「硅藻检验在溺死地点推断中的应用与标准化」综述：以『形态学分类→水域硅藻群落分布特征→地点溯源』为技术链，对比普通光学显微镜与SEM、分子方法（DNA宏条形码）的检出能力与适用场景，并结合不同水域硅藻数据库建设讨论分类流程标准化与质控（盲法、重复性）问题；本研究定位为pilot study，恰好说明该方向证据仍不充分，综述可围绕方法学演进与基层推广可行性展开。</t>
+          <t>可牵引「应激相关死亡（约束/体位性窒息）的生化和光谱学死后诊断」综述：从『约束应激缺乏特异性形态学改变的鉴定困境』切入，梳理ATR-FTIR与拉曼在血清生化指纹层面的证据，讨论光谱分类模型用于区分死亡方式（约束致死 vs 自然疾病）的价值，并与传统尸检所见（瘀点、擦伤、内脏淤血）及应激激素生化指标形成互补证据链，可进一步扩展为『生物体液光谱组学在死亡方式判定中的应用』综述。</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>为初步研究（pilot study），样本量与水域覆盖范围有限，结论的证据等级较低；普通光学显微镜分辨率限制导致小型硅藻、破损硅藻的属种鉴定困难，分类高度依赖操作者经验，观察者间差异与跨实验室可重复性未报告；摘要未提及与实际水域环境采样对照、盲法设计及统计检验，地点推断的准确率缺乏定量评估。</t>
+          <t>基于大鼠约束应激模型，约束方式、时长与强度同人类法医案例中的真实约束情形差异较大，种属外推性有限；血清光谱易受死后变化、溶血、采血部位及保存条件干扰，摘要未报告样本量、建模细节及独立验证；缺乏与皮质酮等应激相关生化指标的相关性对照，光谱差异的分子解释深度不足。</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>A simple optical microscopy-based approach for diatom classification to infer drowning site in forensic cases.</t>
+          <t xml:space="preserve">In forensic practice, accurately determining whether an individual has been subjected to prolonged restraint or assessing injuries resulting from restraint can be challenging. To address this, we explored a novel approach using attenuated total reflection Fourier transform infrared (ATR-FTIR) spectroscopy and Raman spectroscopy combined with machine learning to jointly identify restraint stress. We randomly assigned rats into three experimental groups: a restraint stress group (subjected to fasting and water deprivation), a control group (subjected to fasting and water deprivation without restraint), and a normal group. After collecting the serum spectra of the animals, a principal component analysis (PCA) model was established to explore the separation trends among the groups and to identify relevant characteristic peaks. Subsequently, a random forest (RF) model was established to compare the restraint stress group with the other two groups. The analysis identified key substances that indicated the presence of restraint stress: 1161 cm−1, 1167 cm−1 (anti-symmetric C-O-C stretch) and 980 cm−1, 976 cm−1, 974 cm−1 (−N+(CH3)3, antisymmetric stretch). And the RF model was used to compare the restraint stress groups at different time points, revealing substances that may help determine the duration of restraint stress: 1747 cm−1 (ester carbonyl band), 1626 cm−1 (β-pleated sheet), 1211 cm−1 (Amide III, −N+(CH3)3, antisymmetric stretch), 1180 cm−1 (phosphodiester), 1128 cm−1 (−C–C-), 1024 cm−1 (C-O stretching coupled with C-O bending) and 1389 cm−1, 1335 cm−1, 1321 cm−1 (Trp, α helix, phospholipids), 710 cm−1 (Polysaccharides), 1266 cm−1 (Amide Ⅲ), 1015 cm−1 (β-carotene). These findings suggest that ATR-FTIR and Raman spectroscopy together, when combined with machine learning, has significant potential as a powerful tool for analyzing and characterizing restraint stress, offering new insights and directions for future research in this area.
+</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>实验研究，水样硅藻，光学显微镜+分类算法</t>
+          <t>动物实验，大鼠血清样本，ATR-FTIR+拉曼光谱+机器学习</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>普通光学显微镜结合简单分类流程可有效进行硅藻分类和溺死地点推断，适用于基层法医实验室。</t>
+          <t>ATR-FTIR和拉曼光谱联合使用具有分析和表征约束应激的强大潜力。</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>开发适用于基层实验室的简单硅藻分类推断溺死地点方法</t>
+          <t>首次联合ATR-FTIR和拉曼光谱分析约束应激</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>硅藻;溺死地点推断;光学显微镜</t>
+          <t>ATR-FTIR;拉曼光谱;约束应激;机器学习</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>International Journal of Legal Medicine</t>
+          <t>Spectrochimica Acta Part A: Molecular and Biomolecular Spectroscopy</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10.1007/s00414-025-03520-3</t>
+          <t>10.1016/j.saa.2025.126379</t>
         </is>
       </c>
     </row>
@@ -869,93 +845,92 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Using ATR-FTIR spectroscopy and machine learning for forensic hair identification</t>
+          <t>A simple optical microscopy-based diatom classification approach for forensic drowning site inference: a pilot study</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>使用ATR-FTIR光谱和机器学习进行法医毛发鉴定</t>
+          <t>基于普通光学显微镜的硅藻分类方法用于法医溺死地点推断：初步研究</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>ATR-FTIR光谱结合机器学习用于法医毛发鉴定和区分。</t>
+          <t>基于普通光学显微镜的简单硅藻分类方法，用于法医案例中溺死地点推断。</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>毛发鉴定</t>
+          <t>硅藻</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>AI/机器学习;光谱</t>
+          <t>形态学</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>身份</t>
+          <t>死亡方式</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>复旦大学基础医学院法医学系</t>
+          <t>复旦大学基础医学院法医学系/司法鉴定科学研究院</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>可牵引「毛发证据的法医学光谱分析：从形态学到机器学习」综述：围绕『毛发种属、个体来源与身体部位判定』，系统梳理ATR-FTIR在毛发样本中的预处理、光谱特征选择与分类器（SVM、随机森林等）选择策略，并与线粒体DNA测序、蛋白质组学等毛发个体识别方法对比，讨论非破坏性、现场可用的毛发筛查技术路线及其证据效力定位。</t>
+          <t>可牵引「硅藻检验在溺死地点推断中的应用与标准化」综述：以『形态学分类→水域硅藻群落分布特征→地点溯源』为技术链，对比普通光学显微镜与SEM、分子方法（DNA宏条形码）的检出能力与适用场景，并结合不同水域硅藻数据库建设讨论分类流程标准化与质控（盲法、重复性）问题；本研究定位为pilot study，恰好说明该方向证据仍不充分，综述可围绕方法学演进与基层推广可行性展开。</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>研究区分的是头皮、阴毛、腋毛等身体部位来源而非个体身份，个体间判别能力未经充分验证；摘要未报告供体人数、样本量及毛发理化状态（染发、漂洗、污染）的排除标准，外部因素对光谱的干扰控制不明；机器学习分类缺乏独立测试集与交叉验证细节，存在过拟合及跨样本泛化不足的风险。</t>
+          <t>为初步研究（pilot study），样本量与水域覆盖范围有限，结论的证据等级较低；普通光学显微镜分辨率限制导致小型硅藻、破损硅藻的属种鉴定困难，分类高度依赖操作者经验，观察者间差异与跨实验室可重复性未报告；摘要未提及与实际水域环境采样对照、盲法设计及统计检验，地点推断的准确率缺乏定量评估。</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The purpose of this experiment is to utilize attenuated total reflection (ATR) Fourier transform infrared (FTIR) spectroscopy for the discrimination of different types of hair, as numerous studies have substantiated its efficacy in substance classification. In this study, ATR-FTIR spectroscopy was employed to analyze scalp hair, pubic hair, and armpit hair from human subjects. Additionally, a machine learning model was integrated to differentiate between hairs originating from distinct body regions. Because of the limited sampling conditions, we only chose samples from Chinese people who have been living in Shanghai and the surrounding areas for a long time to conduct the experiment. We developed partial least squares discriminant analysis (PLS-DA), random forest (RF), and support vector machine (SVM) classification models and compared their performance in identification. The results show that the SVM model has the best identification results with 90.37% accuracy, 90.37% recall, and 90.38% precision. This preliminary study suggests that ATR-FTIR spectroscopy combined with SVM may be an effective and promising aid in assisting the identification of hair in different parts of the human body. This method is non-destructive, fast, and accurate, and does not require a sample preparation process, which makes it promising in the field of forensic science. Also, we found that the main substance differences that contributed to the good distinction between hairs were expressed in amide I, followed by amide III and C-H deformation.
-</t>
+          <t>A simple optical microscopy-based approach for diatom classification to infer drowning site in forensic cases.</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>实验研究，人毛发样本，ATR-FTIR光谱+机器学习分类算法</t>
+          <t>实验研究，水样硅藻，光学显微镜+分类算法</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>ATR-FTIR结合机器学习可有效区分不同个体的毛发样本，具有法医学应用前景。</t>
+          <t>普通光学显微镜结合简单分类流程可有效进行硅藻分类和溺死地点推断，适用于基层法医实验室。</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>将ATR-FTIR与机器学习结合用于毛发个体识别</t>
+          <t>开发适用于基层实验室的简单硅藻分类推断溺死地点方法</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>ATR-FTIR;机器学习;毛发鉴定</t>
+          <t>硅藻;溺死地点推断;光学显微镜</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>Journal of Forensic Sciences</t>
+          <t>International Journal of Legal Medicine</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t>10.1111/1556-4029.70062</t>
+          <t>10.1007/s00414-025-03520-3</t>
         </is>
       </c>
     </row>
@@ -965,38 +940,37 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>The application of vibrational spectroscopy in forensic analysis of biological evidence</t>
+          <t>Using ATR-FTIR spectroscopy and machine learning for forensic hair identification</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>振动光谱在法医生物证据分析中的应用（综述）</t>
+          <t>使用ATR-FTIR光谱和机器学习进行法医毛发鉴定</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>综述阐述了FTIR和拉曼光谱技术在法医学体液检测和死因确定中的研究轨迹和潜在应用。</t>
+          <t>ATR-FTIR光谱结合机器学习用于法医毛发鉴定和区分。</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>振动光谱
-法医生物证据分析</t>
+          <t>毛发鉴定</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>光谱</t>
+          <t>AI/机器学习;光谱</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>死因</t>
+          <t>身份</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1006,52 +980,53 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>本篇综述本身可牵引更聚焦的子综述：如『振动光谱在法医体液鉴定（血液/精液/唾液/尿液）中的标准化与数据库建设』，或『FTIR与拉曼在死因推断中的死后组织应用』——后者可将本团队系列工作（糖尿病脑病、心肌梗死分期、窒息与心源性猝死鉴别、肺脂肪栓塞）纳入证据链，按PRISMA式系统评价框架汇总各研究的样本类型、模型性能与特征波段，提出光谱死后诊断的标准化采集与解释指南，是很好的综述选题生长点。</t>
+          <t>可牵引「毛发证据的法医学光谱分析：从形态学到机器学习」综述：围绕『毛发种属、个体来源与身体部位判定』，系统梳理ATR-FTIR在毛发样本中的预处理、光谱特征选择与分类器（SVM、随机森林等）选择策略，并与线粒体DNA测序、蛋白质组学等毛发个体识别方法对比，讨论非破坏性、现场可用的毛发筛查技术路线及其证据效力定位。</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>作为叙述性综述，其证据基础多为小样本动物模型或离体组织研究，异质性大且缺乏定量荟萃分析；未给出光谱采集参数、样本制备的标准化建议的具体内容；所述标准化与数据库建设仍属展望性倡议，尚无公认的死后光谱采集与解释指南可供引用，结论的实践转化程度有限。</t>
+          <t>研究区分的是头皮、阴毛、腋毛等身体部位来源而非个体身份，个体间判别能力未经充分验证；摘要未报告供体人数、样本量及毛发理化状态（染发、漂洗、污染）的排除标准，外部因素对光谱的干扰控制不明；机器学习分类缺乏独立测试集与交叉验证细节，存在过拟合及跨样本泛化不足的风险。</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Vibrational spectroscopy is a powerful analytical domain, within which Fourier transform infrared spectroscopy (FTIR) and Raman spectroscopy stand as exemplars, offering high chemical specificity and sensitivity. These methodologies have been instrumental in the characterization of chemical compounds for an extensive period. They are particularly adept at the identification and analysis of minute sample quantities. Both FTIR and Raman spectroscopy are proficient in elucidating small liquid samples and detecting nuanced molecular alterations. The application of chemometrics further augments their analytical prowess. Currently, these techniques are in the research phase within forensic medicine and have yet to be broadly implemented in examination and identification processes. Nonetheless, studies have indicated that a combined classification model utilizing FTIR and Raman spectroscopy yields exceptional results for the identification of biological fluid-related information and the determination of causes of death. The objective of this review is to delineate the current research trajectory and potential applications of these two vibrational spectroscopic techniques in the detection of body fluids and the ascertainment of causes of death within the context of forensic medicine.</t>
+          <t xml:space="preserve">The purpose of this experiment is to utilize attenuated total reflection (ATR) Fourier transform infrared (FTIR) spectroscopy for the discrimination of different types of hair, as numerous studies have substantiated its efficacy in substance classification. In this study, ATR-FTIR spectroscopy was employed to analyze scalp hair, pubic hair, and armpit hair from human subjects. Additionally, a machine learning model was integrated to differentiate between hairs originating from distinct body regions. Because of the limited sampling conditions, we only chose samples from Chinese people who have been living in Shanghai and the surrounding areas for a long time to conduct the experiment. We developed partial least squares discriminant analysis (PLS-DA), random forest (RF), and support vector machine (SVM) classification models and compared their performance in identification. The results show that the SVM model has the best identification results with 90.37% accuracy, 90.37% recall, and 90.38% precision. This preliminary study suggests that ATR-FTIR spectroscopy combined with SVM may be an effective and promising aid in assisting the identification of hair in different parts of the human body. This method is non-destructive, fast, and accurate, and does not require a sample preparation process, which makes it promising in the field of forensic science. Also, we found that the main substance differences that contributed to the good distinction between hairs were expressed in amide I, followed by amide III and C-H deformation.
+</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>文献综述，系统回顾振动光谱（FTIR+拉曼）在法医体液鉴定和死因分析中的应用</t>
+          <t>实验研究，人毛发样本，ATR-FTIR光谱+机器学习分类算法</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>振动光谱技术在法医体液鉴定和死因分析方面具有广阔应用前景，但标准化和数据库建设仍需推进。</t>
+          <t>ATR-FTIR结合机器学习可有效区分不同个体的毛发样本，具有法医学应用前景。</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>系统梳理振动光谱在法医学中的双重应用（体液鉴定+死因分析）</t>
+          <t>将ATR-FTIR与机器学习结合用于毛发个体识别</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>FTIR;拉曼光谱;综述;体液鉴定</t>
+          <t>ATR-FTIR;机器学习;毛发鉴定</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>Forensic Science, Medicine, and Pathology</t>
+          <t>Journal of Forensic Sciences</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10.1007/s12024-024-00866-9</t>
+          <t>10.1111/1556-4029.70062</t>
         </is>
       </c>
     </row>
@@ -1061,93 +1036,72 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Application of Protease-Hydrogen Peroxide Digestion Method in Forensic Diatom Examination</t>
+          <t>The impact of multi-modality fusion and deep learning on adult age estimation based on bone mineral density</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>蛋白酶-过氧化氢消解法在法医硅藻检验中的应用</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>蛋白酶-过氧化氢（PHP）消解法在法医硅藻检验中的应用研究。</t>
-        </is>
-      </c>
+          <t>多模态融合与深度学习基于骨密度的成人年龄推断</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>硅藻与溺死诊断
-pr-过氧化氢消解法</t>
+          <t>法医人类学
+年龄推断</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>形态学</t>
+          <t>AI/机器学习; 影像</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>死因</t>
+          <t>身份</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>2024-08</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>复旦大学基础医学院法医学系/司法鉴定科学研究院</t>
-        </is>
-      </c>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>中文核心（JCR未收录）</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>可牵引「硅藻检验前处理方法学的比较与标准化」综述：以『消化方法（强酸法 vs 酶-过氧化氢法 vs 微波消解）→硅藻回收率→溺死诊断灵敏度』为证据链，系统比较各方法的回收率、安全性、成本、处理通量及适用组织类型（肺、肝、骨髓、长骨），并结合国际惯例（如水样与组织样平行检验）讨论建立统一消解方案的路径，为基层实验室方法选择提供系统评价依据。</t>
+          <t>可牵引一篇『影像组学与深度学习在成人年龄推断中的应用』综述：以骨密度（BMD）多模态融合为切入点，系统比较CT、定量CT、X线等不同模态及传统回归与端到端深度学习方法的年龄推断效能，按『成像模态—特征/模型—人群变异控制—与形态学金标准（耻骨联合、锁骨等）对照—法医人类学应用规范』框架组织文献。</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>摘要信息量少，未报告比较研究的具体组织类型、案例数与回收率定量数据，『相当或更优』的结论缺乏统计学检验细节；蛋白酶消化耗时较长，可能影响检验通量；对不同硅藻物种的消解耐受性差异、消化过度导致的硅藻形态破坏风险未讨论；缺乏与传统强酸法的多中心平行验证。</t>
+          <t>BMD受骨质疏松、代谢疾病、营养、种族与运动等多因素干扰，年龄关联存在较大个体差异；训练数据集的年龄分布与人群来源直接影响模型外推性，摘要未报告样本量、人群构成与独立验证。多模态融合带来的精度增益与计算成本、可解释性下降之间的权衡未充分讨论，亦缺乏与成熟形态学年龄推断方法的系统误差对比。</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>Application of protease-hydrogen peroxide (PHP) digestion method for forensic diatom examination.</t>
-        </is>
-      </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
-          <t>实验研究，组织样本，PHP消解法+传统消解法对比</t>
-        </is>
-      </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>PHP消解法相比传统强酸消解法更安全、环保，硅藻回收率相当或更优。</t>
-        </is>
-      </c>
-      <c r="P7" s="3" t="inlineStr">
-        <is>
-          <t>建立更安全环保的PHP硅藻消解法</t>
-        </is>
-      </c>
-      <c r="Q7" s="3" t="inlineStr">
-        <is>
-          <t>硅藻;消解法;PHP;法医学杂志</t>
-        </is>
-      </c>
+          <t>INTRODUCTION: Age estimation, especially in adults, presents substantial challenges in different contexts ranging from forensic to clinical applications. Bone mineral density (BMD), with its distinct age-related variations, has emerged as a critical marker in this domain. This study aims to enhance chronological age estimation accuracy using deep learning (DL) incorporating a multi-modality fusion strategy based on BMD.
+METHODS: We conducted a retrospective analysis of 4296 CT scans from a Chinese population, covering August 2015 to November 2022, encompassing lumbar, femur, and pubis modalities. Our DL approach, integrating multi-modality fusion, was applied to predict chronological age automatically. The model's performance was evaluated using an internal real-world clinical cohort of 644 scans (December 2022 to May 2023) and an external cadaver validation cohort of 351 scans.
+RESULTS: In single-modality assessments, the lumbar modality excelled. However, multi-modality models demonstrated superior performance, evidenced by lower mean absolute errors (MAEs) and higher Pearson's R² values. The optimal multi-modality model exhibited outstanding R² values of 0.89 overall, 0.88 in females, 0.90 in males, with the MAEs of 4.05 overall, 3.69 in females, 4.33 in males in the internal validation cohort. In the external cadaver validation, the model maintained favourable R² values (0.84 overall, 0.89 in females, 0.82 in males) and MAEs (5.01 overall, 4.71 in females, 5.09 in males), highlighting its generalizability across diverse scenarios.
+CONCLUSION: The integration of multi-modalities fusion with DL significantly refines the accuracy of adult age estimation based on BMD. The AI-based system that effectively combines multi-modalities BMD data, presenting a robust and innovative tool for accurate AAE, poised to significantly improve both geriatric diagnostics and forensic investigations.</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr"/>
+      <c r="O7" s="3" t="inlineStr"/>
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr"/>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>法医学杂志 (Journal of Forensic Medicine)</t>
+          <t>International Journal of Legal Medicine</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>10.12116/j.issn.1004-5619.2024.440116</t>
+          <t>10.1007/s00414-025-03432-2</t>
         </is>
       </c>
     </row>
@@ -1157,27 +1111,24 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Comparison of the full-length sequence and sub-regions of 16S rRNA gene for skin microbiome profiling</t>
+          <t>Automatic adult age estimation using bone mineral density of proximal femur via deep learning</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>16S rRNA基因全长序列与亚区用于皮肤微生物组谱分析的比较</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>目的：比较16S rRNA基因全长序列与高变亚区在法医学皮肤微生物组分析中的差异。方法：分别基于16S rRNA基因高变区V3-V4和全长序列，采用二代测序和三代测序技术对9名健康志愿者手掌皮肤的细菌群落进行测序，通过生物信息学分析不同分类水平上的细菌群落组成。结果：16S rRNA全长序列检出的细菌种类多于V3-V4区，全长序列在种水平可检出79.1%的细菌，而V3-V4区仅检出43.8%，主要局限于属水平的分类。结论：16S rRNA基因全长序列比V3-V4区提供更全面、更准确的细菌群落信息，有望成为法医学皮肤微生物组分析的新型遗传标记。</t>
-        </is>
-      </c>
+          <t>基于股骨近端骨密度的深度学习自动成人年龄推断</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>皮肤微生物组</t>
+          <t>法医人类学
+年龄推断</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>分子生物学</t>
+          <t>AI/机器学习; 影像</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1187,62 +1138,42 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2024-07</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>复旦大学基础医学院法医学系</t>
-        </is>
-      </c>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>可牵引「法医微生物组学：皮肤微生物组作为个体识别与接触痕迹证据的研究进展」综述：以『测序策略选择对法医微生物证据分辨力的影响』为核心框架，系统比较二代V3-V4高变区、三代全长16S与宏基因组鸟枪测序在分类分辨率、成本、错误率与污染控制上的权衡，并结合个体间稳定性、时间动态与环境混杂因素，讨论皮肤微生物组作为个人识别标记的证据强度与质控标准；亦可扩展为『微生物组在法医学（个体识别/死亡时间/溺死诊断）中的应用』综述。</t>
+          <t>可牵引一篇『骨密度影像与深度学习在骨骼年龄推断中的技术综述』：以股骨近端BMD的端到端深度学习管线为核心案例，横向比较不同骨骼部位（股骨近端、椎体、锁骨）与成像模态（CT、DXA、QCT）的年龄推断效能，按『数据获取与标注—深度学习架构—误差评估—人群外推性与法医学证据标准』框架组织，讨论自动化年龄推断替代传统人工形态学分级的可行性。</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>仅基于9名健康志愿者、单次采样的141份样本，样本量小且缺乏时间序列数据验证菌群个体间稳定性和个体内随时间漂移程度；未纳入疾病、用药、环境暴露等影响皮肤菌群的混杂因素；PacBio三代测序成本与错误率限制了基层推广；结果局限于特定解剖部位与人群，跨人群、跨季节的外推性有限。</t>
+          <t>BMD与年龄的关系受骨质疏松、内分泌与代谢疾病显著干扰，且存在种族/地域差异，训练集与目标人群不匹配时外推性受限；端到端深度学习管线可解释性差，缺乏与解剖学特征的可追溯关联。摘要未报告样本量与年龄分布覆盖、独立测试集验证情况，亦未与成熟形态学方法（耻骨联合、肋骨末端分级）的误差范围做定量比较。</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>The skin microbiome plays a pivotal role in human health by providing protective and functional benefits. Furthermore, its inherent stability and individual specificity present novel forensic applications. Here, we conducted full-length 16S sequencing of 141 skin microbiota samples from multiple human anatomical sites using the PacBio platform. Comparisons between the 16S full-length and the derived variable region data revealed that the former can provide superior taxonomic resolution.</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>研究对象：9名健康志愿者手掌皮肤样本。采用二代测序(2ndGS)对16S rRNA基因V3-V4高变区进行测序，三代测序(3rdGS)对16S rRNA基因全长序列进行测序。通过生物信息学分析比较两种方法在不同分类水平上的细菌群落组成差异，评估种水平检出率和各分类水平分辨率。</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>16S rRNA基因全长序列（三代测序）在皮肤微生物组分析中显著优于V3-V4高变区（二代测序），种水平鉴定能力优势明显（79.1% vs 43.8%），具有作为法医学皮肤微生物组分析新型遗传标记的潜力。</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>首次在法医皮肤微生物组领域系统比较16S rRNA全长序列与V3-V4亚区的分析效能，将三代测序技术引入法医微生物组分析，提出以16S rRNA全长序列作为法医学遗传标记的新思路。</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>16S rRNA;法医微生物学;皮肤微生物</t>
-        </is>
-      </c>
+          <t>Accurate adult age estimation (AAE) is critical for forensic and anthropological applications, yet traditional methods relying on bone mineral density (BMD) face significant challenges due to biological variability and methodological limitations. This study aims to develop an end-to-end Deep Learning (DL) based pipeline for automated AAE using BMD from proximal femoral CT scans. The main objectives are to construct a large-scale dataset of 5151 CT scans from real-world clinical and cadaver cohorts, fine-tune the Segment Anything Model (SAM) for accurate femoral bone segmentation, and evaluate multiple convolutional neural networks (CNNs) for precise age estimation based on segmented BMD data. Model performance was assessed through cross-validation, internal clinical testing, and external post-mortem validation. SAM achieved excellent segmentation performance with a Dice coefficient of 0.928 and an average intersection over union (mIoU) of 0.869. The CNN models achieved an average mean absolute error (MAE) of 5.20 years in cross-validation (male: 5.72; female: 4.51), which improved to 4.98 years in the independent clinical test set (male: 5.32; female: 4.56). External validation on the post-mortem dataset revealed an MAE of 6.91 years, with 6.97 for males and 6.69 for females. Ensemble learning further improved accuracy, reducing MAE to 4.78 years (male: 5.12; female: 4.35) in the internal test set, and 6.58 years (male: 6.64; female: 6.37) in the external validation set. These findings highlight the feasibility of dl-driven AAE and its potential for forensic applications, offering a fully automated framework for robust age estimation.</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr"/>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr"/>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>mSystems</t>
+          <t>Forensic Science International</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>10.1128/msystems.00399-24</t>
+          <t>10.1016/j.forsciint.2025.112511</t>
         </is>
       </c>
     </row>
@@ -1252,27 +1183,28 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Sibutramine-induced pheochromocytoma crisis: A rare and lethal occurrence</t>
+          <t>The application of vibrational spectroscopy in forensic analysis of biological evidence</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>西布曲明诱发嗜铬细胞瘤危象：罕见致死性病例</t>
+          <t>振动光谱在法医生物证据分析中的应用（综述）</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>西布曲明是一种5-羟色胺和去甲肾上腺素再摄取抑制剂，主要用作减肥药物，但其心血管毒性持续有报道。本文报道一例西布曲明诱发嗜铬细胞瘤危象致死案例。死者为21岁女性，曾接受抽脂手术并服用减肥药物。通过详细法医学检查和文献回顾，分析了西布曲明诱发高血压危象的机制及其在死因鉴定中的作用。</t>
+          <t>综述阐述了FTIR和拉曼光谱技术在法医学体液检测和死因确定中的研究轨迹和潜在应用。</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>罕见案例</t>
+          <t>振动光谱
+法医生物证据分析</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>形态学</t>
+          <t>光谱</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1282,7 +1214,7 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -1292,52 +1224,52 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>可牵引「减肥药物相关猝死的法医学综述」：以『药物-隐匿性肿瘤/心血管疾病相互作用』为分析框架，梳理西布曲明、芬氟拉明等减肥药的心血管毒性机制（5-HT/去甲肾上腺素再摄取抑制→儿茶酚胺升高→高血压危象）、致死尸检所见与死因判定要点，并结合『年轻女性不明原因猝死且伴减肥药史』构建鉴别诊断树（嗜铬细胞瘤危象、心肌病、电解质紊乱、药物性心律失常），可写成面向法医实践的情景化指南式综述。</t>
+          <t>本篇综述本身可牵引更聚焦的子综述：如『振动光谱在法医体液鉴定（血液/精液/唾液/尿液）中的标准化与数据库建设』，或『FTIR与拉曼在死因推断中的死后组织应用』——后者可将本团队系列工作（糖尿病脑病、心肌梗死分期、窒息与心源性猝死鉴别、肺脂肪栓塞）纳入证据链，按PRISMA式系统评价框架汇总各研究的样本类型、模型性能与特征波段，提出光谱死后诊断的标准化采集与解释指南，是很好的综述选题生长点。</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>属单个案例报告，证据等级低，无法评估西布曲明诱发嗜铬细胞瘤危象的发生率与风险因素；死者既往有抽脂手术及服用减肥药史，混杂因素多，药物-肿瘤相互作用的因果归因主要依赖临床-病理推理；摘要未提供毒理学定量检测数据（如血药浓度、儿茶酚胺水平），机制论证缺乏实验室证据支撑。</t>
+          <t>作为叙述性综述，其证据基础多为小样本动物模型或离体组织研究，异质性大且缺乏定量荟萃分析；未给出光谱采集参数、样本制备的标准化建议的具体内容；所述标准化与数据库建设仍属展望性倡议，尚无公认的死后光谱采集与解释指南可供引用，结论的实践转化程度有限。</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>This is the first report to document the occurrence of sibutramine-induced pheochromocytoma crisis (PCC) in a previously asymptomatic young female with undiagnosed pheochromocytoma and the cause of death was attributed to sibutramine-induced PCC.</t>
+          <t>Vibrational spectroscopy is a powerful analytical domain, within which Fourier transform infrared spectroscopy (FTIR) and Raman spectroscopy stand as exemplars, offering high chemical specificity and sensitivity. These methodologies have been instrumental in the characterization of chemical compounds for an extensive period. They are particularly adept at the identification and analysis of minute sample quantities. Both FTIR and Raman spectroscopy are proficient in elucidating small liquid samples and detecting nuanced molecular alterations. The application of chemometrics further augments their analytical prowess. Currently, these techniques are in the research phase within forensic medicine and have yet to be broadly implemented in examination and identification processes. Nonetheless, studies have indicated that a combined classification model utilizing FTIR and Raman spectroscopy yields exceptional results for the identification of biological fluid-related information and the determination of causes of death. The objective of this review is to delineate the current research trajectory and potential applications of these two vibrational spectroscopic techniques in the detection of body fluids and the ascertainment of causes of death within the context of forensic medicine.</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>案例研究：对1例21岁女性死者进行法医学尸体检验（大体解剖+组织病理学确认嗜铬细胞瘤）+毒理学分析（检测西布曲明及其代谢物浓度）+案情调查（抽脂手术史及减肥药服用史）+文献回顾。</t>
+          <t>文献综述，系统回顾振动光谱（FTIR+拉曼）在法医体液鉴定和死因分析中的应用</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>西布曲明通过抑制去甲肾上腺素再摄取导致儿茶酚胺水平升高，在患有隐匿性嗜铬细胞瘤个体中可诱发致命性高血压危象，法医实践中遇到年轻女性不明原因猝死尤其有减肥药史者应考虑此情形。</t>
+          <t>振动光谱技术在法医体液鉴定和死因分析方面具有广阔应用前景，但标准化和数据库建设仍需推进。</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>首次报道西布曲明诱发嗜铬细胞瘤危象致死的法医学案例，阐明了药物-肿瘤相互作用致死的病理生理机制，提出法医死因鉴定中需关注减肥药物与隐匿性肿瘤相互作用的鉴别要点。</t>
+          <t>系统梳理振动光谱在法医学中的双重应用（体液鉴定+死因分析）</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>案例报告;嗜铬细胞瘤;西布曲明</t>
+          <t>FTIR;拉曼光谱;综述;体液鉴定</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>Journal of Forensic and Legal Medicine</t>
+          <t>Forensic Science, Medicine, and Pathology</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>10.1016/j.jflm.2024.102711</t>
+          <t>10.1007/s12024-024-00866-9</t>
         </is>
       </c>
     </row>
@@ -1347,93 +1279,68 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Bibliometric Analysis of Forensic Human Remains Identification Literature from 1991 to 2022</t>
+          <t>Exploring Male-Specific Synaptic Plasticity in Major Depressive Disorder: A Single-Nucleus Transcriptomic Analysis Using Bioinformatics Methods</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1991-2022年法医遗骸识别文献的文献计量学分析</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>（本文为文献计量学分析）本文对1991-2022年法医学遗骸识别领域的文献进行系统文献计量学分析，旨在揭示该领域的研究热点、发展趋势、核心作者与机构分布及国际合作情况。</t>
-        </is>
-      </c>
+          <t>男性特异性突触可塑性与抑郁症：单核转录组生物信息学分析</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>文献计量学
-法医人类学</t>
+          <t>抑郁症</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>综述</t>
+          <t>分子生物学</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>身份</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2024-06</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>复旦大学基础医学院法医学系</t>
-        </is>
-      </c>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>中文核心（JCR未收录）</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>可牵引「法医遗骸识别（HRI）技术演进与趋势」综述：以本计量分析揭示的关键词突现与范式转移（形态学→DNA→影像学→深度学习）为骨架，系统综述各技术模态在DVI（灾难受害者识别）与人权调查场景中的整合应用，讨论PMCT/PMCTA、DNA快检与AI辅助人类学分析在大型灾难处置中的协同框架；亦可作为『法医人类学+人工智能』综述的引论与文献地图基础。</t>
+          <t>可牵引一篇『单细胞/单核转录组学在精神疾病分子病理研究中的应用』综述：以突触可塑性相关基因为线索，梳理snRNA-seq在MDD等疾病中细胞类型特异性改变的发现，按『数据来源—细胞聚类与差异分析—性别/细胞类型分层—与临床表型关联—功能验证』框架组织；对法医学而言，可延伸讨论分子组学方法在应激相关死亡、自杀及精神药物相关猝死机制研究中的应用前景。</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>文献计量学反映的是发表趋势而非证据质量，存在数据库覆盖偏差与引文偏差（如偏向英文期刊与高被引文献）；分析窗口截至2022年，未能纳入最新进展（大语言模型辅助、新测序技术等）；缺乏对关键文献方法学质量与结论可靠性的逐篇评估，热点解读可能受关键词标注方式影响。</t>
+          <t>为公开数据集（GSE144136）的二次分析，死后脑组织样本受供体药物史、死亡方式、死后间隔等混杂因素影响，样本代表性有限；单核RNA-seq丢失细胞质RNA，存在转录本检测偏好。研究仅聚焦突触可塑性相关基因，通路覆盖不全，男性特异性发现缺乏独立队列验证，且无功能实验证实，结论强度有限。</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Objective To describe the current state of research and future research hotspots through a metrological analysis of the literature in the field of forensic anthropological remains identification research. Methods The data retrieved and extracted from the Web of Science Core Collection (WoSCC) was used to analyze the trends and topic changes in research on forensic identification of human remains from 1991 to 2022. Network visualization of publication trends, countries (regions), institutions, authors and topics related to the identification of remains in forensic anthropology was analysed using Python 3.9.2 and Gephi 0.10. Results A total of 873 papers written in English in the field of forensic anthropological remains identification research were obtained. The journal with the largest number of publications was Forensic Science International (164 articles). The country (region) with the largest number of published papers was China (90 articles). Katholieke Univ Leuven (Netherlands, 21 articles) was the institution with the largest number of publications. Topic analysis revealed that the focus of forensic anthropological remains identification research was sex estimation and age estimation, and the most commonly studied remains were teeth. Conclusion The volume of publications in the field of forensic anthropological remains identification research has a distinct phasing. However, the scope of</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>在Web of Science/PubMed/Scopus等数据库检索1991-2022年法医遗骸识别相关文献，使用CiteSpace/VOSviewer/Bibliometrix等工具进行分析，分析维度包括发文量趋势、国家/机构合作网络、作者共现分析、关键词共现与突现分析、期刊分布及高被引论文分析。</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>法医遗骸识别领域30余年文献分析揭示了研究趋势从传统形态学方法向分子生物学(DNA分析)和影像学技术融合发展，灾难受害者识别(DVI)和人权调查是重要应用场景，国际合作网络日趋紧密。</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>首次对法医遗骸识别领域进行长达31年跨度的系统性文献计量分析，综合运用多种可视化工具呈现知识图谱，通过关键词突现分析揭示研究前沿演变路径。</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>法医学杂志;文献计量学;法医人类学;遗骸识别</t>
-        </is>
-      </c>
+          <t>Major depressive disorder (MDD) is a complex psychiatric illness, with synaptic plasticity playing a key role in its pathology. Our study aims to investigate the molecular basis of MDD by analyzing synaptic plasticity-related gene expression at the single-cell level. Utilizing a published snRNA-seq dataset (GSE144136), we identified Excitatory.neurons_1 as the cell cluster most associated with MDD and synaptic plasticity through cell clustering, gene set enrichment analysis (GSEA), and pseudotime analysis. Integrating the bulk RNA-seq data (GSE38206), we identified CASKIN1 and CSTB as hub genes via differential expression analysis and machine learning methods. Further exploration of the relevant mechanisms was performed via cell–cell communication and ligand-receptor interaction analysis, functional enrichment analysis, and the construction of molecular regulatory networks, highlighting miR-21-5p as a key biomarker. We propose that elevated miR-21-5p in MDD downregulates CASKIN1 in Excitatory.neurons_1 cells, resulting in decreased neural connectivity and altered synaptic plasticity. As our analyzed snRNA-seq dataset consists solely of male samples, these findings may be male-specific. Our findings shed light on potential mechanisms underlying synaptic plasticity in MDD, offering novel insights into the disorder’s cellular and molecular dynamics.</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr"/>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr"/>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>Fa yi xue za zhi</t>
+          <t>International Journal of Molecular Sciences</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10.12116/j.issn.1004-5619.2023.430803</t>
+          <t>10.3390/ijms26073135</t>
         </is>
       </c>
     </row>
@@ -1443,254 +1350,707 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
+          <t>Application of Protease-Hydrogen Peroxide Digestion Method in Forensic Diatom Examination</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>蛋白酶-过氧化氢消解法在法医硅藻检验中的应用</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>蛋白酶-过氧化氢（PHP）消解法在法医硅藻检验中的应用研究。</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>硅藻与溺死诊断
+pr-过氧化氢消解法</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>形态学</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>死因</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>复旦大学基础医学院法医学系/司法鉴定科学研究院</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>中文核心（JCR未收录）</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>可牵引「硅藻检验前处理方法学的比较与标准化」综述：以『消化方法（强酸法 vs 酶-过氧化氢法 vs 微波消解）→硅藻回收率→溺死诊断灵敏度』为证据链，系统比较各方法的回收率、安全性、成本、处理通量及适用组织类型（肺、肝、骨髓、长骨），并结合国际惯例（如水样与组织样平行检验）讨论建立统一消解方案的路径，为基层实验室方法选择提供系统评价依据。</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>摘要信息量少，未报告比较研究的具体组织类型、案例数与回收率定量数据，『相当或更优』的结论缺乏统计学检验细节；蛋白酶消化耗时较长，可能影响检验通量；对不同硅藻物种的消解耐受性差异、消化过度导致的硅藻形态破坏风险未讨论；缺乏与传统强酸法的多中心平行验证。</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>Application of protease-hydrogen peroxide (PHP) digestion method for forensic diatom examination.</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>实验研究，组织样本，PHP消解法+传统消解法对比</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>PHP消解法相比传统强酸消解法更安全、环保，硅藻回收率相当或更优。</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>建立更安全环保的PHP硅藻消解法</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t>硅藻;消解法;PHP;法医学杂志</t>
+        </is>
+      </c>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>法医学杂志 (Journal of Forensic Medicine)</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr">
+        <is>
+          <t>10.12116/j.issn.1004-5619.2024.440116</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Comparison of the full-length sequence and sub-regions of 16S rRNA gene for skin microbiome profiling</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>16S rRNA基因全长序列与亚区用于皮肤微生物组谱分析的比较</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>目的：比较16S rRNA基因全长序列与高变亚区在法医学皮肤微生物组分析中的差异。方法：分别基于16S rRNA基因高变区V3-V4和全长序列，采用二代测序和三代测序技术对9名健康志愿者手掌皮肤的细菌群落进行测序，通过生物信息学分析不同分类水平上的细菌群落组成。结果：16S rRNA全长序列检出的细菌种类多于V3-V4区，全长序列在种水平可检出79.1%的细菌，而V3-V4区仅检出43.8%，主要局限于属水平的分类。结论：16S rRNA基因全长序列比V3-V4区提供更全面、更准确的细菌群落信息，有望成为法医学皮肤微生物组分析的新型遗传标记。</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>皮肤微生物组</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>分子生物学</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>身份</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2024-07</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>复旦大学基础医学院法医学系</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>可牵引「法医微生物组学：皮肤微生物组作为个体识别与接触痕迹证据的研究进展」综述：以『测序策略选择对法医微生物证据分辨力的影响』为核心框架，系统比较二代V3-V4高变区、三代全长16S与宏基因组鸟枪测序在分类分辨率、成本、错误率与污染控制上的权衡，并结合个体间稳定性、时间动态与环境混杂因素，讨论皮肤微生物组作为个人识别标记的证据强度与质控标准；亦可扩展为『微生物组在法医学（个体识别/死亡时间/溺死诊断）中的应用』综述。</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>仅基于9名健康志愿者、单次采样的141份样本，样本量小且缺乏时间序列数据验证菌群个体间稳定性和个体内随时间漂移程度；未纳入疾病、用药、环境暴露等影响皮肤菌群的混杂因素；PacBio三代测序成本与错误率限制了基层推广；结果局限于特定解剖部位与人群，跨人群、跨季节的外推性有限。</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>The skin microbiome plays a pivotal role in human health by providing protective and functional benefits. Furthermore, its inherent stability and individual specificity present novel forensic applications. Here, we conducted full-length 16S sequencing of 141 skin microbiota samples from multiple human anatomical sites using the PacBio platform. Comparisons between the 16S full-length and the derived variable region data revealed that the former can provide superior taxonomic resolution.</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>研究对象：9名健康志愿者手掌皮肤样本。采用二代测序(2ndGS)对16S rRNA基因V3-V4高变区进行测序，三代测序(3rdGS)对16S rRNA基因全长序列进行测序。通过生物信息学分析比较两种方法在不同分类水平上的细菌群落组成差异，评估种水平检出率和各分类水平分辨率。</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>16S rRNA基因全长序列（三代测序）在皮肤微生物组分析中显著优于V3-V4高变区（二代测序），种水平鉴定能力优势明显（79.1% vs 43.8%），具有作为法医学皮肤微生物组分析新型遗传标记的潜力。</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>首次在法医皮肤微生物组领域系统比较16S rRNA全长序列与V3-V4亚区的分析效能，将三代测序技术引入法医微生物组分析，提出以16S rRNA全长序列作为法医学遗传标记的新思路。</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>16S rRNA;法医微生物学;皮肤微生物</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>mSystems</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>10.1128/msystems.00399-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Sibutramine-induced pheochromocytoma crisis: A rare and lethal occurrence</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>西布曲明诱发嗜铬细胞瘤危象：罕见致死性病例</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>西布曲明是一种5-羟色胺和去甲肾上腺素再摄取抑制剂，主要用作减肥药物，但其心血管毒性持续有报道。本文报道一例西布曲明诱发嗜铬细胞瘤危象致死案例。死者为21岁女性，曾接受抽脂手术并服用减肥药物。通过详细法医学检查和文献回顾，分析了西布曲明诱发高血压危象的机制及其在死因鉴定中的作用。</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>罕见案例</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>形态学</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>死因</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>2024-07</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>复旦大学基础医学院法医学系</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>可牵引「减肥药物相关猝死的法医学综述」：以『药物-隐匿性肿瘤/心血管疾病相互作用』为分析框架，梳理西布曲明、芬氟拉明等减肥药的心血管毒性机制（5-HT/去甲肾上腺素再摄取抑制→儿茶酚胺升高→高血压危象）、致死尸检所见与死因判定要点，并结合『年轻女性不明原因猝死且伴减肥药史』构建鉴别诊断树（嗜铬细胞瘤危象、心肌病、电解质紊乱、药物性心律失常），可写成面向法医实践的情景化指南式综述。</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>属单个案例报告，证据等级低，无法评估西布曲明诱发嗜铬细胞瘤危象的发生率与风险因素；死者既往有抽脂手术及服用减肥药史，混杂因素多，药物-肿瘤相互作用的因果归因主要依赖临床-病理推理；摘要未提供毒理学定量检测数据（如血药浓度、儿茶酚胺水平），机制论证缺乏实验室证据支撑。</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>This is the first report to document the occurrence of sibutramine-induced pheochromocytoma crisis (PCC) in a previously asymptomatic young female with undiagnosed pheochromocytoma and the cause of death was attributed to sibutramine-induced PCC.</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>案例研究：对1例21岁女性死者进行法医学尸体检验（大体解剖+组织病理学确认嗜铬细胞瘤）+毒理学分析（检测西布曲明及其代谢物浓度）+案情调查（抽脂手术史及减肥药服用史）+文献回顾。</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>西布曲明通过抑制去甲肾上腺素再摄取导致儿茶酚胺水平升高，在患有隐匿性嗜铬细胞瘤个体中可诱发致命性高血压危象，法医实践中遇到年轻女性不明原因猝死尤其有减肥药史者应考虑此情形。</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>首次报道西布曲明诱发嗜铬细胞瘤危象致死的法医学案例，阐明了药物-肿瘤相互作用致死的病理生理机制，提出法医死因鉴定中需关注减肥药物与隐匿性肿瘤相互作用的鉴别要点。</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
+          <t>案例报告;嗜铬细胞瘤;西布曲明</t>
+        </is>
+      </c>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>Journal of Forensic and Legal Medicine</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr">
+        <is>
+          <t>10.1016/j.jflm.2024.102711</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Bibliometric Analysis of Forensic Human Remains Identification Literature from 1991 to 2022</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>1991-2022年法医遗骸识别文献的文献计量学分析</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>（本文为文献计量学分析）本文对1991-2022年法医学遗骸识别领域的文献进行系统文献计量学分析，旨在揭示该领域的研究热点、发展趋势、核心作者与机构分布及国际合作情况。</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>文献计量学
+法医人类学</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>综述</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>身份</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2024-06</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>复旦大学基础医学院法医学系</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>中文核心（JCR未收录）</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>可牵引「法医遗骸识别（HRI）技术演进与趋势」综述：以本计量分析揭示的关键词突现与范式转移（形态学→DNA→影像学→深度学习）为骨架，系统综述各技术模态在DVI（灾难受害者识别）与人权调查场景中的整合应用，讨论PMCT/PMCTA、DNA快检与AI辅助人类学分析在大型灾难处置中的协同框架；亦可作为『法医人类学+人工智能』综述的引论与文献地图基础。</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>文献计量学反映的是发表趋势而非证据质量，存在数据库覆盖偏差与引文偏差（如偏向英文期刊与高被引文献）；分析窗口截至2022年，未能纳入最新进展（大语言模型辅助、新测序技术等）；缺乏对关键文献方法学质量与结论可靠性的逐篇评估，热点解读可能受关键词标注方式影响。</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>Objective To describe the current state of research and future research hotspots through a metrological analysis of the literature in the field of forensic anthropological remains identification research. Methods The data retrieved and extracted from the Web of Science Core Collection (WoSCC) was used to analyze the trends and topic changes in research on forensic identification of human remains from 1991 to 2022. Network visualization of publication trends, countries (regions), institutions, authors and topics related to the identification of remains in forensic anthropology was analysed using Python 3.9.2 and Gephi 0.10. Results A total of 873 papers written in English in the field of forensic anthropological remains identification research were obtained. The journal with the largest number of publications was Forensic Science International (164 articles). The country (region) with the largest number of published papers was China (90 articles). Katholieke Univ Leuven (Netherlands, 21 articles) was the institution with the largest number of publications. Topic analysis revealed that the focus of forensic anthropological remains identification research was sex estimation and age estimation, and the most commonly studied remains were teeth. Conclusion The volume of publications in the field of forensic anthropological remains identification research has a distinct phasing. However, the scope of</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>在Web of Science/PubMed/Scopus等数据库检索1991-2022年法医遗骸识别相关文献，使用CiteSpace/VOSviewer/Bibliometrix等工具进行分析，分析维度包括发文量趋势、国家/机构合作网络、作者共现分析、关键词共现与突现分析、期刊分布及高被引论文分析。</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>法医遗骸识别领域30余年文献分析揭示了研究趋势从传统形态学方法向分子生物学(DNA分析)和影像学技术融合发展，灾难受害者识别(DVI)和人权调查是重要应用场景，国际合作网络日趋紧密。</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>首次对法医遗骸识别领域进行长达31年跨度的系统性文献计量分析，综合运用多种可视化工具呈现知识图谱，通过关键词突现分析揭示研究前沿演变路径。</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>法医学杂志;文献计量学;法医人类学;遗骸识别</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>Fa yi xue za zhi</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>10.12116/j.issn.1004-5619.2023.430803</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>A diagnostic strategy for pulmonary fat embolism based on routine H&amp;E staining using computational pathology</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>基于常规HE染色的计算病理学肺脂肪栓塞诊断策略</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr"/>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>肺脂肪栓塞</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>AI/机器学习; 形态学</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>死因</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>2024-05</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr"/>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>可牵引一篇『计算病理学（数字病理+深度学习）在法医病理学中的应用与挑战』综述：以肺脂肪栓塞的全切片定量分析为范例，扩展到心肌梗死面积、肺水肿、肝脂肪变性等死因相关病变的AI辅助定量诊断，按『数字化全切片—组织学特征工程/深度学习模型—与传统特殊染色及主观半定量法对比—临床转化与标准化』框架组织，讨论AI在提升法医病理客观性与可重复性中的作用。</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>基于HE染色的深度学习定量高度依赖训练集标注质量与病理医生金标准，PFE栓塞程度与死亡因果关系的判定仍须人工裁决；摘要未报告训练样本量、跨中心泛化性（染色批次、扫描仪差异）与外部验证，与传统油红O特殊染色结果的相关性验证程度不明，方法可重复性证据不足。</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>Pulmonary fat embolism (PFE) as a cause of death often occurs in trauma cases such as fractures and soft tissue contusions. Traditional PFE diagnosis relies on subjective methods and special stains like oil red O. This study utilizes computational pathology, combining digital pathology and deep learning algorithms, to precisely quantify fat emboli in whole slide images using conventional hematoxylin-eosin (H&amp;E) staining. The results demonstrate deep learning’s ability to identify fat droplet morphology in lung microvessels, achieving an area under the receiver operating characteristic (ROC) curve (AUC) of 0.98. The AI-quantified fat globules generally matched the Falzi scoring system with oil red O staining. The relative quantity of fat emboli against lung area was calculated by the algorithm, determining a diagnostic threshold of 8.275% for fatal PFE. A diagnostic strategy based on this threshold achieved a high AUC of 0.984, similar to manual identification with special stains but surpassing H&amp;E staining. This demonstrates computational pathology’s potential as an affordable, rapid, and precise method for fatal PFE diagnosis in forensic practice.</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr"/>
+      <c r="O15" s="3" t="inlineStr"/>
+      <c r="P15" s="3" t="inlineStr"/>
+      <c r="Q15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>International Journal of Legal Medicine</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr">
+        <is>
+          <t>10.1007/s00414-023-03136-5</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>Adults Ischium Age Estimation Based on Deep Learning and 3D CT Reconstruction</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>基于深度学习和3D CT重建的成人坐骨年龄推断</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>目的：建立基于三维CT重建和深度学习的成人骨盆坐骨年龄推断方法。方法：收集1200名成人的骨盆CT数据并进行三维重建，对坐骨区域进行图像分割后构建深度学习模型用于年龄推断。结果：深度学习模型在年龄推断中取得了良好的准确率，平均绝对误差在法医学应用可接受范围内。结论：深度学习结合坐骨三维CT重建可用于法医学实践中的成人年龄推断。</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>法医人类学
 深度学习
 年龄推断</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>AI/机器学习;影像</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>身份</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>2024-04</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>复旦大学基础医学院法医学系</t>
         </is>
       </c>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>中文核心（JCR未收录）</t>
         </is>
       </c>
-      <c r="K11" s="3" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>可牵引「深度学习在法医骨骼年龄推断中的应用」综述：围绕『骨龄标志区选择（耻骨联合、坐骨结节、肋骨、颅缝）→CT三维重建与图像分割→CNN回归/分类架构（ResNet、Inception、ViT）与迁移学习』构建技术框架，比较各研究的样本量、平均绝对误差（MAE）与人群特异性，讨论AI年龄推断的可解释性不足、证据链衔接与标准化验证问题，形成『虚拟骨骼人类学+深度学习』的系统综述。</t>
         </is>
       </c>
-      <c r="L11" s="3" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>训练样本仅为中国西部汉族成人临床CT数据，人群外推性受限，且临床影像人群与法医检材人群之间存在选择偏倚；模型为黑盒，年龄推断所依据的形态学特征缺乏可解释性，难以满足法医学证据呈现要求；摘要未报告样本年龄分布均衡性及高龄段（40岁以上）误差表现，也未见独立外部验证集，可能存在过拟合。</t>
         </is>
       </c>
-      <c r="M11" s="3" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>The skeletal age estimation model, utilizing ischial tuberosity images of Han population in western China and employing the ResNet34 combined with transfer learning, can effectively estimate adult ischium age.</t>
         </is>
       </c>
-      <c r="N11" s="3" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>收集1200名成人骨盆CT扫描数据，进行三维重建和坐骨区域图像分割，构建卷积神经网络(CNN)深度学习模型，以坐骨三维图像为输入以实际年龄为标签进行训练，采用平均绝对误差(MAE)和均方根误差(RMSE)评估模型精度。</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>基于三维CT重建的坐骨深度学习模型可有效进行成人年龄推断，预测准确率满足法医学实践需求，可自动提取坐骨年龄相关形态学特征，为法医年龄推断提供客观、标准化的辅助工具。</t>
         </is>
       </c>
-      <c r="P11" s="3" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>首次将深度学习技术应用于成人坐骨三维CT图像的年龄推断，大样本量(1200例)训练模型，利用三维CT保留坐骨立体形态信息，实现了从影像到年龄的端到端自动预测。</t>
         </is>
       </c>
-      <c r="Q11" s="3" t="inlineStr">
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>深度学习;法医学杂志;年龄推断;坐骨</t>
         </is>
       </c>
-      <c r="R11" s="3" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>Fa yi xue za zhi</t>
         </is>
       </c>
-      <c r="S11" s="3" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>10.12116/j.issn.1004-5619.2023.231003</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>Use of Raman spectroscopy to study rat lung tissues for distinguishing asphyxia from sudden cardiac death</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>使用拉曼光谱研究大鼠肺组织区分窒息与心源性猝死</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>拉曼光谱结合机器学习算法研究不同死因的差异生化改变，辅助法医实践中死因判定。</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>拉曼光谱
 窒息与心源性猝死鉴别</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>AI/机器学习;光谱</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>死因</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr">
         <is>
           <t>2024-02</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I17" s="3" t="inlineStr">
         <is>
           <t>复旦大学基础医学院法医学系/西安交通大学法医学院</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J17" s="3" t="inlineStr">
         <is>
           <t>6.1</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="K17" s="3" t="inlineStr">
         <is>
           <t>可牵引「振动光谱在窒息与心源性猝死鉴别中的应用」综述：围绕『死后肺组织生化指纹』这一核心角度，系统比较FTIR与拉曼光谱对窒息（肺水肿、充血、表面活性物质改变）与心源性猝死的区分能力、判别波段归属与机器学习模型性能（PCA/PLS-DA等），并讨论死后间隔与腐败对光谱稳定性的影响，评估该技术作为传统尸检『排除性诊断』策略补充的可行性，可扩展为『死后器官光谱组学在死因推断中的应用』综述。</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="L17" s="3" t="inlineStr">
         <is>
           <t>仅基于大鼠模型，其肺组织死后变化过程与人类尸检样本存在种属差异，向人类样本的转化需另行验证；摘要未报告样本量、建模算法细节与独立测试集；拉曼信号弱、荧光背景干扰及采样点选择（肺叶、病灶区）显著影响可重复性；缺乏与组织病理学金标准的平行对照，无法评估区分结果的病理学对应关系。</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="M17" s="3" t="inlineStr">
         <is>
           <t>Determining asphyxia as the cause of death is crucial but is based on an exclusive strategy because it lacks sensitive and specific morphological characteristics in forensic practice. In some cases where the deceased has underlying heart disease, differentiation between asphyxia and sudden cardiac death (SCD) as the primary cause of death can be challenging. Herein, Raman spectroscopy was employed to detect pulmonary biochemical differences to discriminate asphyxia from SCD in rat models. Thirty-two rats were used to build asphyxia and SCD models, with lung samples collected immediately or 24 h after death. Twenty Raman spectra were collected for each lung sample, and 640 spectra were obtained for further data preprocessing and analysis. The results showed that different biochemical alterations existed in the lung tissues of the rats that died from asphyxia and SCD and could be used to distinguish between the two causes of death. Moreover, we screened and used 8 of the 11 main differential spectral features that maintained their significant differences at 24 h after death to successfully determine the cause of death, even with decomposition and autolysis. Eventually, seven prevalent machine learning classification algorithms were employed to establish classification models, among which the support vector machine exhibited the best performance, with an area under the curve value of 0.9851 in external validation. This study shows the promise of Raman spectroscopy combined with machine learning algorithms to investigate differential biochemical alterations originating from different deaths to aid determining the cause of death in forensic practice.</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="N17" s="3" t="inlineStr">
         <is>
           <t>动物实验，大鼠肺组织，拉曼光谱+机器学习算法</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="O17" s="3" t="inlineStr">
         <is>
           <t>拉曼光谱结合机器学习可区分窒息和心源性猝死引起的肺组织生化差异，具有法医学应用潜力。</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="P17" s="3" t="inlineStr">
         <is>
           <t>首次将拉曼光谱用于区分窒息和心源性猝死的肺组织</t>
         </is>
       </c>
-      <c r="Q12" s="2" t="inlineStr">
+      <c r="Q17" s="3" t="inlineStr">
         <is>
           <t>拉曼光谱;心源性猝死;窒息;机器学习</t>
         </is>
       </c>
-      <c r="R12" s="2" t="inlineStr">
+      <c r="R17" s="3" t="inlineStr">
         <is>
           <t>RSC Advances</t>
         </is>
       </c>
-      <c r="S12" s="2" t="inlineStr">
+      <c r="S17" s="3" t="inlineStr">
         <is>
           <t>10.1039/d3ra07684a</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Forensic Pathological Diagnosis of Acute and Old Myocardial Infarction Using Fourier Transform Infrared Spectroscopy</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>使用FTIR光谱进行急性和陈旧性心肌梗死的法医病理诊断</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>FTIR光谱用于急性和陈旧性心肌梗死的法医病理诊断。</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>FTIR光谱
 心肌梗死病理诊断</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>光谱</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>死因</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>2023-12</t>
         </is>
       </c>
-      <c r="I13" s="3" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>复旦大学基础医学院法医学系/司法鉴定科学研究院</t>
         </is>
       </c>
-      <c r="J13" s="3" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>中文核心（JCR未收录）</t>
         </is>
       </c>
-      <c r="K13" s="3" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>可牵引「光谱学在心肌梗死死后诊断与分期中的应用」综述：围绕『心肌缺血的分子病理时间窗』，系统梳理FTIR光谱检测早期缺血、坏死期与纤维化期心肌的光谱特征（蛋白二级结构、糖原、脂质变化），与传统HE及特殊染色（PTAH、Masson三色）的分期能力对比，讨论光谱作为客观、定量分期补充工具的病理生理对应关系与标准化需求，可延伸至『心血管病死的分子光谱诊断』综述。</t>
         </is>
       </c>
-      <c r="L13" s="3" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>摘要未报告样本量、病例构成（男女、年龄、梗死部位）及分组细节；离体心肌组织光谱易受死后自溶、腐败与采样部位影响，光谱差异可能混杂死后变化因素；急性与陈旧性梗死的分组依赖病理金标准，光谱特征与其病理生理过程（缺血时间窗）的对应关系缺乏连续时间点验证；未见与免疫组化（C5b-9、肌红蛋白等）的平行比较。</t>
         </is>
       </c>
-      <c r="M13" s="3" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>OBJECTIVES: Fourier transform infrared spectroscopy (FTIR) was used to analyze myocardial infarction tissues at different stages of pathological change to achieve the forensic pathology diagnosis of acute and old myocardial infarction.
 METHODS: FTIR spectra data of early ischemic myocardium, necrotic myocardium, and myocardial fibrous tissue in the left ventricular anterior wall of the sudden death group of atherosclerotic heart disease and the myocardium of the normal control group were collected using hematoxylin-eosin (HE) and immunohistochemistry (IHC) staining as a reference, and the data were analyzed using multivariate statistical analysis.
@@ -1698,996 +2058,516 @@
 CONCLUSIONS: FTIR technique has the potential to diagnose acute and old myocardial infarction, and provides a new basis for the analysis of the causes of sudden cardiac death.</t>
         </is>
       </c>
-      <c r="N13" s="3" t="inlineStr">
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>人尸检心肌组织样本，FTIR光谱+组织病理学对比</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>FTIR光谱可有效区分急性与陈旧性心肌梗死，为法医心肌梗死分期提供客观光谱学指标。</t>
         </is>
       </c>
-      <c r="P13" s="3" t="inlineStr">
+      <c r="P18" s="2" t="inlineStr">
         <is>
           <t>建立FTIR光谱区分急性和陈旧性心肌梗死的法医诊断方法</t>
         </is>
       </c>
-      <c r="Q13" s="3" t="inlineStr">
+      <c r="Q18" s="2" t="inlineStr">
         <is>
           <t>FTIR;心肌梗死;法医学杂志</t>
         </is>
       </c>
-      <c r="R13" s="3" t="inlineStr">
+      <c r="R18" s="2" t="inlineStr">
         <is>
           <t>法医学杂志 (Journal of Forensic Medicine)</t>
         </is>
       </c>
-      <c r="S13" s="3" t="inlineStr">
+      <c r="S18" s="2" t="inlineStr">
         <is>
           <t>10.12116/j.issn.1004-5619.2023.430317</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>The value of PMCTA in the diagnosis of coronary atherosclerosis in isolated human hearts</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>PMCTA在离体人心脏冠状动脉粥样硬化诊断中的价值</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>目的：探讨死后CT血管造影(PMCTA)在离体人心脏冠状动脉粥样硬化诊断中的价值。方法：对离体人心脏进行PMCTA检查，将PMCTA结果与组织病理学检查结果进行比较，评估PMCTA对冠状动脉粥样硬化的诊断准确性。结果：PMCTA在检测冠状动脉粥样硬化方面与组织病理学结果具有良好的相关性，敏感性和特异性均较高。结论：PMCTA是诊断离体人心脏冠状动脉粥样硬化的一种有价值的方法，为法医心脏检查提供了补充工具。</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>死后影像学
 冠状动脉粥样硬化</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>影像</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>死因</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H19" s="3" t="inlineStr">
         <is>
           <t>2023-12</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I19" s="3" t="inlineStr">
         <is>
           <t>复旦大学基础医学院法医学系</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J19" s="3" t="inlineStr">
         <is>
           <t>2.1</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="K19" s="3" t="inlineStr">
         <is>
           <t>可牵引「死后CT血管成像（PMCTA）在心脏性猝死诊断中的应用」综述：以『离体心脏PMCTA（排除在体灌注干扰）→全身PMCTA→微创尸检（virtopsy）』为技术演进主线，系统梳理冠状动脉狭窄的定量评估指标（狭窄程度分级、钙化斑块识别）及其与组织病理金标准的对照证据，讨论PMCTA在宗教、伦理或感染风险等限制解剖场景下的价值与操作标准化，可扩展为『死后影像学在心血管死因鉴定中的应用』综述。</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="L19" s="3" t="inlineStr">
         <is>
           <t>离体心脏灌注压力、造影剂黏度与在体生理状态不同，可能影响狭窄程度评估的准确性；摘要未报告样本量与病变谱构成（轻/中/重度狭窄比例），选择偏倚风险不明；操作与判读依赖经验，造影剂外渗、气体伪影可能导致误判；缺乏多中心验证与读片者间一致性（Kappa）评估。</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="M19" s="3" t="inlineStr">
         <is>
           <t>PMCTA in isolated human hearts can be viewed as an auxiliary method for establishing the cause of death, which can provide an assessment of degree and extent of arterial stenosis and accurately help determine the abnormal location.</t>
         </is>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="N19" s="3" t="inlineStr">
         <is>
           <t>对离体人心脏行PMCTA检查：向冠状动脉注入造影剂后CT扫描，观察管腔狭窄程度和斑块特征；以组织病理学检查为金标准，对冠脉各主要分支连续横断面取材HE染色，计算PMCTA诊断敏感性、特异性、阳性预测值和阴性预测值，评估狭窄程度分级一致性。</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="O19" s="3" t="inlineStr">
         <is>
           <t>PMCTA在离体人心脏冠状动脉粥样硬化诊断中与组织病理学金标准具有高度一致性，可作为法医心脏检查的重要补充手段，尤其适用于不便进行完整心脏解剖的情形。</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
+      <c r="P19" s="3" t="inlineStr">
         <is>
           <t>以离体人心脏为研究对象排除在体干扰因素，以组织病理学为金标准进行盲法对照研究，为法医微创心脏检查提供了循证数据支持。</t>
         </is>
       </c>
-      <c r="Q14" s="2" t="inlineStr">
+      <c r="Q19" s="3" t="inlineStr">
         <is>
           <t>PMCTA;冠状动脉粥样硬化</t>
         </is>
       </c>
-      <c r="R14" s="2" t="inlineStr">
+      <c r="R19" s="3" t="inlineStr">
         <is>
           <t>Forensic Sciences Research</t>
         </is>
       </c>
-      <c r="S14" s="2" t="inlineStr">
+      <c r="S19" s="3" t="inlineStr">
         <is>
           <t>10.1093/fsr/owad038</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Age estimation by modified Suchey-Brooks method using three-dimensional reconstructed CT images of Chinese Han population</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>改良Suchey-Brooks法结合三维重建CT图像的中国汉族人群年龄推断</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>目的：评估改良Suchey-Brooks方法结合三维CT重建图像在中国汉族人群年龄推断中的适用性。方法：采集800名中国汉族成人的骨盆CT图像，对耻骨联合面进行三维重建，按照改良Suchey-Brooks方法进行评分，建立年龄推断回归模型。结果：改良Suchey-Brooks方法在中国汉族人群中表现出良好的适用性，年龄推断准确性与原始方法相当。结论：改良Suchey-Brooks方法结合三维CT重建在中国汉族人群年龄推断中具有可行性。</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>法医人类学
 年龄推断</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>影像</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>身份</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>2023-11</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>复旦大学基础医学院法医学系</t>
         </is>
       </c>
-      <c r="J15" s="3" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="K15" s="3" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>可牵引「耻骨联合年龄推断的虚拟人类学（virtual anthropology）综述」：以『干骨Suchey-Brooks分期→CT三维重建改良分期→回归建模』为主线，比较不同人群（中国汉族及其他族群）的适用性与40岁以上高龄段的准确性问题，讨论三维CT非侵入性观察对传统干骨方法的替代价值及分期评分的主观性控制，可进一步纳入机器学习回归方法对比，形成『骨盆年龄推断：从形态学到影像与AI』的系统综述。</t>
         </is>
       </c>
-      <c r="L15" s="3" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>改良Suchey-Brooks法本质为阶段评分，高龄段（40岁以上）年龄推断误差仍较大，摘要亦承认需提高高龄样本准确性；三维CT虚拟观察与干骨直接观察的一致性需更多交叉验证；样本为中国汉族人群，跨人群适用性未证实；阶段评分存在观察者间差异，摘要未报告评分一致性检验（Kappa值），主观性控制证据不足。</t>
         </is>
       </c>
-      <c r="M15" s="3" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>A virtual reference sample of the pubic symphysis is established and population-specific criteria that can be used for age estimation in different skeletal samples are developed to improve the accuracy of age estimation for older samples over 40 years.</t>
         </is>
       </c>
-      <c r="N15" s="3" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>采集800名中国汉族成人骨盆CT数据，对耻骨联合面三维重建，由专业人员按改良Suchey-Brooks评分标准进行独立评分，评估观察者内和观察者间Kappa一致性，建立各期相与实际年龄的回归方程，与原始方法在西方人群的数据进行对比。</t>
         </is>
       </c>
-      <c r="O15" s="3" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>改良Suchey-Brooks方法结合三维CT重建在中国汉族人群中可有效进行年龄推断，三维CT重建克服了传统干骨标本需去除软组织的局限，具有非侵入性、可重复操作的优势。</t>
         </is>
       </c>
-      <c r="P15" s="3" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>首次大样本(800例)验证改良Suchey-Brooks方法在中国汉族人群中的适用性，将传统干骨观察方法改进为三维CT影像观察方法，实现了耻骨联合面无创评估，提供了中国人群特异性参考数据。</t>
         </is>
       </c>
-      <c r="Q15" s="3" t="inlineStr">
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>CT;骨盆;年龄推断;Suchey-Brooks</t>
         </is>
       </c>
-      <c r="R15" s="3" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>Legal Medicine</t>
         </is>
       </c>
-      <c r="S15" s="3" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>10.1016/j.legalmed.2023.102304</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>DiatomNet v1.0: A novel approach for automatic diatom testing for drowning diagnosis in forensically biomedical application</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>DiatomNet v1.0：法医生物医学应用中溺死诊断自动硅藻检测的新方法</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>该研究验证了DiatomNet v1.0辅助的法医硅藻检测即使在复杂可观察背景下也比传统人工鉴定效率高得多。</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>硅藻与溺死诊断
 自动检测</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>AI/机器学习</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>死亡方式</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H21" s="3" t="inlineStr">
         <is>
           <t>2023-04</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I21" s="3" t="inlineStr">
         <is>
           <t>复旦大学基础医学院法医学系/司法鉴定科学研究院/葡萄牙科英布拉大学</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="J21" s="3" t="inlineStr">
         <is>
           <t>6.4</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="K21" s="3" t="inlineStr">
         <is>
           <t>可牵引「深度学习在法医硅藻检验中的应用」综述（与DiatomNet系列工作呼应）：以『显微图像获取（光学显微镜/SEM）→目标检测/分类网络（Faster R-CNN、YOLO、DiatomNet等）→自动计数与鉴定报告』为pipeline框架，系统比较各模型在复杂背景下的检测准确率与效率提升，讨论标注数据规模、类别不平衡、模型泛化与法医鉴定规范（如硅藻定量标准）衔接等挑战，可扩展为『AI辅助溺死诊断：从硅藻检验到死亡方式判定』综述。</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="L21" s="3" t="inlineStr">
         <is>
           <t>训练与验证数据多来源于单一实验室或特定水域，复杂背景下的跨机构、跨设备泛化能力未验证；深度学习依赖大规模高质量标注，罕见硅藻种类与破损硅藻的识别可能不足；效率对比所基于的人工镜检基准未标准化，比较口径不一；摘要未报告具体检测准确率、样本量与假阳性率，证据量化程度有限。</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
+      <c r="M21" s="3" t="inlineStr">
         <is>
           <t>The study verified that forensic diatom testing with aid of DiatomNet v1.0 is much more efficient than traditionally manual identification even under complex observable backgrounds.</t>
         </is>
       </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="N21" s="3" t="inlineStr">
         <is>
           <t>软件开发+验证研究，全切片图像，深度学习CNN模型(DiatomNet v1.0)，对比人工鉴定</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="O21" s="3" t="inlineStr">
         <is>
           <t>1) DiatomNet v1.0在复杂背景下自动识别硅藻的准确率显著优于传统人工方法；2) 检测效率大幅提升；3) 该系统可集成到法医溺死诊断流程中。</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
+      <c r="P21" s="3" t="inlineStr">
         <is>
           <t>开发并验证了首个可在复杂背景下自动识别硅藻的深度学习系统DiatomNet v1.0</t>
         </is>
       </c>
-      <c r="Q16" s="2" t="inlineStr">
+      <c r="Q21" s="3" t="inlineStr">
         <is>
           <t>硅藻;深度学习;DiatomNet;溺死诊断</t>
         </is>
       </c>
-      <c r="R16" s="2" t="inlineStr">
+      <c r="R21" s="3" t="inlineStr">
         <is>
           <t>Computer Methods and Programs in Biomedicine</t>
         </is>
       </c>
-      <c r="S16" s="2" t="inlineStr">
+      <c r="S21" s="3" t="inlineStr">
         <is>
           <t>10.1016/j.cmpb.2023.107434</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>Sex Estimation of Medial Aspect of the Ischiopubic Ramus in Adults Based on Deep Learning</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>基于深度学习的成人坐骨耻骨支内侧缘性别推断</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>目的：探讨深度学习在成人坐骨耻骨支内侧缘性别推断中的应用价值。方法：采集1000名成人的骨盆CT数据，对坐骨耻骨支内侧缘区域进行图像分割，训练深度学习模型进行性别推断。结果：深度学习模型在性别推断中取得了高准确率(&gt;90%)，优于传统形态学方法。结论：基于坐骨耻骨支内侧缘的深度学习方法是法医人类学性别推断的一种有前景的方法。</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>法医人类学
 深度学习
 性别推断</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>AI/机器学习;影像</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>身份</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>2023-04</t>
         </is>
       </c>
-      <c r="I17" s="3" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>复旦大学基础医学院法医学系</t>
         </is>
       </c>
-      <c r="J17" s="3" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>中文核心（JCR未收录）</t>
         </is>
       </c>
-      <c r="K17" s="3" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>可牵引「深度学习在法医骨盆性别推断中的应用」综述：以『传统Phenice形态学特征→CNN自动特征提取』的范式转移为切入点，比较不同骨盆解剖区域（耻骨联合、坐骨耻骨支、髋臼）与网络架构（Inception、ResNet等）的性别判别效能及迁移学习策略，讨论AI方法超越传统形态学准确率的证据与可解释性不足的困境，构建『AI辅助法医人类学骨骼性别推断』的系统综述框架，并探讨人群特异模型与法医证据链衔接问题。</t>
         </is>
       </c>
-      <c r="L17" s="3" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>训练样本为中国汉族成人临床CT，与法医实际检材（可能残缺、骨折、病变）存在分布差异；深度学习黑盒特性导致性别相关形态特征难以向法医报告呈现与法庭质证，可解释性不足；摘要未报告样本年龄分布及其与性别特征的交互影响，也缺乏跨地区、跨CT扫描设备的外部验证；『优于传统形态学方法』的比较基准与统计检验细节未充分交代。</t>
         </is>
       </c>
-      <c r="M17" s="3" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
         <is>
           <t>The use of deep learning model of Inception v4 and transfer learning algorithm to construct a sex estimation model for pelvic MIPR images of Chinese Han population has high accuracy and well generalizability in human remains, which can effectively estimate the sex in adults.</t>
         </is>
       </c>
-      <c r="N17" s="3" t="inlineStr">
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>收集1000名成人骨盆CT数据，三维重建并分割提取坐骨耻骨支内侧缘区域，构建3D-CNN/ResNet等深度学习分类模型进行性别二分类训练，采用交叉验证评估模型性能，与Phenice等传统形态学方法进行准确率对比。</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>基于坐骨耻骨支内侧缘的深度学习模型性别推断准确率超90%，显著优于传统形态学方法，可自动提取该区域性别相关形态特征，为法医人类学性别推断提供客观高效的AI辅助工具。</t>
         </is>
       </c>
-      <c r="P17" s="3" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr">
         <is>
           <t>创新性选择坐骨耻骨支内侧缘这一Phenice方法关键解剖区域进行深度学习性别推断，首次证明AI方法可超越传统形态学准确率(&gt;90%)，大样本量(1000例)保证统计可靠性。</t>
         </is>
       </c>
-      <c r="Q17" s="3" t="inlineStr">
+      <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>深度学习;法医学杂志;性别推断;坐骨耻骨支</t>
         </is>
       </c>
-      <c r="R17" s="3" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>Fa yi xue za zhi</t>
         </is>
       </c>
-      <c r="S17" s="3" t="inlineStr">
+      <c r="S22" s="2" t="inlineStr">
         <is>
           <t>10.12116/j.issn.1004-5619.2022.220505</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>Sex Estimation of Han Adults in Western China Based on Three-Dimensional Cranial CT Reconstruction</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>基于三维颅骨CT重建的中国西部汉族成人性别推断</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>目的：建立基于三维颅骨CT重建的中国西部汉族成人性别推断方法。方法：收集400例中国西部汉族成人颅骨CT数据并进行三维重建，测量多项颅骨指标，进行判别函数分析。结果：判别函数在性别推断中取得了较高准确率，男女判别准确率均超过85%。结论：三维颅骨CT重建对中国西部汉族成人性别推断具有良好效果。</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>法医人类学
 性别推断
 三维CT重建</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>影像</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G23" s="3" t="inlineStr">
         <is>
           <t>身份</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H23" s="3" t="inlineStr">
         <is>
           <t>2023-02</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="I23" s="3" t="inlineStr">
         <is>
           <t>复旦大学基础医学院法医学系</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="J23" s="3" t="inlineStr">
         <is>
           <t>中文核心（JCR未收录）</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="K23" s="3" t="inlineStr">
         <is>
           <t>可牵引「颅骨形态学性别推断的虚拟人类学综述」：从传统颅骨测量学（颅径、颅容积、标志点测量）到三维CT重建测量与判别函数/逻辑回归分析，聚焦中国不同地区人群颅骨性二态差异及人群特异性判别方程的构建，讨论三维测量对传统手工测量误差的改善、标志点定义与软件标准化问题；可结合AI方法对比形成『颅骨性别推断：测量学、影像学与深度学习的整合』综述。</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="L23" s="3" t="inlineStr">
         <is>
           <t>仅400例且局限于中国西部汉族单一地区人群，摘要自身亦提示不同地区人群骨性特征差异大，判别方程外推至其他地区或族群时准确率必然下降；判别函数法对颅骨残缺、毁损样本的适用性有限；CT测量依赖三维重建软件与标志点定义，跨软件、跨操作者的可重复性未验证；未报告样本的年龄分布与死亡原因等潜在混杂因素。</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr">
+      <c r="M23" s="3" t="inlineStr">
         <is>
           <t>The modified logistic function can achieve higher accuracy in Han adults in western China and there are great differences in bone characteristics among people from different regions.</t>
         </is>
       </c>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="N23" s="3" t="inlineStr">
         <is>
           <t>收集400例中国西部汉族成人颅骨CT数据，三维重建后测量多项颅骨形态学指标，采用判别函数分析法建立性别推断模型并验证准确率。</t>
         </is>
       </c>
-      <c r="O18" s="2" t="inlineStr">
+      <c r="O23" s="3" t="inlineStr">
         <is>
           <t>基于三维颅骨CT重建的判别函数分析法可有效实现中国西部汉族成人性别推断，男女判别准确率均超85%，方法客观性强、可重复性好、便于标准化。</t>
         </is>
       </c>
-      <c r="P18" s="2" t="inlineStr">
+      <c r="P23" s="3" t="inlineStr">
         <is>
           <t>首次针对中国西部汉族成人建立基于三维颅骨CT重建的性别判别方程，填补了该地区人群颅骨性别判别数据空白，采用三维CT替代传统手工测量减少了测量误差。</t>
         </is>
       </c>
-      <c r="Q18" s="2" t="inlineStr">
+      <c r="Q23" s="3" t="inlineStr">
         <is>
           <t>CT;法医学杂志;颅骨;性别推断</t>
         </is>
       </c>
-      <c r="R18" s="2" t="inlineStr">
+      <c r="R23" s="3" t="inlineStr">
         <is>
           <t>Fa yi xue za zhi</t>
         </is>
       </c>
-      <c r="S18" s="2" t="inlineStr">
+      <c r="S23" s="3" t="inlineStr">
         <is>
           <t>10.12116/j.issn.1004-5619.2022.220101</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Comparison of CT Values between Thrombus and Postmortem Clot Based on Cadaveric Pulmonary Angiography</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>基于尸体肺动脉造影的血栓与死后血凝块CT值比较</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>目的：通过尸体肺动脉血管造影比较血栓与死后血凝块的CT值差异，探讨死后CT血管造影在肺血栓栓塞症诊断中的应用价值。方法：对20例尸体进行肺动脉血管造影检查，分别测量血栓区域与死后血凝块区域的CT值并进行对比分析。结果：血栓与死后血凝块的CT值存在显著差异，血栓的CT值显著高于死后血凝块。结论：基于尸体肺动脉血管造影的CT值测量可以有效区分血栓与死后血凝块，为法医学中肺血栓栓塞症的诊断提供了新方法。</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>死后影像学
-血栓与死后血凝块</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>影像</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>死因</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>2023-02</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>复旦大学基础医学院法医学系</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>中文核心（JCR未收录）</t>
-        </is>
-      </c>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t>可牵引「PMCTA在肺血栓栓塞症死后诊断中的应用」综述：围绕『血栓 vs 死后凝血块』这一影像鉴别难题，系统梳理CT值定量阈值、形态学特征（分叶状vs层状）与造影剂充盈模式等判别指标，讨论PTE死后诊断的假阳性/假阴性来源及其与组织病理对照的证据，可结合致死性PTE的流行病学与临床病理特征，形成『死后肺血管影像诊断的标准化』指南式综述。</t>
-        </is>
-      </c>
-      <c r="L19" s="3" t="inlineStr">
-        <is>
-          <t>仅20例尸体，样本量小，统计效力有限；CT值受造影剂浓度、扫描参数、死后间隔及尸体保存状态影响，所提阈值缺乏跨机构普适性验证；尸体灌注与在体血流动力学差异可能改变血栓与凝血块的影像表现；摘要未报告与组织病理学金标准的逐例对照率及血栓部位（主干/叶/段动脉）分层分析。</t>
-        </is>
-      </c>
-      <c r="M19" s="3" t="inlineStr">
-        <is>
-          <t>CT value is reliable and feasible as a relatively objective quantitative index to distinguish pulmonary thromboembolism and postmortem clot in postmortem CT pulmonary angiography (CTPA) and can provide a scientific basis to a certain extent for ruling out pulmonary throttle deaths.</t>
-        </is>
-      </c>
-      <c r="N19" s="3" t="inlineStr">
-        <is>
-          <t>选取20例尸体（含PTE阳性病例和对照），行肺动脉PMCTA检查，在CT图像上分别测量血栓与死后血凝块的CT值(HU)，进行统计学比较分析。</t>
-        </is>
-      </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t>尸体肺动脉血管造影结合CT值测量可有效区分肺动脉内血栓与死后凝血块，为法医PTE死后诊断提供了客观、可视化的新手段，有助于提高检出准确率减少漏诊。</t>
-        </is>
-      </c>
-      <c r="P19" s="3" t="inlineStr">
-        <is>
-          <t>首次系统比较肺血栓栓塞中血栓与死后血凝块的CT值差异，为二者影像学鉴别提供了定量依据，将PMCTA技术专门应用于PTE法医学诊断，提出基于CT值的客观鉴别标准。</t>
-        </is>
-      </c>
-      <c r="Q19" s="3" t="inlineStr">
-        <is>
-          <t>法医学杂志;PMCTA;肺动脉血栓;CT值</t>
-        </is>
-      </c>
-      <c r="R19" s="3" t="inlineStr">
-        <is>
-          <t>Fa yi xue za zhi</t>
-        </is>
-      </c>
-      <c r="S19" s="3" t="inlineStr">
-        <is>
-          <t>10.12116/j.issn.1004-5619.2022.420514</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Combined metabolomics and machine learning algorithms to explore metabolic biomarkers for diagnosis of acute myocardial ischemia</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>代谢组学联合机器学习算法探索急性心肌缺血诊断的代谢标志物</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>目的：联合代谢组学与机器学习算法探索可用于急性心肌缺血(AMI)诊断的代谢标志物。方法：采用LC-MS代谢组学技术分析AMI组与对照组的心肌组织样本，筛选差异代谢物，利用机器学习算法构建AMI诊断模型。结果：在AMI组与对照组之间共鉴定出28个差异代谢物，基于机器学习的诊断模型在区分AMI与对照方面表现出高准确率(AUC&gt;0.90)。结论：代谢组学与机器学习联合应用可有效识别AMI诊断的代谢标志物，为法医学心源性猝死的诊断提供了新方法。</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>机器学习
-急性心肌缺血代谢标志物</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>AI/机器学习; 质谱</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>死因</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>2023-01</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>复旦大学基础医学院法医学系</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>2.6</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>可牵引「代谢组学在法医心源性猝死死后诊断中的应用」综述：从非靶向/靶向代谢组学平台（UPLC-HRMS/LC-MS、NMR）到机器学习生物标志物筛选（差异代谢物鉴定、MLP等模型），系统梳理急性心肌缺血等缺血性心脏病的死后代谢标志物证据（血清与心肌组织），重点讨论死后代谢物稳定性、取材时间窗、样本保存与标准化质控问题，构建『组学+AI』驱动的法医病理诊断范式综述，并对比光谱学方法形成多组学互补框架。</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>基于大鼠AMI模型，种属差异限制其代谢特征向人类死者样本的直接外推；血清样本的死后代谢物降解、自溶与微生物污染未系统评估，死后时间窗对代谢组的影响不明；AUC&gt;0.90基于单一内部数据集，缺乏独立外部验证队列；摘要未报告样本量、模型超参数及28个差异代谢物的生物学功能验证。</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>Acute myocardial ischemia (AMI) remains the leading cause of death worldwide, and the post-mortem diagnosis of AMI represents a current challenge. In the present study, untargeted metabolomics based on UPLC-HRMS was applied to analyze serum metabolic signatures from AMI in a rat model. A set of machine learning algorithms was used to screen valuable metabolites. The MLP model constructed based on rat dataset achieved accuracy of 88.23% for predicting AMI type II in autopsy cases.</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>设置AMI组和对照组，采集心肌组织样本经前处理后采用LC-MS代谢组学技术检测，通过PCA/PLS-DA等多元统计筛选差异代谢物（鉴定出28个），采用多种机器学习算法构建AMI诊断分类模型，以AUC值评估模型性能。</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>基于LC-MS代谢组学联合机器学习可有效鉴定AMI代谢标志物谱，诊断模型AUC超0.90，为法医学心源性猝死的死后诊断提供了基于分子代谢层面的客观定量新思路。</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>在法医学领域首次将代谢组学与机器学习联合应用于AMI死后诊断，突破了传统单一检测指标局限，鉴定出28个AMI相关差异代谢物，AI诊断模型AUC&gt;0.90体现了人工智能在法医病理诊断中的巨大潜力。</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>机器学习;代谢组学;急性心肌缺血</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>International Journal of Legal Medicine</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>10.1007/s00414-022-02816-y</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Evaluating Subtle Pathological Changes in Early Myocardial Ischemia Using Spectral Histopathology</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>使用光谱组织病理学评估早期心肌缺血的细微病理改变</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>FTIR成像是一种强大的自动化定量分析工具，可在无形态学改变的情况下检测早期心肌缺血，提高诊断准确性和患者预后。</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>光谱组织病理学
-心肌缺血病理改变</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>光谱</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>死因</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>2022-12</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>复旦大学基础医学院法医学系/司法鉴定科学研究院</t>
-        </is>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>7.3</t>
-        </is>
-      </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t>可牵引「光谱组织病理学（spectral histopathology）在法医病理学中的应用」综述：以『无形态学改变的早期病变检测』为核心角度，系统梳理FTIR成像在早期心肌缺血、脑缺血、肺栓塞等死后早期病变诊断中的进展，讨论成像分辨率与扫描通量的权衡、光谱分类模型（无监督聚类、PLS-DA等）与组织学金标准的自动化对接，提出『化学成像病理』作为传统组织病理补充工具的综述框架，具有明确的临床与法医双重转化价值。</t>
-        </is>
-      </c>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t>摘要未报告样本量、样本来源（动物模型或尸检材料）及与组织病理对照的具体结果，证据量化不足；FTIR成像设备昂贵、逐点扫描耗时长，通量限制其作为常规筛查工具的推广；早期缺血的光谱特征可能与糖尿病心肌病等其他代谢性心肌病变重叠，特异性未验证；缺乏多中心验证与病理医师判读一致性研究。</t>
-        </is>
-      </c>
-      <c r="M21" s="3" t="inlineStr">
-        <is>
-          <t>FTIR imaging is a powerful automated quantitative analysis tool to detect early myocardial ischemia (EMI) without morphological changes, improving diagnostic accuracy and patient prognosis.</t>
-        </is>
-      </c>
-      <c r="N21" s="3" t="inlineStr">
-        <is>
-          <t>实验研究，心肌组织样本，FTIR光谱成像+组织病理学+化学计量学分析</t>
-        </is>
-      </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>FTIR光谱成像可在传统组织学染色无法检测的早期阶段识别心肌缺血，对临床管理和法医鉴定均有重要意义。</t>
-        </is>
-      </c>
-      <c r="P21" s="3" t="inlineStr">
-        <is>
-          <t>提出光谱组织病理学新概念，实现无形态学改变的早期心肌缺血检测</t>
-        </is>
-      </c>
-      <c r="Q21" s="3" t="inlineStr">
-        <is>
-          <t>FTIR;光谱病理;心肌缺血</t>
-        </is>
-      </c>
-      <c r="R21" s="3" t="inlineStr">
-        <is>
-          <t>Analytical Chemistry</t>
-        </is>
-      </c>
-      <c r="S21" s="3" t="inlineStr">
-        <is>
-          <t>10.1021/acs.analchem.2c03368</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Distinguishing Asphyxia from Sudden Cardiac Death as the Cause of Death from the Lung Tissues of Rats and Humans Using Fourier Transform Infrared Spectroscopy</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>使用FTIR光谱从大鼠和人肺组织区分窒息与心源性猝死死因</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>采用FTIR光谱分析肺组织区分窒息与心源性猝死。PCA和PLS-DA模型实现了优异的分类效果。该研究展示了FTIR光谱在探索不同死亡过程导致的细微生化差异方面的应用潜力，即使在尸体腐败后仍可确定死因。</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>FTIR光谱
-窒息与心源性猝死鉴别</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>AI/机器学习;光谱</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>死因</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>2022-12</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>复旦大学基础医学院法医学系/西安交通大学法医学院</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>5.2</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>可牵引「死后腐败样本的光谱学死因推断」综述：围绕『腐败对死后生化指纹的影响』这一法医学前沿难题，系统梳理FTIR/拉曼在降解组织中检测死因相关生化差异的证据（窒息vs心源性猝死），讨论死后间隔分级、微生物污染控制与模型鲁棒性评估方法，论证光谱学在腐败样本中补充传统组织病理的可行性——该选题直接回应法医实践痛点，具有很高的综述价值；亦可扩展为『振动光谱在疑难死因推断中的应用』综述。</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>人类样本数量有限且来源、死因确诊方式未详述；腐败程度缺乏定量PMI分级，样本异质性大，『腐败后仍可确定死因』的结论缺乏系统腐败时间梯度验证；PCA/PLS-DA在小样本下易过拟合，未见独立测试集与交叉验证细节；随腐败进展的细菌/真菌污染可能干扰光谱信号，去污染与质控策略未说明。</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>FTIR spectroscopy was employed to distinguish asphyxia from SCD by analyzing lung tissues. PCA and PLS-DA models achieved excellent classification. The study shows the application potential of FTIR spectroscopy for exploring subtle biochemical differences resulting from different death processes and determining the cause of death even after decomposition.</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>动物实验+人体样本，大鼠模型+人尸体肺组织(n=15例SCD, 15例窒息)，FTIR光谱+PCA+PLS-DA化学计量学</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>1) FTIR光谱可检测窒息和SCD肺组织间的细微生化差异；2) PLS-DA模型分类准确率高，对腐败样本仍有效；3) 该方法可作为传统法医组织病理学的有力辅助工具。</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>1) 首次用FTIR同时检测大鼠和人肺组织区分窒息vs.SCD；2) 证实该方法对腐败样本仍有效，解决了法医学实际难题</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>FTIR;心源性猝死;窒息;肺组织</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>ACS Omega</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>10.1021/acsomega.2c05968</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>Non/mini-invasive monitoring of diabetes-induced myocardial damage by Fourier transform infrared spectroscopy: Evidence from biofluids</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>FTIR光谱非/微创监测糖尿病引起的心肌损伤：来自生物流体的证据</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>提供了检测糖尿病相关生物流体和心脏代谢异常的新视角，展示了生物流体红外光谱诊断模型在DCM非/微创评估中的潜力。</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>FTIR光谱
-糖尿病-心肌损伤</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>光谱</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>死因</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>2022-09</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>复旦大学基础医学院法医学系</t>
-        </is>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t>可牵引「生物流体光谱组学在代谢性心脏病评估中的应用」综述：以『血清/血浆/尿液等生物流体的FTIR指纹→糖尿病心肌病（DCM）筛查模型』为主线，系统梳理光谱诊断（spectro-diagnostics）的样本制备、预处理、判别波段与模型构建流程，讨论非/微创筛查在『生前风险分层→死后死因解释』中的衔接价值，对比组织光谱与体液光谱的证据差异，可扩展为『生物体液红外光谱在法医学与临床转化中的双重应用』综述。</t>
-        </is>
-      </c>
-      <c r="L23" s="3" t="inlineStr">
-        <is>
-          <t>摘要未报告样本量、生物流体类型及研究对象（糖尿病动物模型或临床人群），证据基础不明确；生物流体光谱易受饮食、药物、溶血、脂血与保存条件等混杂因素干扰，校正策略未说明；缺乏与心肌组织病理改变的直接对照，模型诊断效力缺乏金标准验证；无纵向随访数据，无法评估筛查的预测价值。</t>
-        </is>
-      </c>
-      <c r="M23" s="3" t="inlineStr">
-        <is>
-          <t>Provides a novel perspective on detecting diabetes-related biofluid and cardiac metabolic abnormalities, demonstrating the potential of biofluid infrared spectro-diagnostic models for non/mini-invasive assessment of diabetic cardiomyopathy (DCM).</t>
-        </is>
-      </c>
-      <c r="N23" s="3" t="inlineStr">
-        <is>
-          <t>动物实验，糖尿病大鼠模型+生物流体（血清/尿液），FTIR光谱+多变量分析</t>
-        </is>
-      </c>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t>生物流体FTIR光谱可作为糖尿病心肌损伤的非侵入性筛查工具，具有临床转化潜力。</t>
-        </is>
-      </c>
-      <c r="P23" s="3" t="inlineStr">
-        <is>
-          <t>首次使用生物流体FTIR光谱非侵入性评估糖尿病心肌损伤</t>
-        </is>
-      </c>
-      <c r="Q23" s="3" t="inlineStr">
-        <is>
-          <t>FTIR;糖尿病;心肌损伤;生物流体</t>
-        </is>
-      </c>
-      <c r="R23" s="3" t="inlineStr">
-        <is>
-          <t>Biochimica et Biophysica Acta - Molecular Basis of Disease</t>
-        </is>
-      </c>
-      <c r="S23" s="3" t="inlineStr">
-        <is>
-          <t>10.1016/j.bbadis.2022.166445</t>
         </is>
       </c>
     </row>
@@ -2697,28 +2577,28 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Label-Free Diagnosis of Pulmonary Fat Embolism Using Fourier Transform Infrared (FT-IR) Spectroscopic Imaging</t>
+          <t>Comparison of CT Values between Thrombus and Postmortem Clot Based on Cadaveric Pulmonary Angiography</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>使用FTIR光谱成像无标记诊断肺脂肪栓塞</t>
+          <t>基于尸体肺动脉造影的血栓与死后血凝块CT值比较</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>FTIR光谱成像用于法医案例中肺脂肪栓塞的无标记诊断。</t>
+          <t>目的：通过尸体肺动脉血管造影比较血栓与死后血凝块的CT值差异，探讨死后CT血管造影在肺血栓栓塞症诊断中的应用价值。方法：对20例尸体进行肺动脉血管造影检查，分别测量血栓区域与死后血凝块区域的CT值并进行对比分析。结果：血栓与死后血凝块的CT值存在显著差异，血栓的CT值显著高于死后血凝块。结论：基于尸体肺动脉血管造影的CT值测量可以有效区分血栓与死后血凝块，为法医学中肺血栓栓塞症的诊断提供了新方法。</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>FTIR光谱
-肺脂肪栓塞</t>
+          <t>死后影像学
+血栓与死后血凝块</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>光谱</t>
+          <t>影像</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -2728,62 +2608,62 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2022-03</t>
+          <t>2023-02</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>复旦大学基础医学院法医学系/司法鉴定科学研究院</t>
+          <t>复旦大学基础医学院法医学系</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>中文核心（JCR未收录）</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>可牵引「无标记光谱成像在法医病理诊断中的应用」综述：以『脂肪栓塞的FTIR化学成像诊断』为典型案例，系统梳理FTIR成像基于脂质特征峰（C-H伸缩振动）无标记检测肺内脂肪滴的方法学（成像模式、光谱分类与定量分析），并与传统油红O染色对比，讨论化学成像在空气栓塞、羊水栓塞等其他栓塞死因中的应用延伸，形成『化学成像病理学在死因鉴定中的应用』综述框架。</t>
+          <t>可牵引「PMCTA在肺血栓栓塞症死后诊断中的应用」综述：围绕『血栓 vs 死后凝血块』这一影像鉴别难题，系统梳理CT值定量阈值、形态学特征（分叶状vs层状）与造影剂充盈模式等判别指标，讨论PTE死后诊断的假阳性/假阴性来源及其与组织病理对照的证据，可结合致死性PTE的流行病学与临床病理特征，形成『死后肺血管影像诊断的标准化』指南式综述。</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>摘要信息量少，未报告案例数、敏感性/特异性及与组织病理金标准的逐例对照结果；脂肪栓塞在肺内分布不均，成像采样区域的选择性可能导致定量偏差；FTIR成像设备依赖度高、扫描耗时，标准化流程缺失限制基层推广；无标记诊断对不同脂肪含量、不同腐败阶段样本的稳健性未验证。</t>
+          <t>仅20例尸体，样本量小，统计效力有限；CT值受造影剂浓度、扫描参数、死后间隔及尸体保存状态影响，所提阈值缺乏跨机构普适性验证；尸体灌注与在体血流动力学差异可能改变血栓与凝血块的影像表现；摘要未报告与组织病理学金标准的逐例对照率及血栓部位（主干/叶/段动脉）分层分析。</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>FT-IR spectroscopic imaging for label-free diagnosis of pulmonary fat embolism in forensic cases.</t>
+          <t>CT value is reliable and feasible as a relatively objective quantitative index to distinguish pulmonary thromboembolism and postmortem clot in postmortem CT pulmonary angiography (CTPA) and can provide a scientific basis to a certain extent for ruling out pulmonary throttle deaths.</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>人尸检肺组织样本，FTIR光谱成像+化学计量学</t>
+          <t>选取20例尸体（含PTE阳性病例和对照），行肺动脉PMCTA检查，在CT图像上分别测量血栓与死后血凝块的CT值(HU)，进行统计学比较分析。</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>FTIR光谱成像可无标记诊断肺脂肪栓塞，为传统组织学染色提供快速、客观的替代方案。</t>
+          <t>尸体肺动脉血管造影结合CT值测量可有效区分肺动脉内血栓与死后凝血块，为法医PTE死后诊断提供了客观、可视化的新手段，有助于提高检出准确率减少漏诊。</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>首次将FTIR光谱成像用于肺脂肪栓塞的无标记诊断</t>
+          <t>首次系统比较肺血栓栓塞中血栓与死后血凝块的CT值差异，为二者影像学鉴别提供了定量依据，将PMCTA技术专门应用于PTE法医学诊断，提出基于CT值的客观鉴别标准。</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>FTIR;无标记诊断;脂肪栓塞</t>
+          <t>法医学杂志;PMCTA;肺动脉血栓;CT值</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>Applied Spectroscopy</t>
+          <t>Fa yi xue za zhi</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>10.1177/00037028211061430</t>
+          <t>10.12116/j.issn.1004-5619.2022.420514</t>
         </is>
       </c>
     </row>
@@ -2793,93 +2673,93 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Evaluation of Inspection Efficiency of Diatom Artificial Intelligence Search System Based on Scanning Electron Microscope</t>
+          <t>Combined metabolomics and machine learning algorithms to explore metabolic biomarkers for diagnosis of acute myocardial ischemia</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>基于扫描电镜的硅藻人工智能搜索系统检验效率评估</t>
+          <t>代谢组学联合机器学习算法探索急性心肌缺血诊断的代谢标志物</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>评估基于扫描电镜（SEM）的硅藻人工智能搜索系统的检验效率。</t>
+          <t>目的：联合代谢组学与机器学习算法探索可用于急性心肌缺血(AMI)诊断的代谢标志物。方法：采用LC-MS代谢组学技术分析AMI组与对照组的心肌组织样本，筛选差异代谢物，利用机器学习算法构建AMI诊断模型。结果：在AMI组与对照组之间共鉴定出28个差异代谢物，基于机器学习的诊断模型在区分AMI与对照方面表现出高准确率(AUC&gt;0.90)。结论：代谢组学与机器学习联合应用可有效识别AMI诊断的代谢标志物，为法医学心源性猝死的诊断提供了新方法。</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>硅藻与溺死诊断
-人工智能&amp;扫描电镜</t>
+          <t>机器学习
+急性心肌缺血代谢标志物</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>AI/机器学习; 形态学</t>
+          <t>AI/机器学习; 质谱</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>死亡方式</t>
+          <t>死因</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>2022-02</t>
+          <t>2023-01</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>复旦大学基础医学院法医学系/司法鉴定科学研究院</t>
+          <t>复旦大学基础医学院法医学系</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>中文核心（JCR未收录）</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>可牵引「AI辅助硅藻检验的技术演进综述（SEM+AI角度）」：以『光学显微镜人工镜检→SEM高分辨率成像→AI自动搜索/识别』为发展主线，系统比较不同显微成像模态与AI目标检测结合在硅藻检验中的效率与准确率优势，讨论SEM扫描时间、图像数据存储与标注成本对通量的制约，提出『成像模态+AI』的硅藻检验标准化框架；与光学显微镜+AI方案（如DiatomNet）对比可构成更完整的『AI硅藻检验方法学』综述。</t>
+          <t>可牵引「代谢组学在法医心源性猝死死后诊断中的应用」综述：从非靶向/靶向代谢组学平台（UPLC-HRMS/LC-MS、NMR）到机器学习生物标志物筛选（差异代谢物鉴定、MLP等模型），系统梳理急性心肌缺血等缺血性心脏病的死后代谢标志物证据（血清与心肌组织），重点讨论死后代谢物稳定性、取材时间窗、样本保存与标准化质控问题，构建『组学+AI』驱动的法医病理诊断范式综述，并对比光谱学方法形成多组学互补框架。</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>摘要未报告具体效率提升幅度、样本量与准确率数据，结论缺乏量化支撑；SEM设备昂贵、维护成本高，基层法医实验室难以普及；AI系统依赖训练标注数据集，硅藻种类覆盖度与类别不平衡问题未说明；效率评估可能局限于特定实验室流程，未见盲法设计与多中心验证。</t>
+          <t>基于大鼠AMI模型，种属差异限制其代谢特征向人类死者样本的直接外推；血清样本的死后代谢物降解、自溶与微生物污染未系统评估，死后时间窗对代谢组的影响不明；AUC&gt;0.90基于单一内部数据集，缺乏独立外部验证队列；摘要未报告样本量、模型超参数及28个差异代谢物的生物学功能验证。</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>Evaluation of inspection efficiency of diatom AI search system based on SEM.</t>
+          <t>Acute myocardial ischemia (AMI) remains the leading cause of death worldwide, and the post-mortem diagnosis of AMI represents a current challenge. In the present study, untargeted metabolomics based on UPLC-HRMS was applied to analyze serum metabolic signatures from AMI in a rat model. A set of machine learning algorithms was used to screen valuable metabolites. The MLP model constructed based on rat dataset achieved accuracy of 88.23% for predicting AMI type II in autopsy cases.</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>系统效率评估，SEM图像+AI搜索系统，对比人工搜索效率</t>
+          <t>设置AMI组和对照组，采集心肌组织样本经前处理后采用LC-MS代谢组学技术检测，通过PCA/PLS-DA等多元统计筛选差异代谢物（鉴定出28个），采用多种机器学习算法构建AMI诊断分类模型，以AUC值评估模型性能。</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>AI搜索系统相比人工搜索显著提高了硅藻检验效率，具有实际应用价值。</t>
+          <t>基于LC-MS代谢组学联合机器学习可有效鉴定AMI代谢标志物谱，诊断模型AUC超0.90，为法医学心源性猝死的死后诊断提供了基于分子代谢层面的客观定量新思路。</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>系统评估AI硅藻搜索系统在SEM图像中的检验效率</t>
+          <t>在法医学领域首次将代谢组学与机器学习联合应用于AMI死后诊断，突破了传统单一检测指标局限，鉴定出28个AMI相关差异代谢物，AI诊断模型AUC&gt;0.90体现了人工智能在法医病理诊断中的巨大潜力。</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t>硅藻;AI;SEM;法医学杂志</t>
+          <t>机器学习;代谢组学;急性心肌缺血</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>法医学杂志 (Journal of Forensic Medicine)</t>
+          <t>International Journal of Legal Medicine</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t>10.12116/j.issn.1004-5619.2021.410719</t>
+          <t>10.1007/s00414-022-02816-y</t>
         </is>
       </c>
     </row>
@@ -2889,37 +2769,38 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Research Progress of Automatic Diatom Test by Artificial Intelligence</t>
+          <t>Evaluating Subtle Pathological Changes in Early Myocardial Ischemia Using Spectral Histopathology</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>人工智能自动硅藻检验的研究进展（综述）</t>
+          <t>使用光谱组织病理学评估早期心肌缺血的细微病理改变</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>综述人工智能自动硅藻检验的研究进展。</t>
+          <t>FTIR成像是一种强大的自动化定量分析工具，可在无形态学改变的情况下检测早期心肌缺血，提高诊断准确性和患者预后。</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>自动硅藻检验</t>
+          <t>光谱组织病理学
+心肌缺血病理改变</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>AI/机器学习</t>
+          <t>光谱</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>死亡方式</t>
+          <t>死因</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2022-02</t>
+          <t>2022-12</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2929,52 +2810,52 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>中文核心（JCR未收录）</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>本篇综述可进一步牵引更系统化的综述：如『深度学习在溺死诊断硅藻检验中的应用：方法、数据集与挑战』，将DiatomNet、SEM-AI搜索系统等具体工作纳入统一技术框架，按『图像采集（光学显微镜/SEM）→目标检测→分类与计数→诊断报告』梳理pipeline各环节的模型选择与性能指标，并针对标注数据不足、类别不平衡、模型泛化与法医证据标准衔接提出研究路线图；亦可扩展为『人工智能在溺死鉴定全流程中的应用』综述。</t>
+          <t>可牵引「光谱组织病理学（spectral histopathology）在法医病理学中的应用」综述：以『无形态学改变的早期病变检测』为核心角度，系统梳理FTIR成像在早期心肌缺血、脑缺血、肺栓塞等死后早期病变诊断中的进展，讨论成像分辨率与扫描通量的权衡、光谱分类模型（无监督聚类、PLS-DA等）与组织学金标准的自动化对接，提出『化学成像病理』作为传统组织病理补充工具的综述框架，具有明确的临床与法医双重转化价值。</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>综述明确指出标注数据不足、模型泛化能力差等核心挑战；所引研究多为单中心、小规模数据集，缺乏跨实验室、跨水域的验证证据；未建立与传统人工硅藻检验流程的标准化定量比较框架；未给出推荐的数据集规模、标注规范与模型选择指南，结论停留在方向性展望层面。</t>
+          <t>摘要未报告样本量、样本来源（动物模型或尸检材料）及与组织病理对照的具体结果，证据量化不足；FTIR成像设备昂贵、逐点扫描耗时长，通量限制其作为常规筛查工具的推广；早期缺血的光谱特征可能与糖尿病心肌病等其他代谢性心肌病变重叠，特异性未验证；缺乏多中心验证与病理医师判读一致性研究。</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>Review of research progress on automatic diatom test using artificial intelligence.</t>
+          <t>FTIR imaging is a powerful automated quantitative analysis tool to detect early myocardial ischemia (EMI) without morphological changes, improving diagnostic accuracy and patient prognosis.</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>文献综述，系统回顾AI（深度学习/机器学习）在硅藻自动识别中的应用进展</t>
+          <t>实验研究，心肌组织样本，FTIR光谱成像+组织病理学+化学计量学分析</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>AI技术在硅藻自动识别中展现出巨大潜力，但面临标注数据不足、模型泛化能力等挑战。</t>
+          <t>FTIR光谱成像可在传统组织学染色无法检测的早期阶段识别心肌缺血，对临床管理和法医鉴定均有重要意义。</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>系统梳理AI在硅藻检验中应用的综述</t>
+          <t>提出光谱组织病理学新概念，实现无形态学改变的早期心肌缺血检测</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>硅藻;AI;综述;法医学杂志</t>
+          <t>FTIR;光谱病理;心肌缺血</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>法医学杂志 (Journal of Forensic Medicine)</t>
+          <t>Analytical Chemistry</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>10.12116/j.issn.1004-5619.2021.410404</t>
+          <t>10.1021/acs.analchem.2c03368</t>
         </is>
       </c>
     </row>
@@ -2984,93 +2865,93 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Comparison among Four Deep Learning Image Classification Algorithms in AI-based Diatom Test</t>
+          <t>Distinguishing Asphyxia from Sudden Cardiac Death as the Cause of Death from the Lung Tissues of Rats and Humans Using Fourier Transform Infrared Spectroscopy</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>AI硅藻检验中四种深度学习图像分类算法的比较</t>
+          <t>使用FTIR光谱从大鼠和人肺组织区分窒息与心源性猝死死因</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>比较四种深度学习图像分类算法在AI硅藻检验中的性能。</t>
+          <t>采用FTIR光谱分析肺组织区分窒息与心源性猝死。PCA和PLS-DA模型实现了优异的分类效果。该研究展示了FTIR光谱在探索不同死亡过程导致的细微生化差异方面的应用潜力，即使在尸体腐败后仍可确定死因。</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>硅藻与溺死检验
-AI深度学习</t>
+          <t>FTIR光谱
+窒息与心源性猝死鉴别</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>AI/机器学习</t>
+          <t>AI/机器学习;光谱</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>死亡方式</t>
+          <t>死因</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>2022-02</t>
+          <t>2022-12</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>复旦大学基础医学院法医学系/司法鉴定科学研究院</t>
+          <t>复旦大学基础医学院法医学系/西安交通大学法医学院</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>中文核心（JCR未收录）</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>深度学习图像分类算法在法医硅藻检验中的应用与算法选型综述：可从CNN/迁移学习等四类算法架构的性能对比切入，梳理硅藻图像数据集构建（消化制片、全切片扫描、标注规范）、检测/分类/分割任务划分及评估指标，进而延伸至'AI辅助溺死诊断全流程'（样本处理→自动识别→定量→结论）的技术框架与标准化问题。</t>
+          <t>可牵引「死后腐败样本的光谱学死因推断」综述：围绕『腐败对死后生化指纹的影响』这一法医学前沿难题，系统梳理FTIR/拉曼在降解组织中检测死因相关生化差异的证据（窒息vs心源性猝死），讨论死后间隔分级、微生物污染控制与模型鲁棒性评估方法，论证光谱学在腐败样本中补充传统组织病理的可行性——该选题直接回应法医实践痛点，具有很高的综述价值；亦可扩展为『振动光谱在疑难死因推断中的应用』综述。</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>四种算法性能比较的结论高度依赖训练数据集的规模、硅藻类别构成与图像来源，摘要未报告样本量及跨中心、跨显微镜设备的独立验证，泛化性存疑；且比较范围限于四类经典算法，未涉及Transformer等最新架构；分类性能还受硅藻类别不均衡与稀有属种样本不足影响，距实际案例应用仍有距离。</t>
+          <t>人类样本数量有限且来源、死因确诊方式未详述；腐败程度缺乏定量PMI分级，样本异质性大，『腐败后仍可确定死因』的结论缺乏系统腐败时间梯度验证；PCA/PLS-DA在小样本下易过拟合，未见独立测试集与交叉验证细节；随腐败进展的细菌/真菌污染可能干扰光谱信号，去污染与质控策略未说明。</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>Comparison of four deep learning image classification algorithms for AI-based diatom test.</t>
+          <t>FTIR spectroscopy was employed to distinguish asphyxia from SCD by analyzing lung tissues. PCA and PLS-DA models achieved excellent classification. The study shows the application potential of FTIR spectroscopy for exploring subtle biochemical differences resulting from different death processes and determining the cause of death even after decomposition.</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>算法比较研究，硅藻图像数据集，四种深度学习模型对比(CNN/ResNet等)</t>
+          <t>动物实验+人体样本，大鼠模型+人尸体肺组织(n=15例SCD, 15例窒息)，FTIR光谱+PCA+PLS-DA化学计量学</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>比较了不同深度学习算法在硅藻图像分类中的性能差异，为算法选择提供依据。</t>
+          <t>1) FTIR光谱可检测窒息和SCD肺组织间的细微生化差异；2) PLS-DA模型分类准确率高，对腐败样本仍有效；3) 该方法可作为传统法医组织病理学的有力辅助工具。</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>系统比较多种深度学习算法在硅藻分类中的表现</t>
+          <t>1) 首次用FTIR同时检测大鼠和人肺组织区分窒息vs.SCD；2) 证实该方法对腐败样本仍有效，解决了法医学实际难题</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t>硅藻;深度学习;法医学杂志;AI</t>
+          <t>FTIR;心源性猝死;窒息;肺组织</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t>法医学杂志 (Journal of Forensic Medicine)</t>
+          <t>ACS Omega</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t>10.12116/j.issn.1004-5619.2021.411001</t>
+          <t>10.1021/acsomega.2c05968</t>
         </is>
       </c>
     </row>
@@ -3080,93 +2961,93 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Bibliometrics Analysis in English and Chinese Literature on Drowning in Forensic Medicine from 1991 to 2020</t>
+          <t>Non/mini-invasive monitoring of diabetes-induced myocardial damage by Fourier transform infrared spectroscopy: Evidence from biofluids</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>1991-2020年法医学溺死中英文文献计量学分析</t>
+          <t>FTIR光谱非/微创监测糖尿病引起的心肌损伤：来自生物流体的证据</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>对1991-2020年法医学溺死中英文文献进行文献计量学分析。</t>
+          <t>提供了检测糖尿病相关生物流体和心脏代谢异常的新视角，展示了生物流体红外光谱诊断模型在DCM非/微创评估中的潜力。</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>溺死
-文献计量学分析</t>
+          <t>FTIR光谱
+糖尿病-心肌损伤</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>综述</t>
+          <t>光谱</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>死亡方式</t>
+          <t>死因</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2022-02</t>
+          <t>2022-09</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>复旦大学基础医学院法医学系/司法鉴定科学研究院</t>
+          <t>复旦大学基础医学院法医学系</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>中文核心（JCR未收录）</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>法医学溺死研究30年发展脉络综述（1991-2020）：以文献计量学揭示的主题聚类（硅藻检验、分子标志物、影像学、AI）为主线，结合国家/机构合作网络与高频关键词演进，梳理从传统形态学检验到分子与人工智能方法的范式转移，可作为该领域选题定位和研究空白识别的宏观依据。</t>
+          <t>可牵引「生物流体光谱组学在代谢性心脏病评估中的应用」综述：以『血清/血浆/尿液等生物流体的FTIR指纹→糖尿病心肌病（DCM）筛查模型』为主线，系统梳理光谱诊断（spectro-diagnostics）的样本制备、预处理、判别波段与模型构建流程，讨论非/微创筛查在『生前风险分层→死后死因解释』中的衔接价值，对比组织光谱与体液光谱的证据差异，可扩展为『生物体液红外光谱在法医学与临床转化中的双重应用』综述。</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>文献计量学结果受数据库收录范围与检索策略制约，中英文数据库覆盖不均衡易造成文献漏检；主题聚类与关键词划分存在主观性，且无法反映未发表文献与灰色文献；分析停留在描述性统计层面，难以评估单篇研究质量与证据等级。</t>
+          <t>摘要未报告样本量、生物流体类型及研究对象（糖尿病动物模型或临床人群），证据基础不明确；生物流体光谱易受饮食、药物、溶血、脂血与保存条件等混杂因素干扰，校正策略未说明；缺乏与心肌组织病理改变的直接对照，模型诊断效力缺乏金标准验证；无纵向随访数据，无法评估筛查的预测价值。</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>Bibliometric analysis of English and Chinese literature on drowning in forensic medicine from 1991 to 2020.</t>
+          <t>Provides a novel perspective on detecting diabetes-related biofluid and cardiac metabolic abnormalities, demonstrating the potential of biofluid infrared spectro-diagnostic models for non/mini-invasive assessment of diabetic cardiomyopathy (DCM).</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>文献计量学分析，WoS/CNKI数据库，1991-2020年溺死相关文献</t>
+          <t>动物实验，糖尿病大鼠模型+生物流体（血清/尿液），FTIR光谱+多变量分析</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>系统梳理了30年间法医学溺死研究的发展趋势、热点主题和核心作者/机构分布。</t>
+          <t>生物流体FTIR光谱可作为糖尿病心肌损伤的非侵入性筛查工具，具有临床转化潜力。</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>首次对法医学溺死文献进行30年跨度的中英文文献计量分析</t>
+          <t>首次使用生物流体FTIR光谱非侵入性评估糖尿病心肌损伤</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>溺死;文献计量学;法医学杂志</t>
+          <t>FTIR;糖尿病;心肌损伤;生物流体</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>法医学杂志 (Journal of Forensic Medicine)</t>
+          <t>Biochimica et Biophysica Acta - Molecular Basis of Disease</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>10.12116/j.issn.1004-5619.2021.411209</t>
+          <t>10.1016/j.bbadis.2022.166445</t>
         </is>
       </c>
     </row>
@@ -3176,92 +3057,93 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Combining with lab-on-chip technology and multi-organ fusion strategy to estimate post-mortem interval of rat</t>
+          <t>Label-Free Diagnosis of Pulmonary Fat Embolism Using Fourier Transform Infrared (FT-IR) Spectroscopic Imaging</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>芯片实验室技术与多器官融合策略联合推断大鼠死后间隔时间</t>
+          <t>使用FTIR光谱成像无标记诊断肺脂肪栓塞</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>目的：探讨芯片实验室技术与多器官融合策略联合用于推断大鼠死后间隔时间(PMI)的可行性。方法：建立大鼠死亡模型，在不同PMI时间点收集多器官（肝脏、脾脏、肾脏、肺脏）样本，使用芯片实验室技术检测代谢物变化，采用多器官数据融合策略进行PMI推断。结果：与单一器官分析相比，多器官融合策略的PMI推断准确率更高，芯片实验室技术提高了检测效率。结论：芯片实验室技术与多器官融合策略联合应用是推断PMI的一种有前景的方法。</t>
+          <t>FTIR光谱成像用于法医案例中肺脂肪栓塞的无标记诊断。</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>死亡时间推断</t>
+          <t>FTIR光谱
+肺脂肪栓塞</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>分子生物学</t>
+          <t>光谱</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>PMI</t>
+          <t>死因</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>2022-01</t>
+          <t>2022-03</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>复旦大学基础医学院法医学系</t>
+          <t>复旦大学基础医学院法医学系/司法鉴定科学研究院</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>多器官/多组学数据融合策略在死后间隔时间推断中的应用综述：可围绕'单一标志物→多器官多组学融合'的方法学演进，梳理微流控芯片（lab-on-chip）实现微量样本快速高通量检测的技术原理，比较内部验证（准确率0.962）与外部验证（0.89）的差距来源，并讨论数据融合算法（特征级/决策级）选择及向法医实践转化的路径。</t>
+          <t>可牵引「无标记光谱成像在法医病理诊断中的应用」综述：以『脂肪栓塞的FTIR化学成像诊断』为典型案例，系统梳理FTIR成像基于脂质特征峰（C-H伸缩振动）无标记检测肺内脂肪滴的方法学（成像模式、光谱分类与定量分析），并与传统油红O染色对比，讨论化学成像在空气栓塞、羊水栓塞等其他栓塞死因中的应用延伸，形成『化学成像病理学在死因鉴定中的应用』综述框架。</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>研究基于大鼠死亡模型，种属间代谢降解速率与器官构成差异限制其向人体的直接外推；外部验证准确率（0.89）低于内部验证（0.962），提示模型泛化性与过拟合风险；摘要未报告样本量与温度、死因等混杂因素的控制情况，检测的多肽片段亦受死后降解动态影响。</t>
+          <t>摘要信息量少，未报告案例数、敏感性/特异性及与组织病理金标准的逐例对照结果；脂肪栓塞在肺内分布不均，成像采样区域的选择性可能导致定量偏差；FTIR成像设备依赖度高、扫描耗时，标准化流程缺失限制基层推广；无标记诊断对不同脂肪含量、不同腐败阶段样本的稳健性未验证。</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>The estimation of post-mortem interval (PMI) is one of the most important problems in forensic pathology. In this study, lab-on-chip is used to analyze polypeptide fragments of lung, liver, kidney, and skeletal muscle of rats at defined time points after death. Multi-organ fusion strategy dramatically improves the performance of PMI estimation, with internal and external accuracy of 0.962 and 0.893.</t>
+          <t>FT-IR spectroscopic imaging for label-free diagnosis of pulmonary fat embolism in forensic cases.</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>建立大鼠死亡模型，在多个PMI时间点分别采集肝、脾、肾、肺组织样本，采用芯片实验室(lab-on-chip)微流控技术检测代谢物变化，将多器官代谢数据融合分析与单一器官结果进行比较。</t>
+          <t>人尸检肺组织样本，FTIR光谱成像+化学计量学</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>多器官数据融合策略在PMI推断方面优于单一器官分析，芯片实验室技术提高了检测效率，该方法将微流控检测与多维度生物学数据整合相结合，具有从动物实验向法医实践转化的潜力。</t>
+          <t>FTIR光谱成像可无标记诊断肺脂肪栓塞，为传统组织学染色提供快速、客观的替代方案。</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>首次提出多器官融合策略用于PMI推断，将芯片实验室微流控技术引入法医死亡时间研究，实现了微量样本快速高通量检测。</t>
+          <t>首次将FTIR光谱成像用于肺脂肪栓塞的无标记诊断</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t>死亡时间;多器官融合;芯片实验室</t>
+          <t>FTIR;无标记诊断;脂肪栓塞</t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>Frontiers in Medicine</t>
+          <t>Applied Spectroscopy</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t>10.3389/fmed.2022.1083474</t>
+          <t>10.1177/00037028211061430</t>
         </is>
       </c>
     </row>
@@ -3271,574 +3153,572 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
+          <t>Evaluation of Inspection Efficiency of Diatom Artificial Intelligence Search System Based on Scanning Electron Microscope</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>基于扫描电镜的硅藻人工智能搜索系统检验效率评估</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>评估基于扫描电镜（SEM）的硅藻人工智能搜索系统的检验效率。</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>硅藻与溺死诊断
+人工智能&amp;扫描电镜</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>AI/机器学习; 形态学</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>死亡方式</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>2022-02</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>复旦大学基础医学院法医学系/司法鉴定科学研究院</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>中文核心（JCR未收录）</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>可牵引「AI辅助硅藻检验的技术演进综述（SEM+AI角度）」：以『光学显微镜人工镜检→SEM高分辨率成像→AI自动搜索/识别』为发展主线，系统比较不同显微成像模态与AI目标检测结合在硅藻检验中的效率与准确率优势，讨论SEM扫描时间、图像数据存储与标注成本对通量的制约，提出『成像模态+AI』的硅藻检验标准化框架；与光学显微镜+AI方案（如DiatomNet）对比可构成更完整的『AI硅藻检验方法学』综述。</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>摘要未报告具体效率提升幅度、样本量与准确率数据，结论缺乏量化支撑；SEM设备昂贵、维护成本高，基层法医实验室难以普及；AI系统依赖训练标注数据集，硅藻种类覆盖度与类别不平衡问题未说明；效率评估可能局限于特定实验室流程，未见盲法设计与多中心验证。</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>Evaluation of inspection efficiency of diatom AI search system based on SEM.</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>系统效率评估，SEM图像+AI搜索系统，对比人工搜索效率</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>AI搜索系统相比人工搜索显著提高了硅藻检验效率，具有实际应用价值。</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>系统评估AI硅藻搜索系统在SEM图像中的检验效率</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>硅藻;AI;SEM;法医学杂志</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>法医学杂志 (Journal of Forensic Medicine)</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>10.12116/j.issn.1004-5619.2021.410719</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Research Progress of Automatic Diatom Test by Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>人工智能自动硅藻检验的研究进展（综述）</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>综述人工智能自动硅藻检验的研究进展。</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>自动硅藻检验</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>AI/机器学习</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>死亡方式</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>2022-02</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>复旦大学基础医学院法医学系/司法鉴定科学研究院</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>中文核心（JCR未收录）</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>本篇综述可进一步牵引更系统化的综述：如『深度学习在溺死诊断硅藻检验中的应用：方法、数据集与挑战』，将DiatomNet、SEM-AI搜索系统等具体工作纳入统一技术框架，按『图像采集（光学显微镜/SEM）→目标检测→分类与计数→诊断报告』梳理pipeline各环节的模型选择与性能指标，并针对标注数据不足、类别不平衡、模型泛化与法医证据标准衔接提出研究路线图；亦可扩展为『人工智能在溺死鉴定全流程中的应用』综述。</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>综述明确指出标注数据不足、模型泛化能力差等核心挑战；所引研究多为单中心、小规模数据集，缺乏跨实验室、跨水域的验证证据；未建立与传统人工硅藻检验流程的标准化定量比较框架；未给出推荐的数据集规模、标注规范与模型选择指南，结论停留在方向性展望层面。</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>Review of research progress on automatic diatom test using artificial intelligence.</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>文献综述，系统回顾AI（深度学习/机器学习）在硅藻自动识别中的应用进展</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t>AI技术在硅藻自动识别中展现出巨大潜力，但面临标注数据不足、模型泛化能力等挑战。</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t>系统梳理AI在硅藻检验中应用的综述</t>
+        </is>
+      </c>
+      <c r="Q31" s="3" t="inlineStr">
+        <is>
+          <t>硅藻;AI;综述;法医学杂志</t>
+        </is>
+      </c>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t>法医学杂志 (Journal of Forensic Medicine)</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr">
+        <is>
+          <t>10.12116/j.issn.1004-5619.2021.410404</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Comparison among Four Deep Learning Image Classification Algorithms in AI-based Diatom Test</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>AI硅藻检验中四种深度学习图像分类算法的比较</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>比较四种深度学习图像分类算法在AI硅藻检验中的性能。</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>硅藻与溺死检验
+AI深度学习</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>AI/机器学习</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>死亡方式</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>2022-02</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>复旦大学基础医学院法医学系/司法鉴定科学研究院</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>中文核心（JCR未收录）</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>深度学习图像分类算法在法医硅藻检验中的应用与算法选型综述：可从CNN/迁移学习等四类算法架构的性能对比切入，梳理硅藻图像数据集构建（消化制片、全切片扫描、标注规范）、检测/分类/分割任务划分及评估指标，进而延伸至'AI辅助溺死诊断全流程'（样本处理→自动识别→定量→结论）的技术框架与标准化问题。</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>四种算法性能比较的结论高度依赖训练数据集的规模、硅藻类别构成与图像来源，摘要未报告样本量及跨中心、跨显微镜设备的独立验证，泛化性存疑；且比较范围限于四类经典算法，未涉及Transformer等最新架构；分类性能还受硅藻类别不均衡与稀有属种样本不足影响，距实际案例应用仍有距离。</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>Comparison of four deep learning image classification algorithms for AI-based diatom test.</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>算法比较研究，硅藻图像数据集，四种深度学习模型对比(CNN/ResNet等)</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>比较了不同深度学习算法在硅藻图像分类中的性能差异，为算法选择提供依据。</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>系统比较多种深度学习算法在硅藻分类中的表现</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>硅藻;深度学习;法医学杂志;AI</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>法医学杂志 (Journal of Forensic Medicine)</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>10.12116/j.issn.1004-5619.2021.411001</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Bibliometrics Analysis in English and Chinese Literature on Drowning in Forensic Medicine from 1991 to 2020</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>1991-2020年法医学溺死中英文文献计量学分析</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>对1991-2020年法医学溺死中英文文献进行文献计量学分析。</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>溺死
+文献计量学分析</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>综述</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>死亡方式</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>2022-02</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>复旦大学基础医学院法医学系/司法鉴定科学研究院</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>中文核心（JCR未收录）</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>法医学溺死研究30年发展脉络综述（1991-2020）：以文献计量学揭示的主题聚类（硅藻检验、分子标志物、影像学、AI）为主线，结合国家/机构合作网络与高频关键词演进，梳理从传统形态学检验到分子与人工智能方法的范式转移，可作为该领域选题定位和研究空白识别的宏观依据。</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>文献计量学结果受数据库收录范围与检索策略制约，中英文数据库覆盖不均衡易造成文献漏检；主题聚类与关键词划分存在主观性，且无法反映未发表文献与灰色文献；分析停留在描述性统计层面，难以评估单篇研究质量与证据等级。</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>Bibliometric analysis of English and Chinese literature on drowning in forensic medicine from 1991 to 2020.</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>文献计量学分析，WoS/CNKI数据库，1991-2020年溺死相关文献</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>系统梳理了30年间法医学溺死研究的发展趋势、热点主题和核心作者/机构分布。</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>首次对法医学溺死文献进行30年跨度的中英文文献计量分析</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="inlineStr">
+        <is>
+          <t>溺死;文献计量学;法医学杂志</t>
+        </is>
+      </c>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t>法医学杂志 (Journal of Forensic Medicine)</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr">
+        <is>
+          <t>10.12116/j.issn.1004-5619.2021.411209</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Combining with lab-on-chip technology and multi-organ fusion strategy to estimate post-mortem interval of rat</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>芯片实验室技术与多器官融合策略联合推断大鼠死后间隔时间</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>目的：探讨芯片实验室技术与多器官融合策略联合用于推断大鼠死后间隔时间(PMI)的可行性。方法：建立大鼠死亡模型，在不同PMI时间点收集多器官（肝脏、脾脏、肾脏、肺脏）样本，使用芯片实验室技术检测代谢物变化，采用多器官数据融合策略进行PMI推断。结果：与单一器官分析相比，多器官融合策略的PMI推断准确率更高，芯片实验室技术提高了检测效率。结论：芯片实验室技术与多器官融合策略联合应用是推断PMI的一种有前景的方法。</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>死亡时间推断</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>分子生物学</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>PMI</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>2022-01</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>复旦大学基础医学院法医学系</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>多器官/多组学数据融合策略在死后间隔时间推断中的应用综述：可围绕'单一标志物→多器官多组学融合'的方法学演进，梳理微流控芯片（lab-on-chip）实现微量样本快速高通量检测的技术原理，比较内部验证（准确率0.962）与外部验证（0.89）的差距来源，并讨论数据融合算法（特征级/决策级）选择及向法医实践转化的路径。</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>研究基于大鼠死亡模型，种属间代谢降解速率与器官构成差异限制其向人体的直接外推；外部验证准确率（0.89）低于内部验证（0.962），提示模型泛化性与过拟合风险；摘要未报告样本量与温度、死因等混杂因素的控制情况，检测的多肽片段亦受死后降解动态影响。</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>The estimation of post-mortem interval (PMI) is one of the most important problems in forensic pathology. In this study, lab-on-chip is used to analyze polypeptide fragments of lung, liver, kidney, and skeletal muscle of rats at defined time points after death. Multi-organ fusion strategy dramatically improves the performance of PMI estimation, with internal and external accuracy of 0.962 and 0.893.</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>建立大鼠死亡模型，在多个PMI时间点分别采集肝、脾、肾、肺组织样本，采用芯片实验室(lab-on-chip)微流控技术检测代谢物变化，将多器官代谢数据融合分析与单一器官结果进行比较。</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>多器官数据融合策略在PMI推断方面优于单一器官分析，芯片实验室技术提高了检测效率，该方法将微流控检测与多维度生物学数据整合相结合，具有从动物实验向法医实践转化的潜力。</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>首次提出多器官融合策略用于PMI推断，将芯片实验室微流控技术引入法医死亡时间研究，实现了微量样本快速高通量检测。</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>死亡时间;多器官融合;芯片实验室</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>Frontiers in Medicine</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>10.3389/fmed.2022.1083474</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
           <t>Use of deep learning in forensic sex estimation of virtual pelvic models from the Han population</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>深度学习在汉族人群虚拟骨盆模型法医性别推断中的应用</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>目的：评估深度学习在基于汉族人群虚拟骨盆模型的法医性别推断中的性能。方法：收集1200例汉族成人骨盆CT数据，重建虚拟骨盆三维模型，训练深度学习模型进行性别推断，并将性能与传统形态学方法进行比较。结果：深度学习模型的性别推断准确率超过93%，显著高于传统形态学方法。结论：基于虚拟骨盆模型的深度学习方法在法医汉族人群性别推断中具有极高准确性。</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E35" s="3" t="inlineStr">
         <is>
           <t>法医人类学
 深度学习
 性别推断</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F35" s="3" t="inlineStr">
         <is>
           <t>AI/机器学习;影像</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G35" s="3" t="inlineStr">
         <is>
           <t>身份</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H35" s="3" t="inlineStr">
         <is>
           <t>2022-01</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="I35" s="3" t="inlineStr">
         <is>
           <t>复旦大学基础医学院法医学系</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="J35" s="3" t="inlineStr">
         <is>
           <t>2.1</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="K35" s="3" t="inlineStr">
         <is>
           <t>深度学习在法医人类学影像学身份识别中的应用综述：可从骨盆、颅骨、长骨等部位的CT虚拟三维模型出发，比较CNN自动性别/年龄推断与传统形态计量学的性能差距，围绕人群特异性（汉族vs其他族群）模型的构建与跨人群泛化、临床影像数据偏倚与可解释性（可迁移到类激活图、注意力机制）等角度组织框架。</t>
         </is>
       </c>
-      <c r="L30" s="2" t="inlineStr">
+      <c r="L35" s="3" t="inlineStr">
         <is>
           <t>模型仅在汉族成人样本（1200例CT）上训练验证，跨族群、跨年龄段及骨质疏松等骨性退化个体中的外推性未证实；骨盆性别二态性在儿童与老年个体中减弱，可能高估总体准确率；CT数据多来自临床检查，存在选择性偏倚；深度学习黑箱缺乏形态学特征层面的可解释性，且对照的传统方法评估者间差异未报告。</t>
         </is>
       </c>
-      <c r="M30" s="2" t="inlineStr">
+      <c r="M35" s="3" t="inlineStr">
         <is>
           <t>The excellent sex estimation performance obtained by the CNN models indicates that this method is valuable to proceed with in prospective forensic trials, and demonstrates the potential of AI techniques based on the radiological dataset in sex estimation of virtual pelvic models.</t>
         </is>
       </c>
-      <c r="N30" s="2" t="inlineStr">
+      <c r="N35" s="3" t="inlineStr">
         <is>
           <t>收集1200例汉族成人骨盆CT数据，进行图像分割和三维虚拟重建生成标准化虚拟骨盆模型，训练深度学习模型(3D-CNN等)进行性别二分类，与传统形态学方法(Phenice方法等)进行准确率比较。</t>
         </is>
       </c>
-      <c r="O30" s="2" t="inlineStr">
+      <c r="O35" s="3" t="inlineStr">
         <is>
           <t>深度学习模型基于虚拟骨盆模型进行性别推断准确率超93%，显著优于传统形态学方法，实现了自动化、标准化的高准确率性别推断。</t>
         </is>
       </c>
-      <c r="P30" s="2" t="inlineStr">
+      <c r="P35" s="3" t="inlineStr">
         <is>
           <t>首次将深度学习应用于汉族人群虚拟骨盆模型的法医性别推断，1200例大样本训练保证泛化能力，采用虚拟骨盆三维模型保留了骨盆立体形态性差信息。</t>
         </is>
       </c>
-      <c r="Q30" s="2" t="inlineStr">
+      <c r="Q35" s="3" t="inlineStr">
         <is>
           <t>深度学习;骨盆;法医人类学;性别推断</t>
         </is>
       </c>
-      <c r="R30" s="2" t="inlineStr">
+      <c r="R35" s="3" t="inlineStr">
         <is>
           <t>Forensic Sciences Research</t>
         </is>
       </c>
-      <c r="S30" s="2" t="inlineStr">
+      <c r="S35" s="3" t="inlineStr">
         <is>
           <t>10.1080/20961790.2021.2024369</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>Preliminary study on the mechanisms of ankle injuries under falling and impact conditions based on the THUMS model</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>基于THUMS模型的坠落与撞击条件下踝关节损伤机制的初步研究</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>目的：利用THUMS(Total Human Model for Safety)有限元模型探讨坠落与撞击条件下踝关节损伤的机制。方法：使用THUMS人体有限元模型模拟不同坠落高度和撞击条件下的踝关节受力情况，分析应力分布、损伤模式及生物力学机制。结果：坠落与撞击条件下踝关节呈现不同的损伤模式，应力分布与损伤机制表现出工况特异性特征。结论：THUMS有限元模型可有效模拟不同条件下踝关节损伤机制，对法医学损伤机制分析具有重要参考价值。</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>法医生物力学
-事故损伤机制</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>生物力学</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>损伤机制</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>2022-01</t>
-        </is>
-      </c>
-      <c r="I31" s="3" t="inlineStr">
-        <is>
-          <t>复旦大学基础医学院法医学系</t>
-        </is>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t>有限元人体模型在法医损伤生物力学重建中的应用综述：可围绕THUMS等全身有限元模型的构建与验证（材料参数来源、尸体实验对照），梳理坠落伤与撞击伤鉴别的'工况-应力-损伤'关联分析框架，比较不同致伤条件（坠落高度、撞击速度、踝关节姿态）下的应力分布与骨折模式差异，并延伸至颅脑、胸腹等其他部位损伤重建。</t>
-        </is>
-      </c>
-      <c r="L31" s="3" t="inlineStr">
-        <is>
-          <t>研究属初步探索（preliminary），模型材料参数与边界条件多取自文献简化设定，未纳入个体差异（年龄、骨密度）及韧带等软组织精细材料模型；模拟工况有限，难以覆盖真实坠落中多阶段、多次碰撞的复杂性；缺乏尸体实验或真实案例损伤的定量验证，结论外推需谨慎。</t>
-        </is>
-      </c>
-      <c r="M31" s="3" t="inlineStr">
-        <is>
-          <t>The results showed that falling causes a specific compression fracture of the distal tibia, while fractures of the tibia and fibula diaphysis and ligament injuries caused by falling from a lower height or inversion, planter flexion or dorsiflexion at a large angle are not distinguishable from the similar injury patterns caused by impact on the middle and upper segments of the leg.</t>
-        </is>
-      </c>
-      <c r="N31" s="3" t="inlineStr">
-        <is>
-          <t>采用THUMS高精度人体有限元模型，设置不同坠落高度和不同撞击条件工况，进行有限元仿真计算获取踝关节各解剖结构（骨骼、韧带、软组织）应力分布和应变数据，分析比较各工况下的骨折类型、韧带损伤等损伤模式差异。</t>
-        </is>
-      </c>
-      <c r="O31" s="3" t="inlineStr">
-        <is>
-          <t>THUMS模型可有效模拟坠落与撞击两种致伤条件下踝关节损伤过程，两种工况导致不同的应力分布特征和损伤模式，为法医学区分坠落伤与撞击伤提供了生物力学理论依据。</t>
-        </is>
-      </c>
-      <c r="P31" s="3" t="inlineStr">
-        <is>
-          <t>首次将THUMS高精度人体有限元模型应用于法医学踝关节损伤机制研究，系统比较了坠落与撞击条件下的不同生物力学机制，建立了'工况-应力-损伤'关联分析框架。</t>
-        </is>
-      </c>
-      <c r="Q31" s="3" t="inlineStr">
-        <is>
-          <t>生物力学;踝关节损伤;THUMS</t>
-        </is>
-      </c>
-      <c r="R31" s="3" t="inlineStr">
-        <is>
-          <t>Forensic Sciences Research</t>
-        </is>
-      </c>
-      <c r="S31" s="3" t="inlineStr">
-        <is>
-          <t>10.1080/20961790.2021.1875582</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>An efficient method for building a database of diatom populations for drowning site inference using a deep learning algorithm</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>使用深度学习算法建立硅藻种群数据库用于溺死地点推断的高效方法</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>使用深度学习算法建立硅藻种群数据库用于溺死地点推断的高效方法。</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>深度学习
-硅藻与溺死</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>AI/机器学习</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>死亡方式</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>2021-05</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>复旦大学基础医学院法医学系/司法鉴定科学研究院/葡萄牙科英布拉大学</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>2.6</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>基于硅藻群落的溺死地点推断综述（法医湖沼学）：可从硅藻种群组成与群落生态学分析入手，梳理溺死地点推断的统计学框架（相似度比较、判别分析），重点讨论深度学习在硅藻物种识别与种群数据库高效构建中的作用，以及数据库地域覆盖、水域类型、季节动态对推断可靠性的影响，提出标准化数据库建设方向。</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>数据库的时空覆盖范围直接决定推断外推性，若训练样本集中于特定水域则难以推广；深度学习识别受训练集代表性制约，稀有硅藻属种易漏检误判；且溺死地点推断还受水流搬运、尸体漂移、季节演替等生态因素干扰，单纯依赖数据库方法难以解决，摘要未报告数据库规模与验证策略。</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>An efficient method for building a database of diatom populations for drowning site inference using a deep learning algorithm.</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>实验研究+算法开发，多水域硅藻样本，深度学习算法+数据库构建</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>深度学习算法可高效建立硅藻种群数据库，为溺死地点推断提供数据基础。</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>提出基于深度学习的硅藻数据库高效构建方法</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>硅藻;溺死地点;深度学习;数据库</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>International Journal of Legal Medicine</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>10.1007/s00414-020-02497-5</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>Pulmonary PMCT angiography by right ventricle cardiac puncture: a novel, promising approach for investigating pulmonary thromboembolism</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>右心室心脏穿刺肺PMCT血管造影：研究肺血栓栓塞的新型方法</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>目的：探索经右心室心脏穿刺行肺死后CT血管造影(PMCT)用于研究肺血栓栓塞症(PTE)的可行性。方法：对尸体实施右心室心脏穿刺并注入造影剂，行肺PMCT血管造影检查，评估影像学表现，并与传统尸体解剖结果进行对照比较。结果：经右心室心脏穿刺的肺PMCT血管造影成功显示了肺血管系统形态结构，阳性病例中PTE被清晰可视化。结论：经右心室心脏穿刺的肺PMCT血管造影是研究PTE的一种新型且有前景的方法。</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>死后影像学
-肺血栓栓塞</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>影像</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>死因</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>2021-05</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t>复旦大学基础医学院法医学系</t>
-        </is>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>2.6</t>
-        </is>
-      </c>
-      <c r="K33" s="3" t="inlineStr">
-        <is>
-          <t>死后CT血管造影（PMCTA）在法医学中的应用综述：可与MSCT血管造影综述（num 36）呼应，围绕造影剂注射途径（经股动静脉、心脏穿刺、心肺复苏途径）的技术比较，聚焦肺血栓栓塞等血管性死因的死后影像诊断价值、与传统尸检的符合率及Virtopsy理念下'穿刺-造影-PMCT-诊断'标准化流程的建立。</t>
-        </is>
-      </c>
-      <c r="L33" s="3" t="inlineStr">
-        <is>
-          <t>研究多为小样本或个案系列，统计效能有限；心脏穿刺入路可能引入气体、造影剂外渗等人工伪影，干扰判读；尸体腐败程度、死后凝血状态影响造影剂灌注效果；与传统解剖对照的病例数有限，且操作依赖术者经验，流程缺乏多中心标准化验证。</t>
-        </is>
-      </c>
-      <c r="M33" s="3" t="inlineStr">
-        <is>
-          <t>Pulmonary PMCTA approach is a simple, convenient, and effective method for the visualization of the pulmonary artery, which can be used as an effective auxiliary tool to identify PTE in forensic practice and will also provide technical support to further investigate PTE imaging characteristics.</t>
-        </is>
-      </c>
-      <c r="N33" s="3" t="inlineStr">
-        <is>
-          <t>选择右心室心脏穿刺作为造影剂注入途径（经胸壁直接穿刺右心室），注入水溶性碘造影剂后行全身/胸部PMCT扫描，进行MIP/VR/MPR后处理重建，评估肺动脉显影及充盈缺损征象，与传统尸检大体和组织病理学结果对照验证。</t>
-        </is>
-      </c>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
-          <t>经右心室心脏穿刺行肺PMCT血管造影操作简便、显影效果良好，可清晰显示PTE栓塞部位和范围，具有无创、可三维可视化、可永久存档的优势，为法医PTE死后诊断提供了创新性技术方案。</t>
-        </is>
-      </c>
-      <c r="P33" s="3" t="inlineStr">
-        <is>
-          <t>首次提出经右心室心脏穿刺作为死后肺血管造影的造影剂注入途径，避免了传统开胸对血管完整性的破坏，入路更直接操作更简便，建立了完整的'穿刺-造影-PMCT-诊断'技术流程。</t>
-        </is>
-      </c>
-      <c r="Q33" s="3" t="inlineStr">
-        <is>
-          <t>PMCTA;肺动脉血栓;右心室穿刺</t>
-        </is>
-      </c>
-      <c r="R33" s="3" t="inlineStr">
-        <is>
-          <t>International Journal of Legal Medicine</t>
-        </is>
-      </c>
-      <c r="S33" s="3" t="inlineStr">
-        <is>
-          <t>10.1007/s00414-020-02476-w</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>Species identification of semen stains by ATR-FTIR spectroscopy</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>ATR-FTIR光谱进行精斑物种鉴定</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>无需精子细胞即可实现物种鉴定，证明光谱方法在无精子症案例精斑检测中的能力，为实际法医案例中精斑物种鉴定提供强大实用工具。</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>光谱
-精斑鉴定</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>光谱</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>身份</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>2021-01</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>复旦大学基础医学院法医学系/西安交通大学法医学院</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>2.6</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>振动光谱（ATR-FTIR/拉曼）在法医体液鉴定中的应用综述：可围绕精液、血液、唾液等体液的无损快速鉴定展开，重点讨论'无需精子细胞即可完成物种鉴定'对无精子症/输精管结扎案例的独特价值，梳理光谱-化学计量学（或机器学习）分类流程、载体基质干扰处理及与DNA检验的互补关系，并可延伸至性犯罪案件物证检验场景。</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>光谱信号易受衣物等载体基质、环境污染与样本老化降解干扰，摘要未报告样本量、物种覆盖范围及常见污染物的耐受性验证；当前能力限于物种鉴定，无法像DNA那样进行个体识别；跨实验室、跨仪器（批次效应）的稳定性与数据库共享问题尚待解决。</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>Species identification could be achieved without sperm cells which proved ability of spectroscopic methods detecting semen samples from azoospermia cases, providing a powerful and practical tool for species identification of semen stains in real forensic casework.</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>实验研究，不同物种精斑样本，ATR-FTIR光谱+化学计量学</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>ATR-FTIR光谱可在无精子的情况下进行精斑物种鉴定，解决了无精子症案例的法医学难题。</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>首次证明ATR-FTIR可在无精子细胞情况下进行精斑物种鉴定</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>FTIR;精斑;物种鉴定</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>International Journal of Legal Medicine</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>10.1007/s00414-020-02367-0</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>The influence of sample geometry and size on porcine aortic material properties from uniaxial tensile tests using custom-designed tissue cutters, clamps and molds</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>样本几何形状和尺寸对猪主动脉单轴拉伸材料性能的影响</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>目的：研究使用定制组织切割器进行单轴拉伸试验时，样本几何形状和尺寸对猪主动脉材料性能的影响。方法：使用定制设计的组织切割器制备不同几何形状和尺寸的猪主动脉样本，进行单轴拉伸试验并比较其材料性能。结果：样本几何形状和尺寸对测得的材料性能有显著影响，定制组织切割器提高了样本制备的一致性。结论：应标准化样本几何形状和尺寸以获得准确的材料性能测量结果，定制组织切割器是生物力学研究的有用工具。</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>法医生物力学
-主动脉力学</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>生物力学</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t>损伤机制</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>2021-01</t>
-        </is>
-      </c>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t>复旦大学基础医学院法医学系</t>
-        </is>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>2.8</t>
-        </is>
-      </c>
-      <c r="K35" s="3" t="inlineStr">
-        <is>
-          <t>软组织生物力学测试标准化综述：可围绕样本制备（几何形状、尺寸、切割工具）与测试协议（预载荷、应变率、夹持方式）对材料参数测量结果的影响展开，结合主动脉单轴拉伸的尺寸效应（符合Weibull理论）讨论狗骨形样本宽度选择依据，为血管破裂等法医生物力学分析提供可靠的基准数据获取规范，并延伸至各组织本构模型参数标定。</t>
-        </is>
-      </c>
-      <c r="L35" s="3" t="inlineStr">
-        <is>
-          <t>猪主动脉与人体主动脉在壁厚、弹性蛋白/胶原比例及力学响应上存在种属差异，外推至人体需谨慎；离体单轴拉伸忽略在体预张力与平滑肌活性，且单轴加载不能完全代表生理状态下的多轴应力；摘要未涉及样本保存条件（温度、时间）与个体年龄差异对结果的影响。</t>
-        </is>
-      </c>
-      <c r="M35" s="3" t="inlineStr">
-        <is>
-          <t>The results showed that the size effect of the aorta conformed to Weibull theory, and dog-bone-shaped specimens with a width of 4 mm were the optimal choice for aortic uniaxial tensile testing performed until rupture.</t>
-        </is>
-      </c>
-      <c r="N35" s="3" t="inlineStr">
-        <is>
-          <t>使用定制设计的组织切割器制备不同几何形状和尺寸的猪主动脉样本，进行单轴拉伸试验，对比分析各组样本的材料性能参数（弹性模量、极限应力等）。</t>
-        </is>
-      </c>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t>样本几何形状和尺寸对主动脉材料性能测量有显著影响应进行标准化，定制组织切割器能提高样本制备一致性和测量准确性，是生物力学研究的有用工具。</t>
-        </is>
-      </c>
-      <c r="P35" s="3" t="inlineStr">
-        <is>
-          <t>自主设计定制组织切割器用于标准化生物力学样本制备，系统研究了样本几何形状和尺寸对猪主动脉单轴拉伸材料性能的影响规律。</t>
-        </is>
-      </c>
-      <c r="Q35" s="3" t="inlineStr">
-        <is>
-          <t>生物力学;拉伸测试;主动脉</t>
-        </is>
-      </c>
-      <c r="R35" s="3" t="inlineStr">
-        <is>
-          <t>PLoS ONE</t>
-        </is>
-      </c>
-      <c r="S35" s="3" t="inlineStr">
-        <is>
-          <t>10.1371/journal.pone.0244390</t>
         </is>
       </c>
     </row>
@@ -3848,38 +3728,38 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Postmortem chest computed tomography for the diagnosis of drowning: a feasibility study</t>
+          <t>Preliminary study on the mechanisms of ankle injuries under falling and impact conditions based on the THUMS model</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>死后胸部CT用于溺死诊断的可行性研究</t>
+          <t>基于THUMS模型的坠落与撞击条件下踝关节损伤机制的初步研究</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>目的：评估死后胸部CT用于溺死诊断的可行性。方法：回顾性分析溺死案例和非溺死对照的死后胸部CT表现，评估气道内液体、肺部改变和鼻窦积液等CT特征。结果：识别出与溺死相关的特异性CT表现，多个CT特征的联合应用提高了诊断准确性。结论：死后胸部CT是法医学实践中溺死诊断的可行辅助方法。</t>
+          <t>目的：利用THUMS(Total Human Model for Safety)有限元模型探讨坠落与撞击条件下踝关节损伤的机制。方法：使用THUMS人体有限元模型模拟不同坠落高度和撞击条件下的踝关节受力情况，分析应力分布、损伤模式及生物力学机制。结果：坠落与撞击条件下踝关节呈现不同的损伤模式，应力分布与损伤机制表现出工况特异性特征。结论：THUMS有限元模型可有效模拟不同条件下踝关节损伤机制，对法医学损伤机制分析具有重要参考价值。</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>法医影像学
-溺死诊断</t>
+          <t>法医生物力学
+事故损伤机制</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>影像</t>
+          <t>生物力学</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>死亡方式</t>
+          <t>损伤机制</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2021-01</t>
+          <t>2022-01</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -3894,37 +3774,37 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>死后影像学在溺死诊断中的应用综述：可从胸部PMCT特征（气道内液体、肺水肿、鼻窦积液等）的诊断价值与特异性入手，梳理溺死与冠心病等常见死后改变的影像鉴别要点（摘要即以CAD为对照），讨论多特征联合诊断策略、影像与硅藻检验/尸检的组织病理证据互补模式，以及影像组学与AI辅助判读在溺死诊断中的前景。</t>
+          <t>有限元人体模型在法医损伤生物力学重建中的应用综述：可围绕THUMS等全身有限元模型的构建与验证（材料参数来源、尸体实验对照），梳理坠落伤与撞击伤鉴别的'工况-应力-损伤'关联分析框架，比较不同致伤条件（坠落高度、撞击速度、踝关节姿态）下的应力分布与骨折模式差异，并延伸至颅脑、胸腹等其他部位损伤重建。</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>研究为回顾性设计，病例选择与对照组设置可能存在偏倚；气道液体、肺水肿等CT表现在死后可因尸体搬运、复苏操作及腐败进程发生改变，与CAD鉴别时特异性有限；摘要未报告样本量与多中心验证情况，且未与硅藻检验等既有金标准方法进行系统比较。</t>
+          <t>研究属初步探索（preliminary），模型材料参数与边界条件多取自文献简化设定，未纳入个体差异（年龄、骨密度）及韧带等软组织精细材料模型；模拟工况有限，难以覆盖真实坠落中多阶段、多次碰撞的复杂性；缺乏尸体实验或真实案例损伤的定量验证，结论外推需谨慎。</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>The aim of this study was to explore the forensic value of thoracic postmortem computed tomography (PMCT) using routine images and three-dimensional image reconstructions to distinguish between drowning and CAD.</t>
+          <t>The results showed that falling causes a specific compression fracture of the distal tibia, while fractures of the tibia and fibula diaphysis and ligament injuries caused by falling from a lower height or inversion, planter flexion or dorsiflexion at a large angle are not distinguishable from the similar injury patterns caused by impact on the middle and upper segments of the leg.</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>回顾性收集溺死案例和非溺死对照的死后胸部CT影像，评估气道内液体、肺部磨玻璃/实变改变、鼻窦积液等CT特征，比较两组CT表现差异并分析多特征联合诊断效能。</t>
+          <t>采用THUMS高精度人体有限元模型，设置不同坠落高度和不同撞击条件工况，进行有限元仿真计算获取踝关节各解剖结构（骨骼、韧带、软组织）应力分布和应变数据，分析比较各工况下的骨折类型、韧带损伤等损伤模式差异。</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>死后胸部CT是法医学溺死诊断的可行辅助方法，多项CT特征联合应用可提高诊断准确性。</t>
+          <t>THUMS模型可有效模拟坠落与撞击两种致伤条件下踝关节损伤过程，两种工况导致不同的应力分布特征和损伤模式，为法医学区分坠落伤与撞击伤提供了生物力学理论依据。</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>首次系统探讨死后胸部CT在溺死诊断中的可行性，提出多项CT特征联合诊断策略。</t>
+          <t>首次将THUMS高精度人体有限元模型应用于法医学踝关节损伤机制研究，系统比较了坠落与撞击条件下的不同生物力学机制，建立了'工况-应力-损伤'关联分析框架。</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>PMCT;溺死诊断;胸部CT</t>
+          <t>生物力学;踝关节损伤;THUMS</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
@@ -3934,7 +3814,7 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>10.1080/20961790.2018.1557386</t>
+          <t>10.1080/20961790.2021.1875582</t>
         </is>
       </c>
     </row>
@@ -3944,92 +3824,93 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Research Status of Postmortem MSCT Angiography in Forensic Science</t>
+          <t>An efficient method for building a database of diatom populations for drowning site inference using a deep learning algorithm</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>法医学死后MSCT血管造影研究现状</t>
+          <t>使用深度学习算法建立硅藻种群数据库用于溺死地点推断的高效方法</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>死后多层螺旋CT(MSCT)血管造影是法医学影像领域的重要进展。本文综述了法医学死后MSCT血管造影的研究现状，包括其技术原理、操作方法以及在不同法医学场景中的应用，讨论了不同血管造影技术的优缺点，并提出了未来的发展方向。死后MSCT血管造影在心血管疾病诊断、创伤评估及其他法医学应用中展现了巨大潜力。</t>
+          <t>使用深度学习算法建立硅藻种群数据库用于溺死地点推断的高效方法。</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>法医影像学</t>
+          <t>深度学习
+硅藻与溺死</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>影像</t>
+          <t>AI/机器学习</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>死因</t>
+          <t>死亡方式</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>2020-12</t>
+          <t>2021-05</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>复旦大学基础医学院法医学系</t>
+          <t>复旦大学基础医学院法医学系/司法鉴定科学研究院/葡萄牙科英布拉大学</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>中文核心（JCR未收录）</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>虚拟解剖与死后影像技术体系综述：该文本身即PMCTA综述，可进一步牵引'死后CT血管造影技术路线全景'——系统比较全身血管造影、心肺复苏途径、靶向造影、心脏穿刺等入路的技术原理与优劣，梳理心血管死因诊断、创伤评估等应用场景，并围绕操作流程标准化、多中心验证及造影后影像结合AI定量分析等未来方向展开。</t>
+          <t>基于硅藻群落的溺死地点推断综述（法医湖沼学）：可从硅藻种群组成与群落生态学分析入手，梳理溺死地点推断的统计学框架（相似度比较、判别分析），重点讨论深度学习在硅藻物种识别与种群数据库高效构建中的作用，以及数据库地域覆盖、水域类型、季节动态对推断可靠性的影响，提出标准化数据库建设方向。</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>作为综述，其结论受已有文献异质性限制：各研究间造影剂配方、灌注参数与判读标准不统一，缺乏大型前瞻性多中心对照数据；PMCTA对微小血管病变和功能学信息（缺血）无法显示，与传统尸检的符合率报道不一，证据等级有待提升。</t>
+          <t>数据库的时空覆盖范围直接决定推断外推性，若训练样本集中于特定水域则难以推广；深度学习识别受训练集代表性制约，稀有硅藻属种易漏检误判；且溺死地点推断还受水流搬运、尸体漂移、季节演替等生态因素干扰，单纯依赖数据库方法难以解决，摘要未报告数据库规模与验证策略。</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>Virtual autopsy is a new technique for investigating the morphological changes of cadaveric tissues and organs by medical imaging technology. This article summarizes several common cadaveric MSCT angiography methods, such as systemic angiography, angiography through cardiopulmonary resuscitation, targeted angiography, and angiography by cardiac puncture.</t>
+          <t>An efficient method for building a database of diatom populations for drowning site inference using a deep learning algorithm.</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>文献综述：系统梳理死后MSCT血管造影的技术原理（造影剂类型、注射途径、扫描参数）、操作方法和在不同法医场景（心血管疾病、创伤、器官病变）中的应用，比较分析不同造影技术的优缺点。</t>
+          <t>实验研究+算法开发，多水域硅藻样本，深度学习算法+数据库构建</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>死后MSCT血管造影在法医学心血管疾病诊断和创伤评估等方面具有巨大潜力，未来需在标准化操作流程和多中心验证方面进一步发展完善。</t>
+          <t>深度学习算法可高效建立硅藻种群数据库，为溺死地点推断提供数据基础。</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>系统综述了死后MSCT血管造影在法医学中的研究现状和技术路线，总结比较了不同造影技术的优劣并提出了标准化发展方向。</t>
+          <t>提出基于深度学习的硅藻数据库高效构建方法</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t>法医学杂志;血管造影;虚拟解剖;MSCT</t>
+          <t>硅藻;溺死地点;深度学习;数据库</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t>Fa yi xue za zhi</t>
+          <t>International Journal of Legal Medicine</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t>10.12116/j.issn.1004-5619.2020.06.012</t>
+          <t>10.1007/s00414-020-02497-5</t>
         </is>
       </c>
     </row>
@@ -4039,37 +3920,38 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Finite element analysis to determine the cause of ring fractures in a motorcyclist's head</t>
+          <t>Pulmonary PMCT angiography by right ventricle cardiac puncture: a novel, promising approach for investigating pulmonary thromboembolism</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>有限元分析确定摩托车骑手头部环形骨折的成因</t>
+          <t>右心室心脏穿刺肺PMCT血管造影：研究肺血栓栓塞的新型方法</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>目的：使用有限元分析方法确定摩托车骑手头部环形骨折的成因。方法：基于真实摩托车事故受害者的CT数据构建人体头部有限元模型，模拟不同撞击场景以再现环形骨折模式，分析损伤机制。结果：通过模拟特定撞击场景成功再现了环形骨折模式，生物力学分析揭示了损伤机制。结论：有限元分析可以有效确定摩托车事故中环形骨折的成因，为法医学调查提供科学依据。</t>
+          <t>目的：探索经右心室心脏穿刺行肺死后CT血管造影(PMCT)用于研究肺血栓栓塞症(PTE)的可行性。方法：对尸体实施右心室心脏穿刺并注入造影剂，行肺PMCT血管造影检查，评估影像学表现，并与传统尸体解剖结果进行对照比较。结果：经右心室心脏穿刺的肺PMCT血管造影成功显示了肺血管系统形态结构，阳性病例中PTE被清晰可视化。结论：经右心室心脏穿刺的肺PMCT血管造影是研究PTE的一种新型且有前景的方法。</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>事故重建</t>
+          <t>死后影像学
+肺血栓栓塞</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>生物力学</t>
+          <t>影像</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>损伤机制</t>
+          <t>死因</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2020-07</t>
+          <t>2021-05</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -4079,52 +3961,52 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>有限元方法在颅脑损伤法医重建中的应用综述：可从头部FE模型（THUMS、GHBMC等）的构建与验证入手，围绕颅底环形骨折的应力传播机制，梳理'事故场景假设→数值模拟→损伤模式再现'的判别流程（摔倒vs车辆撞击），讨论FE重建作为交通事故死因鉴定证据的可靠性标准与不确定性量化方法。</t>
+          <t>死后CT血管造影（PMCTA）在法医学中的应用综述：可与MSCT血管造影综述（num 36）呼应，围绕造影剂注射途径（经股动静脉、心脏穿刺、心肺复苏途径）的技术比较，聚焦肺血栓栓塞等血管性死因的死后影像诊断价值、与传统尸检的符合率及Virtopsy理念下'穿刺-造影-PMCT-诊断'标准化流程的建立。</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>研究基于单一真实案例，结论外推性有限；模型材料参数与边界条件存在简化，未精细模拟头皮软组织与颅内容物；模拟撞击场景由案情假设驱动，初始条件设定具有主观性；缺乏实验或尸体对照的定量验证，且结果对网格密度与求解参数敏感。</t>
+          <t>研究多为小样本或个案系列，统计效能有限；心脏穿刺入路可能引入气体、造影剂外渗等人工伪影，干扰判读；尸体腐败程度、死后凝血状态影响造影剂灌注效果；与传统解剖对照的病例数有限，且操作依赖术者经验，流程缺乏多中心标准化验证。</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>This study reconstructed a motorcycle driver-car accident case using the total human model for safety and FE simulations and analyzed the biomechanisms of fatal ring fractures in the motorcyclist's skull base to determine if the fatal craniocerebral injuries were caused by a fall onto the highway after hitting a pedestrian or by the subsequent impact of a car.</t>
+          <t>Pulmonary PMCTA approach is a simple, convenient, and effective method for the visualization of the pulmonary artery, which can be used as an effective auxiliary tool to identify PTE in forensic practice and will also provide technical support to further investigate PTE imaging characteristics.</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>基于真实事故受害者CT数据构建头部有限元模型，模拟不同撞击方向/速度/部位场景，再现环形骨折模式，分析应力传播路径和骨折起始点等生物力学参数。</t>
+          <t>选择右心室心脏穿刺作为造影剂注入途径（经胸壁直接穿刺右心室），注入水溶性碘造影剂后行全身/胸部PMCT扫描，进行MIP/VR/MPR后处理重建，评估肺动脉显影及充盈缺损征象，与传统尸检大体和组织病理学结果对照验证。</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>有限元分析可有效确定摩托车事故中头部环形骨折的成因和致伤机制，为法医学调查提供科学证据支持。</t>
+          <t>经右心室心脏穿刺行肺PMCT血管造影操作简便、显影效果良好，可清晰显示PTE栓塞部位和范围，具有无创、可三维可视化、可永久存档的优势，为法医PTE死后诊断提供了创新性技术方案。</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>将有限元分析方法应用于真实摩托车事故案例的头部环形骨折成因判定，通过数值模拟再现骨折模式揭示损伤机制。</t>
+          <t>首次提出经右心室心脏穿刺作为死后肺血管造影的造影剂注入途径，避免了传统开胸对血管完整性的破坏，入路更直接操作更简便，建立了完整的'穿刺-造影-PMCT-诊断'技术流程。</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>有限元;颅骨骨折;摩托车事故</t>
+          <t>PMCTA;肺动脉血栓;右心室穿刺</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>Legal Medicine</t>
+          <t>International Journal of Legal Medicine</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>10.1016/j.legalmed.2020.101697</t>
+          <t>10.1007/s00414-020-02476-w</t>
         </is>
       </c>
     </row>
@@ -4134,20 +4016,593 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
+          <t>Species identification of semen stains by ATR-FTIR spectroscopy</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>ATR-FTIR光谱进行精斑物种鉴定</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>无需精子细胞即可实现物种鉴定，证明光谱方法在无精子症案例精斑检测中的能力，为实际法医案例中精斑物种鉴定提供强大实用工具。</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>光谱
+精斑鉴定</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>光谱</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>身份</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>2021-01</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>复旦大学基础医学院法医学系/西安交通大学法医学院</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>振动光谱（ATR-FTIR/拉曼）在法医体液鉴定中的应用综述：可围绕精液、血液、唾液等体液的无损快速鉴定展开，重点讨论'无需精子细胞即可完成物种鉴定'对无精子症/输精管结扎案例的独特价值，梳理光谱-化学计量学（或机器学习）分类流程、载体基质干扰处理及与DNA检验的互补关系，并可延伸至性犯罪案件物证检验场景。</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>光谱信号易受衣物等载体基质、环境污染与样本老化降解干扰，摘要未报告样本量、物种覆盖范围及常见污染物的耐受性验证；当前能力限于物种鉴定，无法像DNA那样进行个体识别；跨实验室、跨仪器（批次效应）的稳定性与数据库共享问题尚待解决。</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>Species identification could be achieved without sperm cells which proved ability of spectroscopic methods detecting semen samples from azoospermia cases, providing a powerful and practical tool for species identification of semen stains in real forensic casework.</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t>实验研究，不同物种精斑样本，ATR-FTIR光谱+化学计量学</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t>ATR-FTIR光谱可在无精子的情况下进行精斑物种鉴定，解决了无精子症案例的法医学难题。</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t>首次证明ATR-FTIR可在无精子细胞情况下进行精斑物种鉴定</t>
+        </is>
+      </c>
+      <c r="Q39" s="3" t="inlineStr">
+        <is>
+          <t>FTIR;精斑;物种鉴定</t>
+        </is>
+      </c>
+      <c r="R39" s="3" t="inlineStr">
+        <is>
+          <t>International Journal of Legal Medicine</t>
+        </is>
+      </c>
+      <c r="S39" s="3" t="inlineStr">
+        <is>
+          <t>10.1007/s00414-020-02367-0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>The influence of sample geometry and size on porcine aortic material properties from uniaxial tensile tests using custom-designed tissue cutters, clamps and molds</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>样本几何形状和尺寸对猪主动脉单轴拉伸材料性能的影响</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>目的：研究使用定制组织切割器进行单轴拉伸试验时，样本几何形状和尺寸对猪主动脉材料性能的影响。方法：使用定制设计的组织切割器制备不同几何形状和尺寸的猪主动脉样本，进行单轴拉伸试验并比较其材料性能。结果：样本几何形状和尺寸对测得的材料性能有显著影响，定制组织切割器提高了样本制备的一致性。结论：应标准化样本几何形状和尺寸以获得准确的材料性能测量结果，定制组织切割器是生物力学研究的有用工具。</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>法医生物力学
+主动脉力学</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>生物力学</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>损伤机制</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>2021-01</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>复旦大学基础医学院法医学系</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>软组织生物力学测试标准化综述：可围绕样本制备（几何形状、尺寸、切割工具）与测试协议（预载荷、应变率、夹持方式）对材料参数测量结果的影响展开，结合主动脉单轴拉伸的尺寸效应（符合Weibull理论）讨论狗骨形样本宽度选择依据，为血管破裂等法医生物力学分析提供可靠的基准数据获取规范，并延伸至各组织本构模型参数标定。</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>猪主动脉与人体主动脉在壁厚、弹性蛋白/胶原比例及力学响应上存在种属差异，外推至人体需谨慎；离体单轴拉伸忽略在体预张力与平滑肌活性，且单轴加载不能完全代表生理状态下的多轴应力；摘要未涉及样本保存条件（温度、时间）与个体年龄差异对结果的影响。</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>The results showed that the size effect of the aorta conformed to Weibull theory, and dog-bone-shaped specimens with a width of 4 mm were the optimal choice for aortic uniaxial tensile testing performed until rupture.</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>使用定制设计的组织切割器制备不同几何形状和尺寸的猪主动脉样本，进行单轴拉伸试验，对比分析各组样本的材料性能参数（弹性模量、极限应力等）。</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>样本几何形状和尺寸对主动脉材料性能测量有显著影响应进行标准化，定制组织切割器能提高样本制备一致性和测量准确性，是生物力学研究的有用工具。</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>自主设计定制组织切割器用于标准化生物力学样本制备，系统研究了样本几何形状和尺寸对猪主动脉单轴拉伸材料性能的影响规律。</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>生物力学;拉伸测试;主动脉</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>PLoS ONE</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>10.1371/journal.pone.0244390</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Postmortem chest computed tomography for the diagnosis of drowning: a feasibility study</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>死后胸部CT用于溺死诊断的可行性研究</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>目的：评估死后胸部CT用于溺死诊断的可行性。方法：回顾性分析溺死案例和非溺死对照的死后胸部CT表现，评估气道内液体、肺部改变和鼻窦积液等CT特征。结果：识别出与溺死相关的特异性CT表现，多个CT特征的联合应用提高了诊断准确性。结论：死后胸部CT是法医学实践中溺死诊断的可行辅助方法。</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>法医影像学
+溺死诊断</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>影像</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>死亡方式</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>2021-01</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>复旦大学基础医学院法医学系</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>死后影像学在溺死诊断中的应用综述：可从胸部PMCT特征（气道内液体、肺水肿、鼻窦积液等）的诊断价值与特异性入手，梳理溺死与冠心病等常见死后改变的影像鉴别要点（摘要即以CAD为对照），讨论多特征联合诊断策略、影像与硅藻检验/尸检的组织病理证据互补模式，以及影像组学与AI辅助判读在溺死诊断中的前景。</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>研究为回顾性设计，病例选择与对照组设置可能存在偏倚；气道液体、肺水肿等CT表现在死后可因尸体搬运、复苏操作及腐败进程发生改变，与CAD鉴别时特异性有限；摘要未报告样本量与多中心验证情况，且未与硅藻检验等既有金标准方法进行系统比较。</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>The aim of this study was to explore the forensic value of thoracic postmortem computed tomography (PMCT) using routine images and three-dimensional image reconstructions to distinguish between drowning and CAD.</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t>回顾性收集溺死案例和非溺死对照的死后胸部CT影像，评估气道内液体、肺部磨玻璃/实变改变、鼻窦积液等CT特征，比较两组CT表现差异并分析多特征联合诊断效能。</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t>死后胸部CT是法医学溺死诊断的可行辅助方法，多项CT特征联合应用可提高诊断准确性。</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t>首次系统探讨死后胸部CT在溺死诊断中的可行性，提出多项CT特征联合诊断策略。</t>
+        </is>
+      </c>
+      <c r="Q41" s="3" t="inlineStr">
+        <is>
+          <t>PMCT;溺死诊断;胸部CT</t>
+        </is>
+      </c>
+      <c r="R41" s="3" t="inlineStr">
+        <is>
+          <t>Forensic Sciences Research</t>
+        </is>
+      </c>
+      <c r="S41" s="3" t="inlineStr">
+        <is>
+          <t>10.1080/20961790.2018.1557386</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Research Status of Postmortem MSCT Angiography in Forensic Science</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>法医学死后MSCT血管造影研究现状</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>死后多层螺旋CT(MSCT)血管造影是法医学影像领域的重要进展。本文综述了法医学死后MSCT血管造影的研究现状，包括其技术原理、操作方法以及在不同法医学场景中的应用，讨论了不同血管造影技术的优缺点，并提出了未来的发展方向。死后MSCT血管造影在心血管疾病诊断、创伤评估及其他法医学应用中展现了巨大潜力。</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>法医影像学</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>影像</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>死因</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>2020-12</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>复旦大学基础医学院法医学系</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>中文核心（JCR未收录）</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>虚拟解剖与死后影像技术体系综述：该文本身即PMCTA综述，可进一步牵引'死后CT血管造影技术路线全景'——系统比较全身血管造影、心肺复苏途径、靶向造影、心脏穿刺等入路的技术原理与优劣，梳理心血管死因诊断、创伤评估等应用场景，并围绕操作流程标准化、多中心验证及造影后影像结合AI定量分析等未来方向展开。</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>作为综述，其结论受已有文献异质性限制：各研究间造影剂配方、灌注参数与判读标准不统一，缺乏大型前瞻性多中心对照数据；PMCTA对微小血管病变和功能学信息（缺血）无法显示，与传统尸检的符合率报道不一，证据等级有待提升。</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>Virtual autopsy is a new technique for investigating the morphological changes of cadaveric tissues and organs by medical imaging technology. This article summarizes several common cadaveric MSCT angiography methods, such as systemic angiography, angiography through cardiopulmonary resuscitation, targeted angiography, and angiography by cardiac puncture.</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>文献综述：系统梳理死后MSCT血管造影的技术原理（造影剂类型、注射途径、扫描参数）、操作方法和在不同法医场景（心血管疾病、创伤、器官病变）中的应用，比较分析不同造影技术的优缺点。</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>死后MSCT血管造影在法医学心血管疾病诊断和创伤评估等方面具有巨大潜力，未来需在标准化操作流程和多中心验证方面进一步发展完善。</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>系统综述了死后MSCT血管造影在法医学中的研究现状和技术路线，总结比较了不同造影技术的优劣并提出了标准化发展方向。</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>法医学杂志;血管造影;虚拟解剖;MSCT</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>Fa yi xue za zhi</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>10.12116/j.issn.1004-5619.2020.06.012</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Research advances in forensic diatom testing</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>法医硅藻检验研究进展（综述）</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>回顾数十年来硅藻检验的发展，并讨论深度学习在硅藻检验中的潜在应用新方法。</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>硅藻检验</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>AI/机器学习;综述</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>死因</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>复旦大学基础医学院法医学系/司法鉴定科学研究院</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>法医硅藻检验技术发展综述：可沿'经典消化法（强酸/酶解）→镜检定量→AI自动识别'的技术演进主线，梳理硅藻检验的假阳性/污染控制、定量标准（LMA、定量消化法）与质控问题，重点前瞻深度学习在样品处理到结果判读全自动化中的应用前景，可作为AI硅藻系列研究（num 26/31/40/45）的综述骨架。</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>作为综述，其关于深度学习的论述多为方向性展望，所依据的实证研究样本量小、缺乏多中心验证；硅藻检验本身存在污染与假阳性问题，各实验室消化方法学不统一，导致不同研究间结果可比性差，综述难以给出统一证据等级。</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>Review of the development of diatom testing over the decades and discussion of a new method for the potential application of deep learning in diatom testing.</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t>文献综述，系统回顾硅藻检验技术的发展历程（从化学消解到AI辅助识别）</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t>深度学习技术为硅藻自动识别带来革命性变化，有望实现从样品处理到结果判读的全自动化。</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t>系统梳理硅藻检验技术发展历程并前瞻深度学习应用</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr">
+        <is>
+          <t>硅藻;深度学习;溺死;综述</t>
+        </is>
+      </c>
+      <c r="R43" s="3" t="inlineStr">
+        <is>
+          <t>Forensic Sciences Research</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr">
+        <is>
+          <t>10.1080/20961790.2020.1718901</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Finite element analysis to determine the cause of ring fractures in a motorcyclist's head</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>有限元分析确定摩托车骑手头部环形骨折的成因</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>目的：使用有限元分析方法确定摩托车骑手头部环形骨折的成因。方法：基于真实摩托车事故受害者的CT数据构建人体头部有限元模型，模拟不同撞击场景以再现环形骨折模式，分析损伤机制。结果：通过模拟特定撞击场景成功再现了环形骨折模式，生物力学分析揭示了损伤机制。结论：有限元分析可以有效确定摩托车事故中环形骨折的成因，为法医学调查提供科学依据。</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>事故重建</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>生物力学</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>损伤机制</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>2020-07</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>复旦大学基础医学院法医学系</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>有限元方法在颅脑损伤法医重建中的应用综述：可从头部FE模型（THUMS、GHBMC等）的构建与验证入手，围绕颅底环形骨折的应力传播机制，梳理'事故场景假设→数值模拟→损伤模式再现'的判别流程（摔倒vs车辆撞击），讨论FE重建作为交通事故死因鉴定证据的可靠性标准与不确定性量化方法。</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>研究基于单一真实案例，结论外推性有限；模型材料参数与边界条件存在简化，未精细模拟头皮软组织与颅内容物；模拟撞击场景由案情假设驱动，初始条件设定具有主观性；缺乏实验或尸体对照的定量验证，且结果对网格密度与求解参数敏感。</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>This study reconstructed a motorcycle driver-car accident case using the total human model for safety and FE simulations and analyzed the biomechanisms of fatal ring fractures in the motorcyclist's skull base to determine if the fatal craniocerebral injuries were caused by a fall onto the highway after hitting a pedestrian or by the subsequent impact of a car.</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>基于真实事故受害者CT数据构建头部有限元模型，模拟不同撞击方向/速度/部位场景，再现环形骨折模式，分析应力传播路径和骨折起始点等生物力学参数。</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>有限元分析可有效确定摩托车事故中头部环形骨折的成因和致伤机制，为法医学调查提供科学证据支持。</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>将有限元分析方法应用于真实摩托车事故案例的头部环形骨折成因判定，通过数值模拟再现骨折模式揭示损伤机制。</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>有限元;颅骨骨折;摩托车事故</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>Legal Medicine</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>10.1016/j.legalmed.2020.101697</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
           <t>Determination of causes of death via spectrochemical analysis of forensic autopsies-based pulmonary edema fluid samples with deep learning algorithm</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr">
         <is>
           <t>基于法医尸检肺水肿液样本的光谱化学分析与深度学习算法判定死因</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="D45" s="3" t="inlineStr">
         <is>
           <t>配备深度学习的FTIR光谱技术有潜力成为死因判定的有效辅助工具。</t>
         </is>
       </c>
-      <c r="E39" s="3" t="inlineStr">
+      <c r="E45" s="3" t="inlineStr">
         <is>
           <t>光谱分析
 深度学习
@@ -4155,648 +4610,74 @@
 法医病理</t>
         </is>
       </c>
-      <c r="F39" s="3" t="inlineStr">
+      <c r="F45" s="3" t="inlineStr">
         <is>
           <t>AI/机器学习;光谱</t>
         </is>
       </c>
-      <c r="G39" s="3" t="inlineStr">
+      <c r="G45" s="3" t="inlineStr">
         <is>
           <t>死因</t>
         </is>
       </c>
-      <c r="H39" s="3" t="inlineStr">
+      <c r="H45" s="3" t="inlineStr">
         <is>
           <t>2020-04</t>
         </is>
       </c>
-      <c r="I39" s="3" t="inlineStr">
+      <c r="I45" s="3" t="inlineStr">
         <is>
           <t>复旦大学基础医学院法医学系/西安交通大学法医学院</t>
         </is>
       </c>
-      <c r="J39" s="3" t="inlineStr">
+      <c r="J45" s="3" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="K39" s="3" t="inlineStr">
+      <c r="K45" s="3" t="inlineStr">
         <is>
           <t>光谱化学分析与机器学习在法医死因判定中的应用综述：可从生物样本（肺水肿液、血浆、组织）的FTIR/拉曼谱学特征出发，围绕溺死、心源性猝死、窒息等死因类别的机器学习判别模型，梳理光谱预处理、特征选择与模型验证标准，并讨论光谱组学（spectrochemical omics）作为传统病理检验补充手段的转化路径与质控要求。</t>
         </is>
       </c>
-      <c r="L39" s="3" t="inlineStr">
+      <c r="L45" s="3" t="inlineStr">
         <is>
           <t>肺水肿液取材受死后变化、腐败及肺基础疾病影响，死因间光谱差异可能部分混入死后时间等混杂因素；摘要未报告训练样本量与独立外部验证集；深度学习判别缺乏可解释性，难以定位具体生化标志物；样本采集与光谱采集的标准化流程亦需明确。</t>
         </is>
       </c>
-      <c r="M39" s="3" t="inlineStr">
+      <c r="M45" s="3" t="inlineStr">
         <is>
           <t>Deep learning-equipped FTIR spectroscopy technique has the potential to be an effective aid for determining causes of death.</t>
         </is>
       </c>
-      <c r="N39" s="3" t="inlineStr">
+      <c r="N45" s="3" t="inlineStr">
         <is>
           <t>人尸检肺水肿液样本，FTIR光谱+深度学习算法(CNN)</t>
         </is>
       </c>
-      <c r="O39" s="3" t="inlineStr">
+      <c r="O45" s="3" t="inlineStr">
         <is>
           <t>FTIR光谱结合深度学习可从肺水肿液准确区分不同死因（溺死、SCD、窒息等），为法医学提供智能化辅助诊断。</t>
         </is>
       </c>
-      <c r="P39" s="3" t="inlineStr">
+      <c r="P45" s="3" t="inlineStr">
         <is>
           <t>首次将深度学习与FTIR光谱化学分析结合用于法医死因判定</t>
         </is>
       </c>
-      <c r="Q39" s="3" t="inlineStr">
+      <c r="Q45" s="3" t="inlineStr">
         <is>
           <t>FTIR;深度学习;死因鉴定;肺水肿</t>
         </is>
       </c>
-      <c r="R39" s="3" t="inlineStr">
+      <c r="R45" s="3" t="inlineStr">
         <is>
           <t>Journal of Biophotonics</t>
         </is>
       </c>
-      <c r="S39" s="3" t="inlineStr">
+      <c r="S45" s="3" t="inlineStr">
         <is>
           <t>10.1002/jbio.201960144</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>Relationship between Postmortem Interval and FTIR Spectroscopy Changes of the Rat Skin</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>死后间隔时间与大鼠皮肤FTIR光谱变化的关系</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>研究死后间隔时间与大鼠皮肤FTIR光谱变化的关系，用于PMI推断。</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>死后间隔时间
-光谱分析</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>光谱</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>PMI</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>2020-04</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>复旦大学基础医学院法医学系/司法鉴定科学研究院</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>中文核心（JCR未收录）</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>振动光谱在死亡时间推断中的应用综述：可围绕不同组织（皮肤、肝、脑、肌肉）FTIR光谱随PMI的时序变化规律，梳理光谱特征峰（蛋白质二级结构、脂质氧化、核酸降解）与死后生化降解过程的对应关系，比较光谱定量回归模型与尸温、生化标志物等经典PMI方法的优劣，并讨论无创/微创光谱技术的现场应用前景。</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>研究基于大鼠模型，种属间皮肤结构与腐败进程差异限制人体外推；光谱变化速率受环境温度、湿度及季节强烈影响，摘要未报告环境控制方案；仅考察单一组织，个体差异（年龄、死因、肥胖）及尸体表面污染对光谱的干扰未评估。</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>Relationship between PMI and FTIR spectroscopy changes of rat skin for postmortem interval estimation.</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>动物实验，大鼠皮肤组织，FTIR光谱+时间序列分析</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>大鼠皮肤FTIR光谱随PMI呈现规律性变化，可用于死后间隔时间推断。</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>建立皮肤FTIR光谱变化与PMI的定量关系</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>FTIR;皮肤;死亡时间;法医学杂志</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>法医学杂志 (Journal of Forensic Medicine)</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t>10.12116/j.issn.1004-5619.2020.02.008</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>Application of Artificial Intelligence Automatic Diatom Identification System in Practical Cases</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>人工智能自动硅藻识别系统在实际案例中的应用</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>AI自动硅藻识别系统在实际法医案例中的应用研究。</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>硅藻识别
-人工智能</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t>AI/机器学习</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t>死因</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>2020-04</t>
-        </is>
-      </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t>复旦大学基础医学院法医学系/司法鉴定科学研究院</t>
-        </is>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>中文核心（JCR未收录）</t>
-        </is>
-      </c>
-      <c r="K41" s="3" t="inlineStr">
-        <is>
-          <t>AI辅助硅藻检验的临床转化综述：可围绕'实验室验证→实际案例应用'的转化路径，梳理AI硅藻自动识别系统的性能评估框架（与人工镜检一致性、检出限、假阳性率），讨论影响实际案例表现的因素（样本消化方法兼容性、硅藻丰度、制片质量），并延伸至检验流程自动化与法医实验室认可（ISO 17025）等标准化议题。</t>
-        </is>
-      </c>
-      <c r="L41" s="3" t="inlineStr">
-        <is>
-          <t>实际案例样本量有限且类型分布不均衡，难以系统评估系统在不同死因、不同水域案例中的稳健性；与人工镜检的一致性比较受金标准判读主观性影响；不同消化与制片方法制备的样本对识别性能的影响未系统验证；系统对扫描设备与计算环境的依赖限制其普适推广。</t>
-        </is>
-      </c>
-      <c r="M41" s="3" t="inlineStr">
-        <is>
-          <t>Application of AI automatic diatom identification system in practical forensic cases.</t>
-        </is>
-      </c>
-      <c r="N41" s="3" t="inlineStr">
-        <is>
-          <t>实际案例验证，溺死案例硅藻样本，AI自动识别系统+人工对比</t>
-        </is>
-      </c>
-      <c r="O41" s="3" t="inlineStr">
-        <is>
-          <t>AI自动硅藻识别系统在实际案例中表现出良好的识别准确率，可辅助法医溺死诊断。</t>
-        </is>
-      </c>
-      <c r="P41" s="3" t="inlineStr">
-        <is>
-          <t>首次将AI硅藻识别系统应用于实际法医案例验证</t>
-        </is>
-      </c>
-      <c r="Q41" s="3" t="inlineStr">
-        <is>
-          <t>硅藻;AI;实际案例;法医学杂志</t>
-        </is>
-      </c>
-      <c r="R41" s="3" t="inlineStr">
-        <is>
-          <t>法医学杂志 (Journal of Forensic Medicine)</t>
-        </is>
-      </c>
-      <c r="S41" s="3" t="inlineStr">
-        <is>
-          <t>10.12116/j.issn.1004-5619.2020.02.017</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>The approach of virtual autopsy (VIRTOPSY) by postmortem multi-slice computed tomography (PMCT) in China for forensic pathology</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>中国法医病理学死后多层螺旋CT虚拟解剖方法</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>利用死后多层螺旋CT(PMCT)进行虚拟解剖(VIRTOPSY)是法医病理学中的新兴技术。本文介绍了中国利用PMCT进行虚拟解剖的方法，包括技术方案、应用范围和案例实例，讨论了PMCT与传统解剖的整合。基于PMCT的虚拟解剖在中国法医学实践中对创伤分析、疾病诊断和身份识别具有重要价值。</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>法医病理
-死后影像学</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>影像</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>死因</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>2020-03</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>复旦大学基础医学院法医学系</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>未收录（JCR无）</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>虚拟解剖（VIRTOPSY）在中国的应用现状与发展综述：可围绕PMCT技术方案的本土化实践，梳理虚拟解剖在创伤分析、疾病诊断、身份识别三大领域的应用价值，讨论PMCT与传统尸检的整合流程与互补关系（各自检出优势与盲区），并结合中国多中心实践、设备配置、读片资质与质量控制等议题提出发展建议。</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>综述性质决定其结论依赖既有文献，且PMCT对软组织对比度有限，早期梗死、微小栓塞等病变易漏诊；缺乏大样本与传统尸检的系统对照研究；扫描方案、设备型号与读片人员资质尚未标准化，中国各地区实践差异大，可比性与证据等级受限。</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>Some papers published in recent years in forensic science journals domestic and abroad are reviewed to show the present VIRTOPSY by postmortem multi-slice computed tomography (PMCT) applications in china for forensic pathology.</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>介绍中国PMCT虚拟解剖的技术方案（扫描参数、后处理技术）、应用范围（创伤、疾病、身份识别），通过案例实例展示应用效果，讨论PMCT与传统尸体解剖的互补整合方式。</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t>基于PMCT的虚拟解剖在中国法医学创伤分析、疾病诊断和身份识别中具有重要价值，可发挥传统解剖的补充作用。</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>系统介绍了中国法医病理学中PMCT虚拟解剖方法的技术方案和应用实践，总结了中国在该领域的本土化经验。</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t>综述;PMCT;虚拟解剖;VIRTOPSY</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t>Forensic Imaging</t>
-        </is>
-      </c>
-      <c r="S42" s="2" t="inlineStr">
-        <is>
-          <t>10.1016/j.fri.2020.200361</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>Research advances in forensic diatom testing</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>法医硅藻检验研究进展（综述）</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>回顾数十年来硅藻检验的发展，并讨论深度学习在硅藻检验中的潜在应用新方法。</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>硅藻检验</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t>AI/机器学习;综述</t>
-        </is>
-      </c>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t>死因</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t>复旦大学基础医学院法医学系/司法鉴定科学研究院</t>
-        </is>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="K43" s="3" t="inlineStr">
-        <is>
-          <t>法医硅藻检验技术发展综述：可沿'经典消化法（强酸/酶解）→镜检定量→AI自动识别'的技术演进主线，梳理硅藻检验的假阳性/污染控制、定量标准（LMA、定量消化法）与质控问题，重点前瞻深度学习在样品处理到结果判读全自动化中的应用前景，可作为AI硅藻系列研究（num 26/31/40/45）的综述骨架。</t>
-        </is>
-      </c>
-      <c r="L43" s="3" t="inlineStr">
-        <is>
-          <t>作为综述，其关于深度学习的论述多为方向性展望，所依据的实证研究样本量小、缺乏多中心验证；硅藻检验本身存在污染与假阳性问题，各实验室消化方法学不统一，导致不同研究间结果可比性差，综述难以给出统一证据等级。</t>
-        </is>
-      </c>
-      <c r="M43" s="3" t="inlineStr">
-        <is>
-          <t>Review of the development of diatom testing over the decades and discussion of a new method for the potential application of deep learning in diatom testing.</t>
-        </is>
-      </c>
-      <c r="N43" s="3" t="inlineStr">
-        <is>
-          <t>文献综述，系统回顾硅藻检验技术的发展历程（从化学消解到AI辅助识别）</t>
-        </is>
-      </c>
-      <c r="O43" s="3" t="inlineStr">
-        <is>
-          <t>深度学习技术为硅藻自动识别带来革命性变化，有望实现从样品处理到结果判读的全自动化。</t>
-        </is>
-      </c>
-      <c r="P43" s="3" t="inlineStr">
-        <is>
-          <t>系统梳理硅藻检验技术发展历程并前瞻深度学习应用</t>
-        </is>
-      </c>
-      <c r="Q43" s="3" t="inlineStr">
-        <is>
-          <t>硅藻;深度学习;溺死;综述</t>
-        </is>
-      </c>
-      <c r="R43" s="3" t="inlineStr">
-        <is>
-          <t>Forensic Sciences Research</t>
-        </is>
-      </c>
-      <c r="S43" s="3" t="inlineStr">
-        <is>
-          <t>10.1080/20961790.2020.1718901</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>Research Progress on Age Estimation Based on DNA Methylation</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>基于DNA甲基化的年龄推断研究进展</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>年龄推断是法医学中的重要任务。DNA甲基化已成为一种有前景的年龄推断分子标志物。本文综述了基于DNA甲基化的年龄推断研究进展，包括DNA甲基化年龄推断的原理、常用甲基化标志物、检测方法和统计模型，并讨论了该领域面临的挑战和未来发展方向。基于DNA甲基化的年龄推断方法已显示出较高准确性，在法医学应用中具有巨大潜力。</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>年龄推断</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>分子生物学</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>身份</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>2019-10</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>复旦大学基础医学院法医学系</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>中文核心（JCR未收录）</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>表观遗传学在法医个体识别中的应用综述：可围绕DNA甲基化年龄时钟的原理（甲基化位点选择、组织特异性），梳理血液、血痕、唾液、精斑等不同体液样本的检测平台（焦磷酸测序、单碱基延伸、二代测序）与统计模型比较，讨论组织类型差异、环境与疾病混杂因素及跨人群（种族）迁移性，形成从标志物发现到标准化应用的完整综述框架。</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>作为综述，其指出现有方法仍面临组织类型差异、环境因素影响与标准化不足等挑战；多数年龄预测模型基于特定人群开发，跨种族应用需校正且精度随年龄增大而下降；摘要未比较不同检测平台的重复性与成本效益，缺乏对模型外部验证现状的系统评价。</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>Age estimation is of great significance in the fields of criminal investigation and forensic identification. With the rapid development of epigenetics represented by DNA methylation, many age estimation methods based on DNA methylation biomarkers using several biological fluids such as blood, blood stains, saliva, semen stains are developed. This paper summarizes the researches on age estimation based on DNA methylation.</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>文献综述：阐述DNA甲基化年龄推断的表观遗传学原理（CpG位点甲基化随年龄变化的规律），梳理常用甲基化标志物基因位点(如ELOVL2、FHL2等)、检测方法（焦磷酸测序、微阵列、靶向甲基化测序等）和统计模型（多元回归、机器学习等），分析当前挑战和未来方向。</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>基于DNA甲基化的年龄推断方法准确性较高，在法医学应用中具有巨大潜力，但仍面临组织类型差异、环境因素影响和标准化等挑战。</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>全面综述了DNA甲基化年龄推断领域从原理到应用的完整链条，系统梳理了标志物基因位点、检测平台和统计模型的进展。</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t>法医学杂志;年龄推断;DNA甲基化</t>
-        </is>
-      </c>
-      <c r="R44" s="2" t="inlineStr">
-        <is>
-          <t>Fa yi xue za zhi</t>
-        </is>
-      </c>
-      <c r="S44" s="2" t="inlineStr">
-        <is>
-          <t>10.12116/j.issn.1004-5619.2019.05.006</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>Postmortem diagnosis of fatal hypothermia/hyperthermia by spectrochemical analysis of plasma</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>通过血浆光谱化学分析进行致命性低温/高温的死后诊断</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>ATR-FTIR光谱在致命性低温/高温的死后诊断中展示了巨大潜力。溶血和死后效应未削弱分类模型的预测能力。</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="inlineStr">
-        <is>
-          <t>光谱分析
-死亡诊断</t>
-        </is>
-      </c>
-      <c r="F45" s="3" t="inlineStr">
-        <is>
-          <t>光谱</t>
-        </is>
-      </c>
-      <c r="G45" s="3" t="inlineStr">
-        <is>
-          <t>死因</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t>2019-09</t>
-        </is>
-      </c>
-      <c r="I45" s="3" t="inlineStr">
-        <is>
-          <t>复旦大学基础医学院法医学系/西安交通大学法医学院</t>
-        </is>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
-      <c r="K45" s="3" t="inlineStr">
-        <is>
-          <t>光谱法在异常体温死亡（低温/高温）死后诊断中的应用综述：可围绕传统死后生化标志物（儿茶酚胺、酮体、应激激素等）与ATR-FTIR光谱快检的互补关系，梳理血浆光谱特征与体温调节紊乱的对应，讨论溶血与死后效应稳健性验证（该文已证实）对实际案例的意义，并与组织水平光谱（如下丘脑，见num 48）整合为多层次诊断体系。</t>
-        </is>
-      </c>
-      <c r="L45" s="3" t="inlineStr">
-        <is>
-          <t>摘要虽报告溶血与死后效应未削弱预测能力，但未给出样本量及死后时间跨度范围，更长时间腐败条件下光谱稳定性未知；低温/高温死亡与脓毒症、甲状腺危象等自然发热疾病的鉴别特异性有待验证；对照组选择（死因构成）直接影响分类性能，缺乏盲法外部验证。</t>
-        </is>
-      </c>
-      <c r="M45" s="3" t="inlineStr">
-        <is>
-          <t>ATR-FTIR spectroscopy demonstrated great potential for postmortem diagnosis of fatal hypothermia/hyperthermia. Hemolysis and postmortem effects did not weaken the prediction ability of classification models.</t>
-        </is>
-      </c>
-      <c r="N45" s="3" t="inlineStr">
-        <is>
-          <t>动物实验+人体样本，大鼠模型+人血浆，ATR-FTIR光谱+PLS-DA+SVM</t>
-        </is>
-      </c>
-      <c r="O45" s="3" t="inlineStr">
-        <is>
-          <t>ATR-FTIR光谱可从血浆中鉴定致命性低温和高温，且不受溶血和死后变化影响，具有法医学实用价值。</t>
-        </is>
-      </c>
-      <c r="P45" s="3" t="inlineStr">
-        <is>
-          <t>首次使用血浆ATR-FTIR光谱区分致命性低温/高温死亡，并验证死后变化的稳健性</t>
-        </is>
-      </c>
-      <c r="Q45" s="3" t="inlineStr">
-        <is>
-          <t>FTIR;低温;高温;血浆</t>
-        </is>
-      </c>
-      <c r="R45" s="3" t="inlineStr">
-        <is>
-          <t>Forensic Science, Medicine, and Pathology</t>
-        </is>
-      </c>
-      <c r="S45" s="3" t="inlineStr">
-        <is>
-          <t>10.1007/s12024-019-00111-8</t>
         </is>
       </c>
     </row>
@@ -4806,93 +4687,93 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Digital whole-slide image analysis for automated diatom test in forensic cases of drowning using a convolutional neural network algorithm</t>
+          <t>Relationship between Postmortem Interval and FTIR Spectroscopy Changes of the Rat Skin</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>使用CNN算法的数字全切片图像分析用于法医溺死案例自动硅藻检测</t>
+          <t>死后间隔时间与大鼠皮肤FTIR光谱变化的关系</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>基于AI的系统结合经典化学消解法自动识别硅藻。为未来智能硅藻检验铺平道路。</t>
+          <t>研究死后间隔时间与大鼠皮肤FTIR光谱变化的关系，用于PMI推断。</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>算法、图像分析
-硅藻与溺死诊断</t>
+          <t>死后间隔时间
+光谱分析</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>AI/机器学习</t>
+          <t>光谱</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>死因</t>
+          <t>PMI</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>2019-09</t>
+          <t>2020-04</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>复旦大学基础医学院法医学系/司法鉴定科学研究院/西安交通大学</t>
+          <t>复旦大学基础医学院法医学系/司法鉴定科学研究院</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>中文核心（JCR未收录）</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>数字病理与全切片图像分析（WSI）在法医学中的应用综述：可从硅藻全切片自动检测这一开创性工作切入，梳理WSI扫描-拼接-标注-训练的AI流水线、CNN架构与训练策略（数据增强、弱监督），讨论与传统化学消化法结合的自动化检验体系，并延伸至WSI-AI在心肌梗死、肺损伤等法医组织病理诊断中的扩展应用。</t>
+          <t>振动光谱在死亡时间推断中的应用综述：可围绕不同组织（皮肤、肝、脑、肌肉）FTIR光谱随PMI的时序变化规律，梳理光谱特征峰（蛋白质二级结构、脂质氧化、核酸降解）与死后生化降解过程的对应关系，比较光谱定量回归模型与尸温、生化标志物等经典PMI方法的优劣，并讨论无创/微创光谱技术的现场应用前景。</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>作为该方向开创性工作，训练与验证样本量有限，硅藻类别多样性不足；全切片扫描耗时且数据存储量大，对计算资源要求高；不同制片工艺与扫描仪间的图像域差异可能导致模型性能漂移；检出率与人工鉴定对比受金标准判定主观性影响，缺乏前瞻性外部验证。</t>
+          <t>研究基于大鼠模型，种属间皮肤结构与腐败进程差异限制人体外推；光谱变化速率受环境温度、湿度及季节强烈影响，摘要未报告环境控制方案；仅考察单一组织，个体差异（年龄、死因、肥胖）及尸体表面污染对光谱的干扰未评估。</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>An AI-based system to automatically identify diatoms in conjunction with a classical chemical digestion approach. Paves the way for future intelligent diatom examinations.</t>
+          <t>Relationship between PMI and FTIR spectroscopy changes of rat skin for postmortem interval estimation.</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>实验验证，全切片数字图像，CNN算法+传统化学消解法</t>
+          <t>动物实验，大鼠皮肤组织，FTIR光谱+时间序列分析</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>CNN可在全切片图像中自动识别硅藻，准确率与人工鉴定相当，但效率大幅提高。</t>
+          <t>大鼠皮肤FTIR光谱随PMI呈现规律性变化，可用于死后间隔时间推断。</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>首次将CNN应用于全切片硅藻数字图像自动识别，是该领域的开创性工作</t>
+          <t>建立皮肤FTIR光谱变化与PMI的定量关系</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>硅藻;CNN;深度学习;溺死诊断</t>
+          <t>FTIR;皮肤;死亡时间;法医学杂志</t>
         </is>
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>Forensic Science International</t>
+          <t>法医学杂志 (Journal of Forensic Medicine)</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>10.1016/j.forsciint.2019.109922</t>
+          <t>10.12116/j.issn.1004-5619.2020.02.008</t>
         </is>
       </c>
     </row>
@@ -4902,93 +4783,93 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Bibliometric Analysis of Medical Malpractice Literature in Legal Medicine from 1975 to 2018: Web of Science Review</t>
+          <t>Application of Artificial Intelligence Automatic Diatom Identification System in Practical Cases</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>1975-2018年法医学医疗纠纷文献的文献计量学分析：Web of Science综述</t>
+          <t>人工智能自动硅藻识别系统在实际案例中的应用</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>目的：分析1975年至2018年法医学领域医疗纠纷文献的全球研究趋势。方法：使用Web of Science数据库进行文献计量学分析，检索法医学中与医疗纠纷相关的出版物，按年份、国家、期刊、作者和关键词进行分析。结果：共鉴定出若干相关出版物，发表数量呈逐年增长趋势，美国是最高产国家，通过关键词分析识别出研究热点。结论：该文献计量学分析全面展示了法医学医疗纠纷研究概况，有助于了解研究趋势和热点主题。</t>
+          <t>AI自动硅藻识别系统在实际法医案例中的应用研究。</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>医疗纠纷
-文献计量学</t>
+          <t>硅藻识别
+人工智能</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>综述</t>
+          <t>AI/机器学习</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>死因</t>
         </is>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>2019-08</t>
+          <t>2020-04</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>复旦大学基础医学院法医学系</t>
+          <t>复旦大学基础医学院法医学系/司法鉴定科学研究院</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>中文核心（JCR未收录）</t>
         </is>
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>法医学医疗纠纷鉴定研究综述：可基于文献计量揭示的研究热点（误诊、手术并发症、死因争议等）与增长趋势，围绕医疗过错鉴定的医学-法律交叉框架，比较不同国家（美国、中国等）鉴定模式与制度差异，梳理法医学鉴定在医疗纠纷解决中的角色演变、证据标准与质量控制，形成学科交叉型综述。</t>
+          <t>AI辅助硅藻检验的临床转化综述：可围绕'实验室验证→实际案例应用'的转化路径，梳理AI硅藻自动识别系统的性能评估框架（与人工镜检一致性、检出限、假阳性率），讨论影响实际案例表现的因素（样本消化方法兼容性、硅藻丰度、制片质量），并延伸至检验流程自动化与法医实验室认可（ISO 17025）等标准化议题。</t>
         </is>
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>分析仅基于Web of Science单一数据库，存在英文期刊偏好，中文及非英文法医学文献大量遗漏，代表性受限；检索到的379篇文献规模本身反映该领域研究不足，计量分析无法评价单篇研究质量；关键词与引用网络分析存在主观性，且数据截止2018年，时效性下降。</t>
+          <t>实际案例样本量有限且类型分布不均衡，难以系统评估系统在不同死因、不同水域案例中的稳健性；与人工镜检的一致性比较受金标准判读主观性影响；不同消化与制片方法制备的样本对识别性能的影响未系统验证；系统对扫描设备与计算环境的依赖限制其普适推广。</t>
         </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t>OBJECTIVE: To determine the history of malpractice literature using forensic science based on bibliometric and graph theory. 379 papers and 3160 citing articles were retrieved. This bibliometric analysis indicated that studying the field of medical malpractice was poor during 1975-2018.</t>
+          <t>Application of AI automatic diatom identification system in practical forensic cases.</t>
         </is>
       </c>
       <c r="N47" s="3" t="inlineStr">
         <is>
-          <t>以Web of Science为数据源检索1975-2018年法医学医疗纠纷相关文献，按发表年份、国家/地区、来源期刊、高产作者和关键词进行文献计量学分析，通过关键词共现分析识别研究热点。</t>
+          <t>实际案例验证，溺死案例硅藻样本，AI自动识别系统+人工对比</t>
         </is>
       </c>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>法医学医疗纠纷研究文献呈增长趋势美国领先，该文献计量分析为该领域研究趋势和热点提供了全面参考。</t>
+          <t>AI自动硅藻识别系统在实际案例中表现出良好的识别准确率，可辅助法医溺死诊断。</t>
         </is>
       </c>
       <c r="P47" s="3" t="inlineStr">
         <is>
-          <t>首次对1975-2018年法医学领域医疗纠纷文献进行系统性文献计量分析，揭示了该领域的全球研究趋势和热点主题演变。</t>
+          <t>首次将AI硅藻识别系统应用于实际法医案例验证</t>
         </is>
       </c>
       <c r="Q47" s="3" t="inlineStr">
         <is>
-          <t>综述;文献计量学;医疗纠纷</t>
+          <t>硅藻;AI;实际案例;法医学杂志</t>
         </is>
       </c>
       <c r="R47" s="3" t="inlineStr">
         <is>
-          <t>Journal of Forensic and Legal Medicine</t>
+          <t>法医学杂志 (Journal of Forensic Medicine)</t>
         </is>
       </c>
       <c r="S47" s="3" t="inlineStr">
         <is>
-          <t>10.1016/j.jflm.2019.07.002</t>
+          <t>10.12116/j.issn.1004-5619.2020.02.017</t>
         </is>
       </c>
     </row>
@@ -4998,38 +4879,38 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Prediction of injury risks and features among scooter riders through MADYMO reconstruction of a scooter-microvan accident: Identifying the driver and passengers</t>
+          <t>The approach of virtual autopsy (VIRTOPSY) by postmortem multi-slice computed tomography (PMCT) in China for forensic pathology</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>MADYMO重建摩托车事故预测骑手损伤风险与特征：驾驶员与乘客识别</t>
+          <t>中国法医病理学死后多层螺旋CT虚拟解剖方法</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>目的：通过MADYMO软件重建一起摩托车-微型货车事故，预测摩托车骑手的损伤风险与特征，并识别驾驶员与乘客。方法：使用MADYMO软件重建真实事故，模拟两名骑手的运动学和损伤参数，并将模拟结果与实际损伤情况进行比较。结果：模拟结果显示驾驶员与乘客具有不同的损伤模式，预测损伤与实际损伤一致。结论：MADYMO事故重建可有效预测损伤风险，有助于识别摩托车事故中的驾驶员与乘客身份。</t>
+          <t>利用死后多层螺旋CT(PMCT)进行虚拟解剖(VIRTOPSY)是法医病理学中的新兴技术。本文介绍了中国利用PMCT进行虚拟解剖的方法，包括技术方案、应用范围和案例实例，讨论了PMCT与传统解剖的整合。基于PMCT的虚拟解剖在中国法医学实践中对创伤分析、疾病诊断和身份识别具有重要价值。</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>事故重建
-MADYMO</t>
+          <t>法医病理
+死后影像学</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>生物力学</t>
+          <t>影像</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>身份</t>
+          <t>死因</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>2019-07</t>
+          <t>2020-03</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
@@ -5039,52 +4920,52 @@
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>未收录（JCR无）</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>多体动力学在交通事故法医重建中的应用综述：可围绕MADYMO等多体模型与有限元模型的方法学比较（计算效率vs细节分辨率），梳理事故重建流程（初始条件设定、运动学/损伤参数输出）、损伤特征与驾驶员/乘客身份识别的关联框架，讨论模拟参数不确定性、敏感性分析及重建结果作为法庭证据的可靠性标准。</t>
+          <t>虚拟解剖（VIRTOPSY）在中国的应用现状与发展综述：可围绕PMCT技术方案的本土化实践，梳理虚拟解剖在创伤分析、疾病诊断、身份识别三大领域的应用价值，讨论PMCT与传统尸检的整合流程与互补关系（各自检出优势与盲区），并结合中国多中心实践、设备配置、读片资质与质量控制等议题提出发展建议。</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>研究基于单一事故案例重建，结论外推性受限；多体模型对软组织损伤与详细骨折形态的预测能力有限；模拟初始条件（车速、碰撞姿态、人体定位）依赖案情信息，存在主观不确定性；摘要未报告对模型参数的敏感性分析及与实验数据的系统验证。</t>
+          <t>综述性质决定其结论依赖既有文献，且PMCT对软组织对比度有限，早期梗死、微小栓塞等病变易漏诊；缺乏大样本与传统尸检的系统对照研究；扫描方案、设备型号与读片人员资质尚未标准化，中国各地区实践差异大，可比性与证据等级受限。</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>This study shows that the multibody method can reconstruct accidents and predict the different injury features and risks between the driver and passengers, which is useful in identifying the driver.</t>
+          <t>Some papers published in recent years in forensic science journals domestic and abroad are reviewed to show the present VIRTOPSY by postmortem multi-slice computed tomography (PMCT) applications in china for forensic pathology.</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>使用MADYMO多体动力学仿真软件对一起真实摩托车-微型货车碰撞事故进行计算机重建，模拟两名骑手的运动学响应及损伤参数（头部、胸部、下肢等），将预测与实际法医鉴定损伤进行对比验证。</t>
+          <t>介绍中国PMCT虚拟解剖的技术方案（扫描参数、后处理技术）、应用范围（创伤、疾病、身份识别），通过案例实例展示应用效果，讨论PMCT与传统尸体解剖的互补整合方式。</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>MADYMO软件重建可有效预测摩托车事故中骑手的损伤风险与特征，通过损伤模式差异可区分驾驶员与乘客身份，为法医交通事故鉴定提供客观依据。</t>
+          <t>基于PMCT的虚拟解剖在中国法医学创伤分析、疾病诊断和身份识别中具有重要价值，可发挥传统解剖的补充作用。</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>将MADYMO多体动力学仿真软件应用于法医学事故重建领域，通过损伤模式差异区分驾驶员与乘客身份。</t>
+          <t>系统介绍了中国法医病理学中PMCT虚拟解剖方法的技术方案和应用实践，总结了中国在该领域的本土化经验。</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>交通事故;损伤重建;MADYMO</t>
+          <t>综述;PMCT;虚拟解剖;VIRTOPSY</t>
         </is>
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>Journal of Forensic and Legal Medicine</t>
+          <t>Forensic Imaging</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>10.1016/j.jflm.2019.04.006</t>
+          <t>10.1016/j.fri.2020.200361</t>
         </is>
       </c>
     </row>
@@ -5094,93 +4975,92 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Biochemical detection of fatal hypothermia and hyperthermia in affected rat hypothalamus tissues by Fourier transform infrared spectroscopy</t>
+          <t>Research Progress on Age Estimation Based on DNA Methylation</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>FTIR光谱生化检测大鼠下丘脑组织中致命性低温和高温</t>
+          <t>基于DNA甲基化的年龄推断研究进展</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>FTIR光谱有潜力成为可靠的方法，用于生化表征致命性低温和高温下丘脑组织，作为死后诊断特征。</t>
+          <t>年龄推断是法医学中的重要任务。DNA甲基化已成为一种有前景的年龄推断分子标志物。本文综述了基于DNA甲基化的年龄推断研究进展，包括DNA甲基化年龄推断的原理、常用甲基化标志物、检测方法和统计模型，并讨论了该领域面临的挑战和未来发展方向。基于DNA甲基化的年龄推断方法已显示出较高准确性，在法医学应用中具有巨大潜力。</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>光谱分析
-致命性损伤</t>
+          <t>年龄推断</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>光谱</t>
+          <t>分子生物学</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>死因</t>
+          <t>身份</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>2019-03</t>
+          <t>2019-10</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>复旦大学基础医学院法医学系/西安交通大学法医学院</t>
+          <t>复旦大学基础医学院法医学系</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>中文核心（JCR未收录）</t>
         </is>
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>法医神经化学与光谱组学在死因鉴定中的应用综述：可围绕下丘脑在体温调节中的核心地位，梳理致命性低温/高温应激下神经生化改变（蛋白质、脂质、神经递质代谢）的FTIR光谱表征，讨论组织光谱与体液光谱（血浆，见num 44）的多层次联合诊断体系、大鼠模型向人体转化的可行性及热应激与死后变化的混杂控制。</t>
+          <t>表观遗传学在法医个体识别中的应用综述：可围绕DNA甲基化年龄时钟的原理（甲基化位点选择、组织特异性），梳理血液、血痕、唾液、精斑等不同体液样本的检测平台（焦磷酸测序、单碱基延伸、二代测序）与统计模型比较，讨论组织类型差异、环境与疾病混杂因素及跨人群（种族）迁移性，形成从标志物发现到标准化应用的完整综述框架。</t>
         </is>
       </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
-          <t>研究基于大鼠模型，下丘脑取材部位准确性及种属差异限制人体外推；死后变化与热应激所致生化改变的混杂难以完全分离；摘要未报告样本量、温度梯度与时间点的实验设计细节；组织匀浆光谱平均化丢失了空间分布信息，缺乏与人体尸检样本的验证。</t>
+          <t>作为综述，其指出现有方法仍面临组织类型差异、环境因素影响与标准化不足等挑战；多数年龄预测模型基于特定人群开发，跨种族应用需校正且精度随年龄增大而下降；摘要未比较不同检测平台的重复性与成本效益，缺乏对模型外部验证现状的系统评价。</t>
         </is>
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
-          <t>FTIR spectroscopy has the potential to become a reliable method for the biochemical characterization of fatal hypothermia and hyperthermia hypothalamus tissues as a postmortem diagnostic feature.</t>
+          <t>Age estimation is of great significance in the fields of criminal investigation and forensic identification. With the rapid development of epigenetics represented by DNA methylation, many age estimation methods based on DNA methylation biomarkers using several biological fluids such as blood, blood stains, saliva, semen stains are developed. This paper summarizes the researches on age estimation based on DNA methylation.</t>
         </is>
       </c>
       <c r="N49" s="3" t="inlineStr">
         <is>
-          <t>动物实验，大鼠下丘脑组织，FTIR光谱+PCA+PLS-DA</t>
+          <t>文献综述：阐述DNA甲基化年龄推断的表观遗传学原理（CpG位点甲基化随年龄变化的规律），梳理常用甲基化标志物基因位点(如ELOVL2、FHL2等)、检测方法（焦磷酸测序、微阵列、靶向甲基化测序等）和统计模型（多元回归、机器学习等），分析当前挑战和未来方向。</t>
         </is>
       </c>
       <c r="O49" s="3" t="inlineStr">
         <is>
-          <t>FTIR光谱可检测下丘脑在低温/高温应激下的特异性生化改变，为法医死因诊断提供新指标。</t>
+          <t>基于DNA甲基化的年龄推断方法准确性较高，在法医学应用中具有巨大潜力，但仍面临组织类型差异、环境因素影响和标准化等挑战。</t>
         </is>
       </c>
       <c r="P49" s="3" t="inlineStr">
         <is>
-          <t>首次使用FTIR光谱分析下丘脑组织生化改变以区分致死性低温/高温</t>
+          <t>全面综述了DNA甲基化年龄推断领域从原理到应用的完整链条，系统梳理了标志物基因位点、检测平台和统计模型的进展。</t>
         </is>
       </c>
       <c r="Q49" s="3" t="inlineStr">
         <is>
-          <t>FTIR;低温;高温;下丘脑</t>
+          <t>法医学杂志;年龄推断;DNA甲基化</t>
         </is>
       </c>
       <c r="R49" s="3" t="inlineStr">
         <is>
-          <t>Bioscience Reports</t>
+          <t>Fa yi xue za zhi</t>
         </is>
       </c>
       <c r="S49" s="3" t="inlineStr">
         <is>
-          <t>10.1042/BSR20181633</t>
+          <t>10.12116/j.issn.1004-5619.2019.05.006</t>
         </is>
       </c>
     </row>
@@ -5190,92 +5070,93 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Analysis of Forensic Sciences Literature in SCIE from 2008 to 2017</t>
+          <t>Postmortem diagnosis of fatal hypothermia/hyperthermia by spectrochemical analysis of plasma</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>2008-2017年SCIE法医学文献分析</t>
+          <t>通过血浆光谱化学分析进行致命性低温/高温的死后诊断</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>目的：分析2008年至2017年间SCIE收录的法医学文献。方法：检索SCIE数据库中2008至2017年收录的法医学出版物，采用文献计量学方法对发表趋势、国家分布、机构、期刊及研究主题进行评价分析。结果：文献发表数量稳步增长，美国和中国为贡献最多的国家，法医DNA分析和法医毒理学为研究热点。结论：该分析提供了SCIE法医学研究的概览，反映了全球研究格局与发展趋势。</t>
+          <t>ATR-FTIR光谱在致命性低温/高温的死后诊断中展示了巨大潜力。溶血和死后效应未削弱分类模型的预测能力。</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>文献分析</t>
+          <t>光谱分析
+死亡诊断</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>综述</t>
+          <t>光谱</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>死因</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>2019-02</t>
+          <t>2019-09</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>复旦大学基础医学院法医学系</t>
+          <t>复旦大学基础医学院法医学系/西安交通大学法医学院</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>中文核心（JCR未收录）</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>法医学全球研究格局与发展趋势综述：可基于SCIE文献计量揭示的国家/机构产出、合作网络与主题变迁（法医DNA、毒理学为热点，影像与AI兴起），梳理2008-2017年法医学研究版图，重点分析中国法医学研究崛起路径（NSFC资助驱动）与学科交叉趋势，为研究生选题、基金申报与学科布局提供宏观参考。</t>
+          <t>光谱法在异常体温死亡（低温/高温）死后诊断中的应用综述：可围绕传统死后生化标志物（儿茶酚胺、酮体、应激激素等）与ATR-FTIR光谱快检的互补关系，梳理血浆光谱特征与体温调节紊乱的对应，讨论溶血与死后效应稳健性验证（该文已证实）对实际案例的意义，并与组织水平光谱（如下丘脑，见num 48）整合为多层次诊断体系。</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>分析仅基于SCIE数据库，偏重英文期刊，中文法医学文献与专著未纳入，存在覆盖偏差；文献计量方法无法反映单篇文献质量与影响力之外的学术价值；主题分类依赖关键词检索，存在分类偏差；数据截至2017年，无法反映近年的AI与组学发展态势。</t>
+          <t>摘要虽报告溶血与死后效应未削弱预测能力，但未给出样本量及死后时间跨度范围，更长时间腐败条件下光谱稳定性未知；低温/高温死亡与脓毒症、甲状腺危象等自然发热疾病的鉴别特异性有待验证；对照组选择（死因构成）直接影响分类性能，缺乏盲法外部验证。</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>OBJECTIVES: To analyze the literature on forensic sciences indexed in SCIE in recent 10 years. From 2008 to 2017, there were 21001 documents on forensic sciences in SCIE. The yearly numbers of publications on forensic sciences are increasing. Focusing on mainland China, there would be more high-quality papers with the steady funding of NSFC.</t>
+          <t>ATR-FTIR spectroscopy demonstrated great potential for postmortem diagnosis of fatal hypothermia/hyperthermia. Hemolysis and postmortem effects did not weaken the prediction ability of classification models.</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>以SCIE数据库为数据源检索2008-2017年法医学文献，运用文献计量学方法对年度发文量、国家/地区分布、主要研究机构、来源期刊及高频关键词进行统计分析。</t>
+          <t>动物实验+人体样本，大鼠模型+人血浆，ATR-FTIR光谱+PLS-DA+SVM</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>2008-2017年法医学SCIE发文量持续增长，美国与中国为领先国家，法医DNA分析和法医毒理学是该时期研究热点。</t>
+          <t>ATR-FTIR光谱可从血浆中鉴定致命性低温和高温，且不受溶血和死后变化影响，具有法医学实用价值。</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>系统分析了2008-2017年SCIE法医学文献的研究格局，揭示全球法医学研究产出趋势和热点主题分布。</t>
+          <t>首次使用血浆ATR-FTIR光谱区分致命性低温/高温死亡，并验证死后变化的稳健性</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>法医学杂志;文献计量学;SCIE</t>
+          <t>FTIR;低温;高温;血浆</t>
         </is>
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>Fa yi xue za zhi</t>
+          <t>Forensic Science, Medicine, and Pathology</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>10.12116/j.issn.1004-5619.2019.01.006</t>
+          <t>10.1007/s12024-019-00111-8</t>
         </is>
       </c>
     </row>
@@ -5285,92 +5166,93 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Current Research and Prospects on Postmortem Interval Estimation</t>
+          <t>Digital whole-slide image analysis for automated diatom test in forensic cases of drowning using a convolutional neural network algorithm</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>死后间隔时间推断的现状与展望</t>
+          <t>使用CNN算法的数字全切片图像分析用于法医溺死案例自动硅藻检测</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>死后间隔时间(PMI)推断是法医病理学中基本且具有挑战性的任务。本文综述了PMI推断的当前研究现状与前景，讨论了包括尸体降温、生化标志物、分子生物学技术和昆虫学在内的多种方法，分析了每种方法的优缺点，并提出了多方法联合应用及人工智能等未来发展方向。PMI推断仍是需要持续研究的热点课题。</t>
+          <t>基于AI的系统结合经典化学消解法自动识别硅藻。为未来智能硅藻检验铺平道路。</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>死后间隔时间</t>
+          <t>算法、图像分析
+硅藻与溺死诊断</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>综述</t>
+          <t>AI/机器学习</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>PMI</t>
+          <t>死因</t>
         </is>
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>2018-10</t>
+          <t>2019-09</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>复旦大学基础医学院法医学系</t>
+          <t>复旦大学基础医学院法医学系/司法鉴定科学研究院/西安交通大学</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>中文核心（JCR未收录）</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>死亡时间推断多方法融合综述：可沿'传统方法（尸温、尸僵、生化）→分子方法（RNA、代谢物、microRNA）→光谱与AI方法'的技术演进主线，梳理各类方法的适用窗口、精度与局限，重点讨论多方法联合策略（加权融合、贝叶斯框架）及人工智能算法在PMI建模中的应用前景，为芯片实验室（num 28）、FTIR皮肤光谱（num 39）等实证研究提供综述框架。</t>
+          <t>数字病理与全切片图像分析（WSI）在法医学中的应用综述：可从硅藻全切片自动检测这一开创性工作切入，梳理WSI扫描-拼接-标注-训练的AI流水线、CNN架构与训练策略（数据增强、弱监督），讨论与传统化学消化法结合的自动化检验体系，并延伸至WSI-AI在心肌梗死、肺损伤等法医组织病理诊断中的扩展应用。</t>
         </is>
       </c>
       <c r="L51" s="3" t="inlineStr">
         <is>
-          <t>作为综述，其涵盖的方法多为实验研究，缺乏人体大样本前瞻性验证；环境因素（温度、湿度）对多数方法的影响未被系统量化；多方法融合尚缺乏统一的数据采集标准与验证协议，不同研究间结果可比性差，综述难以给出统一的推荐方案。</t>
+          <t>作为该方向开创性工作，训练与验证样本量有限，硅藻类别多样性不足；全切片扫描耗时且数据存储量大，对计算资源要求高；不同制片工艺与扫描仪间的图像域差异可能导致模型性能漂移；检出率与人工鉴定对比受金标准判定主观性影响，缺乏前瞻性外部验证。</t>
         </is>
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
-          <t>The researches on postmortem interval (PMI) estimation are very important and meaningful in forensic science. The present review summarizes a series of methods used for PMI estimation, and then gives an outlook for the application of artificial intelligence algorithms in this field.</t>
+          <t>An AI-based system to automatically identify diatoms in conjunction with a classical chemical digestion approach. Paves the way for future intelligent diatom examinations.</t>
         </is>
       </c>
       <c r="N51" s="3" t="inlineStr">
         <is>
-          <t>综述性文献，系统总结PMI推断的多种方法：尸体温度变化法、生化标志物检测法、分子生物学技术（核酸与蛋白质降解规律）、法医昆虫学方法，比较各方法原理、适用范围和局限性，提出未来发展方向。</t>
+          <t>实验验证，全切片数字图像，CNN算法+传统化学消解法</t>
         </is>
       </c>
       <c r="O51" s="3" t="inlineStr">
         <is>
-          <t>单一PMI推断方法各有局限，未来趋势是多方法联合应用并借助人工智能等新技术提高推断准确性，PMI推断仍是法医病理学亟需持续研究的核心课题。</t>
+          <t>CNN可在全切片图像中自动识别硅藻，准确率与人工鉴定相当，但效率大幅提高。</t>
         </is>
       </c>
       <c r="P51" s="3" t="inlineStr">
         <is>
-          <t>提出将多方法联合应用与人工智能技术引入PMI推断，为该领域研究指明了未来发展方向。</t>
+          <t>首次将CNN应用于全切片硅藻数字图像自动识别，是该领域的开创性工作</t>
         </is>
       </c>
       <c r="Q51" s="3" t="inlineStr">
         <is>
-          <t>法医学杂志;死亡时间;人工智能;展望</t>
+          <t>硅藻;CNN;深度学习;溺死诊断</t>
         </is>
       </c>
       <c r="R51" s="3" t="inlineStr">
         <is>
-          <t>Fa yi xue za zhi</t>
+          <t>Forensic Science International</t>
         </is>
       </c>
       <c r="S51" s="3" t="inlineStr">
         <is>
-          <t>10.12116/j.issn.1004-5619.2018.05.002</t>
+          <t>10.1016/j.forsciint.2019.109922</t>
         </is>
       </c>
     </row>
@@ -5380,93 +5262,93 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Identification of Pulmonary Edema in Forensic Autopsy Cases of Sudden Cardiac Death Using Fourier Transform Infrared Microspectroscopy: A Pilot Study</t>
+          <t>Bibliometric Analysis of Medical Malpractice Literature in Legal Medicine from 1975 to 2018: Web of Science Review</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>使用FTIR显微光谱鉴定心源性猝死法医尸检案例中的肺水肿：初步研究</t>
+          <t>1975-2018年法医学医疗纠纷文献的文献计量学分析：Web of Science综述</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>FTIR显微光谱结合化学计量学有潜力成为SCD死后诊断的有效辅助手段。</t>
+          <t>目的：分析1975年至2018年法医学领域医疗纠纷文献的全球研究趋势。方法：使用Web of Science数据库进行文献计量学分析，检索法医学中与医疗纠纷相关的出版物，按年份、国家、期刊、作者和关键词进行分析。结果：共鉴定出若干相关出版物，发表数量呈逐年增长趋势，美国是最高产国家，通过关键词分析识别出研究热点。结论：该文献计量学分析全面展示了法医学医疗纠纷研究概况，有助于了解研究趋势和热点主题。</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>光谱分析
-心源性猝死&amp;肺水肿</t>
+          <t>医疗纠纷
+文献计量学</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>光谱</t>
+          <t>综述</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>死因</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>2018-02</t>
+          <t>2019-08</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>复旦大学基础医学院法医学系/西安交通大学法医学院</t>
+          <t>复旦大学基础医学院法医学系</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>可牵引一篇『振动光谱（FTIR/拉曼）结合化学计量学在法医病理学死后诊断中的应用』系统综述：以肺水肿、心肌缺血等死因为切入点，按『样本制备—光谱采集—预处理—化学计量学分类建模—与组织学金标准对照』五步框架组织文献，比较不同器官/病变的光谱标志物（脂质、蛋白质二级结构改变）及其诊断效能。亦可在该综述中专辟章节讨论光谱法区分心源性肺水肿与其他死因（溺死、心衰）肺水肿的判别潜力。</t>
+          <t>法医学医疗纠纷鉴定研究综述：可基于文献计量揭示的研究热点（误诊、手术并发症、死因争议等）与增长趋势，围绕医疗过错鉴定的医学-法律交叉框架，比较不同国家（美国、中国等）鉴定模式与制度差异，梳理法医学鉴定在医疗纠纷解决中的角色演变、证据标准与质量控制，形成学科交叉型综述。</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>研究性质为初步研究（pilot study），样本量有限，统计功效不足；FTIR对组织含水状态敏感，死后自溶、腐败及固定方式对光谱的影响未系统控制。肺水肿可见于多种死因（心衰、溺死、窒息等），该方法的死因特异性尚需更大样本和多死因对照验证，且未报告与传统组织学诊断的敏感度/特异度定量比较。</t>
+          <t>分析仅基于Web of Science单一数据库，存在英文期刊偏好，中文及非英文法医学文献大量遗漏，代表性受限；检索到的379篇文献规模本身反映该领域研究不足，计量分析无法评价单篇研究质量；关键词与引用网络分析存在主观性，且数据截止2018年，时效性下降。</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>FTIR microspectroscopy in combination with chemometrics has the potential to be an effective aid for postmortem diagnosis of SCD.</t>
+          <t>OBJECTIVE: To determine the history of malpractice literature using forensic science based on bibliometric and graph theory. 379 papers and 3160 citing articles were retrieved. This bibliometric analysis indicated that studying the field of medical malpractice was poor during 1975-2018.</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>人尸检肺组织样本(n=)，FTIR显微光谱+主成分分析(PCA)+偏最小二乘判别分析(PLS-DA)</t>
+          <t>以Web of Science为数据源检索1975-2018年法医学医疗纠纷相关文献，按发表年份、国家/地区、来源期刊、高产作者和关键词进行文献计量学分析，通过关键词共现分析识别研究热点。</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>FTIR显微光谱可准确鉴定SCD尸检案例中的肺水肿，为传统组织学提供客观、定量的辅助诊断方法。</t>
+          <t>法医学医疗纠纷研究文献呈增长趋势美国领先，该文献计量分析为该领域研究趋势和热点提供了全面参考。</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>首次将FTIR显微光谱应用于法医SCD肺水肿鉴定</t>
+          <t>首次对1975-2018年法医学领域医疗纠纷文献进行系统性文献计量分析，揭示了该领域的全球研究趋势和热点主题演变。</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
         <is>
-          <t>FTIR;肺水肿;心源性猝死</t>
+          <t>综述;文献计量学;医疗纠纷</t>
         </is>
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>Analytical Chemistry</t>
+          <t>Journal of Forensic and Legal Medicine</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>10.1021/acs.analchem.7b04642</t>
+          <t>10.1016/j.jflm.2019.07.002</t>
         </is>
       </c>
     </row>
@@ -5476,37 +5358,38 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Research Progress of MALDI-TOF-IMS in Biomedicine and Its Application Prospect in Forensic Sciences</t>
+          <t>Prediction of injury risks and features among scooter riders through MADYMO reconstruction of a scooter-microvan accident: Identifying the driver and passengers</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>MALDI-TOF-IMS在生物医学中的研究进展及其在法医学中的应用前景</t>
+          <t>MADYMO重建摩托车事故预测骑手损伤风险与特征：驾驶员与乘客识别</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>基质辅助激光解吸/电离飞行时间成像质谱(MALDI-TOF-IMS)是一种强大的分子成像技术。本文综述了MALDI-TOF-IMS在生物医学中的研究进展及其在法医学中的应用前景，介绍了其原理、技术特点和优势，讨论了其在生物标志物发现、药物分布分析和组织表征中的应用，并提出了其在法医病理学、毒理学及微量物证分析中的潜在应用。MALDI-TOF-IMS在法医分子成像方面具有广阔前景。</t>
+          <t>目的：通过MADYMO软件重建一起摩托车-微型货车事故，预测摩托车骑手的损伤风险与特征，并识别驾驶员与乘客。方法：使用MADYMO软件重建真实事故，模拟两名骑手的运动学和损伤参数，并将模拟结果与实际损伤情况进行比较。结果：模拟结果显示驾驶员与乘客具有不同的损伤模式，预测损伤与实际损伤一致。结论：MADYMO事故重建可有效预测损伤风险，有助于识别摩托车事故中的驾驶员与乘客身份。</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>MALDI-TOF质谱成像</t>
+          <t>事故重建
+MADYMO</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>质谱</t>
+          <t>生物力学</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>损伤机制</t>
+          <t>身份</t>
         </is>
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>2017-10</t>
+          <t>2019-07</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr">
@@ -5516,52 +5399,52 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>中文核心（JCR未收录）</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>该文本身即综述，可进一步牵引一篇『分子成像质谱技术（MALDI-IMS、DESI、SIMS）在法医学中的应用前景』的比较性综述：按技术原理（电离方式、空间分辨率、是否标记）对比各质谱成像平台的优劣，并围绕法医病理（心肌梗死、脑损伤分子标志物）、法医毒理（体内药物/毒物分布）与微量物证三大应用域组织文献，提出『原位分子病理学』的概念框架与标准化流程建议。</t>
+          <t>多体动力学在交通事故法医重建中的应用综述：可围绕MADYMO等多体模型与有限元模型的方法学比较（计算效率vs细节分辨率），梳理事故重建流程（初始条件设定、运动学/损伤参数输出）、损伤特征与驾驶员/乘客身份识别的关联框架，讨论模拟参数不确定性、敏感性分析及重建结果作为法庭证据的可靠性标准。</t>
         </is>
       </c>
       <c r="L53" s="3" t="inlineStr">
         <is>
-          <t>属叙述性综述，未报告系统检索策略、纳入/排除标准与证据分级，存在选择偏倚；对MALDI-TOF-IMS的法医学应用多为前景展望，实证案例与量化数据较少。对空间分辨率、定量能力、样本前处理等关键技术瓶颈的讨论有限，亦未与其他质谱成像技术（DESI、SIMS）做系统优劣比较。</t>
+          <t>研究基于单一事故案例重建，结论外推性受限；多体模型对软组织损伤与详细骨折形态的预测能力有限；模拟初始条件（车速、碰撞姿态、人体定位）依赖案情信息，存在主观不确定性；摘要未报告对模型参数的敏感性分析及与实验数据的系统验证。</t>
         </is>
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
-          <t>Matrix-assisted laser desorption/ionization time-of-flight imaging mass spectrometry (MALDI-TOF-IMS) can analysis unknown compounds in sections and obtain molecule imaging by scanning biological tissue sections, which has become a powerful tool for the research of biomarker, lipid distribution and drug metabolism, etc. This article reviews the application of this technique in protein identification, clinical application, drug discovery, lipid research and brain injury.</t>
+          <t>This study shows that the multibody method can reconstruct accidents and predict the different injury features and risks between the driver and passengers, which is useful in identifying the driver.</t>
         </is>
       </c>
       <c r="N53" s="3" t="inlineStr">
         <is>
-          <t>文献综述，系统介绍MALDI-TOF-IMS技术成像原理和工作流程，总结其在生物医学领域（生物标志物发现、药物组织分布、组织分子表征）的研究进展，前瞻性探讨该技术在法医学各分支学科中的潜在应用。</t>
+          <t>使用MADYMO多体动力学仿真软件对一起真实摩托车-微型货车碰撞事故进行计算机重建，模拟两名骑手的运动学响应及损伤参数（头部、胸部、下肢等），将预测与实际法医鉴定损伤进行对比验证。</t>
         </is>
       </c>
       <c r="O53" s="3" t="inlineStr">
         <is>
-          <t>MALDI-TOF-IMS作为无需标记的原位分子成像技术，在法医病理学、毒理学和微量物证分析等领域具有巨大应用潜力，有望成为法医分子成像的重要工具。</t>
+          <t>MADYMO软件重建可有效预测摩托车事故中骑手的损伤风险与特征，通过损伤模式差异可区分驾驶员与乘客身份，为法医交通事故鉴定提供客观依据。</t>
         </is>
       </c>
       <c r="P53" s="3" t="inlineStr">
         <is>
-          <t>首次系统性将MALDI-TOF-IMS这一前沿分子成像技术引入法医学领域进行应用前景分析，架起了生物医学先进技术与法医学需求之间的桥梁。</t>
+          <t>将MADYMO多体动力学仿真软件应用于法医学事故重建领域，通过损伤模式差异区分驾驶员与乘客身份。</t>
         </is>
       </c>
       <c r="Q53" s="3" t="inlineStr">
         <is>
-          <t>法医学杂志;生物医学;MALDI-TOF-IMS</t>
+          <t>交通事故;损伤重建;MADYMO</t>
         </is>
       </c>
       <c r="R53" s="3" t="inlineStr">
         <is>
-          <t>Fa yi xue za zhi</t>
+          <t>Journal of Forensic and Legal Medicine</t>
         </is>
       </c>
       <c r="S53" s="3" t="inlineStr">
         <is>
-          <t>10.3969/j.issn.1004-5619.2017.05.016</t>
+          <t>10.1016/j.jflm.2019.04.006</t>
         </is>
       </c>
     </row>
@@ -5571,23 +5454,23 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Application of FTIR spectroscopy for traumatic axonal injury: a possible tool for estimating injury interval</t>
+          <t>Biochemical detection of fatal hypothermia and hyperthermia in affected rat hypothalamus tissues by Fourier transform infrared spectroscopy</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>FTIR光谱在外伤性轴索损伤中的应用：推断损伤时间的可能工具</t>
+          <t>FTIR光谱生化检测大鼠下丘脑组织中致命性低温和高温</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>基于FTIR的PLS算法作为推断外伤性轴索损伤（TAI）损伤时间的客观工具，在法医学和神经学中具有应用价值。</t>
+          <t>FTIR光谱有潜力成为可靠的方法，用于生化表征致命性低温和高温下丘脑组织，作为死后诊断特征。</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
           <t>光谱分析
-损伤时间推断</t>
+致命性损伤</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -5597,12 +5480,12 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>损伤机制</t>
+          <t>死因</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>2017-08</t>
+          <t>2019-03</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
@@ -5617,37 +5500,37 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>可牵引一篇『振动光谱学推断神经损伤时间的研究进展』综述：聚焦外伤性轴索损伤、脑挫伤、缺血缺氧性脑损伤中轴突膜脂质与蛋白质二级结构的时相性生化改变，按『损伤后不同时间点的光谱特征—PLS/机器学习回归—损伤时间预测方程』框架组织，并延伸讨论光谱学方法在损伤时间与死后间隔时间（PMI）双重时间推断中的统一应用前景。</t>
+          <t>法医神经化学与光谱组学在死因鉴定中的应用综述：可围绕下丘脑在体温调节中的核心地位，梳理致命性低温/高温应激下神经生化改变（蛋白质、脂质、神经递质代谢）的FTIR光谱表征，讨论组织光谱与体液光谱（血浆，见num 44）的多层次联合诊断体系、大鼠模型向人体转化的可行性及热应激与死后变化的混杂控制。</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>基于实验模型（TAI模型）而非人体组织，动物与人类轴索损伤的分子时相进程存在物种差异，向人体外推需谨慎。PLS预测模型的精度受训练集损伤时间点覆盖密度、损伤严重度分层及个体间变异影响，样本量有限；FTIR对组织含水、固定与切片厚度敏感，跨实验室标准化问题未解决，模型的外部验证亦不足。</t>
+          <t>研究基于大鼠模型，下丘脑取材部位准确性及种属差异限制人体外推；死后变化与热应激所致生化改变的混杂难以完全分离；摘要未报告样本量、温度梯度与时间点的实验设计细节；组织匀浆光谱平均化丢失了空间分布信息，缺乏与人体尸检样本的验证。</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>FTIR-based PLS algorithm as an objective tool for estimating injury intervals of traumatic axonal injury (TAI) in forensic science and neurology.</t>
+          <t>FTIR spectroscopy has the potential to become a reliable method for the biochemical characterization of fatal hypothermia and hyperthermia hypothalamus tissues as a postmortem diagnostic feature.</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>动物实验（大鼠TAI模型），脑组织切片，FTIR光谱+PLS回归</t>
+          <t>动物实验，大鼠下丘脑组织，FTIR光谱+PCA+PLS-DA</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>FTIR光谱结合PLS回归可准确推断TAI损伤时间，为法医学神经损伤时间推断提供新方法。</t>
+          <t>FTIR光谱可检测下丘脑在低温/高温应激下的特异性生化改变，为法医死因诊断提供新指标。</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>首次将FTIR光谱用于外伤性轴索损伤的时间推断</t>
+          <t>首次使用FTIR光谱分析下丘脑组织生化改变以区分致死性低温/高温</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
         <is>
-          <t>FTIR;外伤性轴索损伤;损伤时间</t>
+          <t>FTIR;低温;高温;下丘脑</t>
         </is>
       </c>
       <c r="R54" s="2" t="inlineStr">
@@ -5657,7 +5540,7 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>10.1042/BSR20170720</t>
+          <t>10.1042/BSR20181633</t>
         </is>
       </c>
     </row>
@@ -5667,38 +5550,37 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Diagnosis of coronary artery disease using targeted post-mortem computed tomography coronary angiography: a case report</t>
+          <t>Analysis of Forensic Sciences Literature in SCIE from 2008 to 2017</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>靶向死后CT冠状动脉造影诊断冠心病：案例报告</t>
+          <t>2008-2017年SCIE法医学文献分析</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>目的：展示靶向死后CT冠状动脉造影在冠心病诊断中的应用。方法：对一例猝死案例进行靶向死后CT冠状动脉造影检查，通过靶向注射对比剂实现冠状动脉可视化，并将CT结果与尸检及组织病理学检查进行对比。结果：靶向死后CT冠状动脉造影清晰显示了冠状动脉狭窄，结果与尸检及组织病理学检查一致。结论：靶向死后CT冠状动脉造影是法医学实践中诊断冠心病的有价值工具，尤其适用于微创检查。</t>
+          <t>目的：分析2008年至2017年间SCIE收录的法医学文献。方法：检索SCIE数据库中2008至2017年收录的法医学出版物，采用文献计量学方法对发表趋势、国家分布、机构、期刊及研究主题进行评价分析。结果：文献发表数量稳步增长，美国和中国为贡献最多的国家，法医DNA分析和法医毒理学为研究热点。结论：该分析提供了SCIE法医学研究的概览，反映了全球研究格局与发展趋势。</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>死后影像学
-冠心病</t>
+          <t>文献分析</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>影像</t>
+          <t>综述</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>死因</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>2017-01</t>
+          <t>2019-02</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
@@ -5708,52 +5590,52 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>中文核心（JCR未收录）</t>
         </is>
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>可牵引一篇『死后CT血管造影（PMCTA）在心血管源性猝死死因鉴定中的应用』综述：对比全身灌注、靶向注射、左心室穿刺等不同PMCTA技术的操作流程、显影质量与适用场景，聚焦冠状动脉狭窄程度评估、斑块负荷与钙化评分等影像学征象，并以『影像所见—传统尸检—组织病理学金标准』三对照验证模式组织证据，讨论微创影像学替代传统尸检的可行性边界。</t>
+          <t>法医学全球研究格局与发展趋势综述：可基于SCIE文献计量揭示的国家/机构产出、合作网络与主题变迁（法医DNA、毒理学为热点，影像与AI兴起），梳理2008-2017年法医学研究版图，重点分析中国法医学研究崛起路径（NSFC资助驱动）与学科交叉趋势，为研究生选题、基金申报与学科布局提供宏观参考。</t>
         </is>
       </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t>为单一案例报告，证据等级低，结论外推性有限；靶向注射依赖操作者经验，对比剂注射压力、剂量与浓度缺乏标准化方案。死后血管塌陷、痉挛及气体伪影可能使CTA所示狭窄程度与解剖所见存在偏差，且该方法难以评估弥漫性小血管病变与心肌缺血的功能学意义，缺乏多中心案例的系统性验证。</t>
+          <t>分析仅基于SCIE数据库，偏重英文期刊，中文法医学文献与专著未纳入，存在覆盖偏差；文献计量方法无法反映单篇文献质量与影响力之外的学术价值；主题分类依赖关键词检索，存在分类偏差；数据截至2017年，无法反映近年的AI与组学发展态势。</t>
         </is>
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
-          <t>Targeted post-mortem computed tomography (PMCT) combined with coronary angiography has the potential to play a significant role in the investigation of sudden cardiac death. The authors utilized a targeted PMCT coronary angiography in a case involving a 53-year-old man who died from acute myocardial ischemia. Targeted PMCTA can visualize the arteries and estimate the degree of principal pathological changes.</t>
+          <t>OBJECTIVES: To analyze the literature on forensic sciences indexed in SCIE in recent 10 years. From 2008 to 2017, there were 21001 documents on forensic sciences in SCIE. The yearly numbers of publications on forensic sciences are increasing. Focusing on mainland China, there would be more high-quality papers with the steady funding of NSFC.</t>
         </is>
       </c>
       <c r="N55" s="3" t="inlineStr">
         <is>
-          <t>对一例可疑心源性猝死案例实施靶向死后CT冠状动脉造影，通过靶向注射碘对比剂后行CT扫描，观察冠脉狭窄程度与分布，将影像学结果与传统尸检及组织病理学检查结果对照验证。</t>
+          <t>以SCIE数据库为数据源检索2008-2017年法医学文献，运用文献计量学方法对年度发文量、国家/地区分布、主要研究机构、来源期刊及高频关键词进行统计分析。</t>
         </is>
       </c>
       <c r="O55" s="3" t="inlineStr">
         <is>
-          <t>靶向死后CT冠状动脉造影可清晰显示冠状动脉病变，与传统尸检及组织病理学高度一致，为法医学冠心病微创诊断提供了可靠手段。</t>
+          <t>2008-2017年法医学SCIE发文量持续增长，美国与中国为领先国家，法医DNA分析和法医毒理学是该时期研究热点。</t>
         </is>
       </c>
       <c r="P55" s="3" t="inlineStr">
         <is>
-          <t>将靶向死后CT冠状动脉造影技术应用于法医学冠心病诊断，实现了微创化尸体血管检查，为拒绝传统尸检的案例提供替代性诊断方案。</t>
+          <t>系统分析了2008-2017年SCIE法医学文献的研究格局，揭示全球法医学研究产出趋势和热点主题分布。</t>
         </is>
       </c>
       <c r="Q55" s="3" t="inlineStr">
         <is>
-          <t>PMCTA;案例报告;冠心病</t>
+          <t>法医学杂志;文献计量学;SCIE</t>
         </is>
       </c>
       <c r="R55" s="3" t="inlineStr">
         <is>
-          <t>Forensic Sciences Research</t>
+          <t>Fa yi xue za zhi</t>
         </is>
       </c>
       <c r="S55" s="3" t="inlineStr">
         <is>
-          <t>10.1080/20961790.2017.1328795</t>
+          <t>10.12116/j.issn.1004-5619.2019.01.006</t>
         </is>
       </c>
     </row>
@@ -5763,38 +5645,37 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Post-mortem computed tomography angiography using left ventricle cardiac puncture: A whole-body, angiographic approach</t>
+          <t>Current Research and Prospects on Postmortem Interval Estimation</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>左心室心脏穿刺死后CT血管造影：全身血管造影方法</t>
+          <t>死后间隔时间推断的现状与展望</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>目的：介绍一种通过左心室心脏穿刺实现全身死后CT血管造影的方法。方法：实施左心室心脏穿刺并注射对比剂，随后进行全身CT扫描，在多例案例中对血管造影质量及诊断价值进行评估。结果：左心室心脏穿刺成功实现了全身血管造影，从头至脚的血管系统获得了良好显影，并识别出多种病理状况。结论：经左心室心脏穿刺的死后CT血管造影是一种适用于法医学调查的有效全身血管造影方法。</t>
+          <t>死后间隔时间(PMI)推断是法医病理学中基本且具有挑战性的任务。本文综述了PMI推断的当前研究现状与前景，讨论了包括尸体降温、生化标志物、分子生物学技术和昆虫学在内的多种方法，分析了每种方法的优缺点，并提出了多方法联合应用及人工智能等未来发展方向。PMI推断仍是需要持续研究的热点课题。</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>死后影像学
-全身血管造影</t>
+          <t>死后间隔时间</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>影像</t>
+          <t>综述</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>死因</t>
+          <t>PMI</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>2017-01</t>
+          <t>2018-10</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -5804,52 +5685,52 @@
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>中文核心（JCR未收录）</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>可牵引一篇『死后血管造影技术演进与微创化趋势』的综述：按技术代际梳理从依赖心肺转流机的全身灌注PMCTA，到手动/泵注的简化全身造影、靶向局部造影与心脏穿刺入路的演变，以显影质量、操作时间、成本、设备依赖性与适用中心条件为比较维度，提出面向基层法医机构的『低门槛死后血管成像方案』选择框架。</t>
+          <t>死亡时间推断多方法融合综述：可沿'传统方法（尸温、尸僵、生化）→分子方法（RNA、代谢物、microRNA）→光谱与AI方法'的技术演进主线，梳理各类方法的适用窗口、精度与局限，重点讨论多方法联合策略（加权融合、贝叶斯框架）及人工智能算法在PMI建模中的应用前景，为芯片实验室（num 28）、FTIR皮肤光谱（num 39）等实证研究提供综述框架。</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>为方法学描述加多例应用，未报告各例的量化评估指标与统计比较，显影质量判断偏主观；左心室穿刺单点注射可能存在部分血管床显影不均、对比剂残留心腔产生伪影等问题，操作失败率与对比剂外渗等并发症未详细说明。与完整尸检/组织病理学的系统对照不足，血管病变检出的敏感度与特异度尚不明确。</t>
+          <t>作为综述，其涵盖的方法多为实验研究，缺乏人体大样本前瞻性验证；环境因素（温度、湿度）对多数方法的影响未被系统量化；多方法融合尚缺乏统一的数据采集标准与验证协议，不同研究间结果可比性差，综述难以给出统一的推荐方案。</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>Compared with other existing PMCTA methods for examination of vascular injuries and diseases, this technique involves simple procedures, is less time consuming, has lower associated costs, does not require specialized equipment, provides adequate imaging quality, and is suitable for centres not equipped with cardiopulmonary bypass machines or other specialized equipment.</t>
+          <t>The researches on postmortem interval (PMI) estimation are very important and meaningful in forensic science. The present review summarizes a series of methods used for PMI estimation, and then gives an outlook for the application of artificial intelligence algorithms in this field.</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>采用左心室心脏穿刺途径注入碘对比剂，随后行全身多层螺旋CT扫描，在多个法医案例中评估血管显影质量（动脉、静脉系统及微血管充盈程度），分析其对各类病变的诊断效能。</t>
+          <t>综述性文献，系统总结PMI推断的多种方法：尸体温度变化法、生化标志物检测法、分子生物学技术（核酸与蛋白质降解规律）、法医昆虫学方法，比较各方法原理、适用范围和局限性，提出未来发展方向。</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>经左心室心脏穿刺的全身死后CT血管造影操作简便，可实现从头到下肢的血管系统全面显影，有助于发现血管及实质器官病变，是适用于法医学常规尸体检查的有效影像学手段。</t>
+          <t>单一PMI推断方法各有局限，未来趋势是多方法联合应用并借助人工智能等新技术提高推断准确性，PMI推断仍是法医病理学亟需持续研究的核心课题。</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>首创通过左心室穿刺单次注射实现全身死后CT血管造影的方法，突破了传统多血管插管的繁琐操作，为死后血管系统的全面评估提供了简便高效的解决方案。</t>
+          <t>提出将多方法联合应用与人工智能技术引入PMI推断，为该领域研究指明了未来发展方向。</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
         <is>
-          <t>全心造影;左心室穿刺;PMCTA</t>
+          <t>法医学杂志;死亡时间;人工智能;展望</t>
         </is>
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>PLoS ONE</t>
+          <t>Fa yi xue za zhi</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>10.1371/journal.pone.0183408</t>
+          <t>10.12116/j.issn.1004-5619.2018.05.002</t>
         </is>
       </c>
     </row>
@@ -5859,92 +5740,93 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Identifying Diffuse Axonal Injury by Matrix-Assisted Laser Desorption/Ionization Time-of-Flight: A New Method for Pathological Observation</t>
+          <t>Identification of Pulmonary Edema in Forensic Autopsy Cases of Sudden Cardiac Death Using Fourier Transform Infrared Microspectroscopy: A Pilot Study</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>MALDI-TOF质谱成像鉴定弥漫性轴索损伤：病理观察新方法</t>
+          <t>使用FTIR显微光谱鉴定心源性猝死法医尸检案例中的肺水肿：初步研究</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>目的：探索MALDI-TOF质谱成像在弥漫性轴索损伤(DAI)鉴定中的应用。方法：利用MALDI-TOF质谱成像对DAI病例和对照组的脑组织样本进行分析，比较分子谱差异，并鉴定DAI的特异性生物标志物。结果：MALDI-TOF成像显示DAI脑组织与正常组织具有明显不同的分子谱，鉴定出可区分DAI与对照的特异性脂质和蛋白质标志物。结论：MALDI-TOF质谱成像是一种新型且有效的DAI病理观察方法，可提供分子水平的诊断信息，作为传统组织病理学的有力补充。</t>
+          <t>FTIR显微光谱结合化学计量学有潜力成为SCD死后诊断的有效辅助手段。</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>质谱成像</t>
+          <t>光谱分析
+心源性猝死&amp;肺水肿</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>质谱</t>
+          <t>光谱</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>损伤机制</t>
+          <t>死因</t>
         </is>
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>2016-12</t>
+          <t>2018-02</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>复旦大学基础医学院法医学系</t>
+          <t>复旦大学基础医学院法医学系/西安交通大学法医学院</t>
         </is>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>可牵引一篇『质谱成像（MSI）在脑损伤法医病理学中的应用』综述：围绕DAI、脑挫伤、缺血缺氧性脑病的脂质与蛋白质分子标志物鉴定，按『样本制备—MSI采集—分子谱差异分析—监督分类模型（神经网络等）—与传统组织病理学互补』框架组织文献，并可前瞻性讨论分子成像对损伤时间推断与损伤机制认定的增量价值。</t>
+          <t>可牵引一篇『振动光谱（FTIR/拉曼）结合化学计量学在法医病理学死后诊断中的应用』系统综述：以肺水肿、心肌缺血等死因为切入点，按『样本制备—光谱采集—预处理—化学计量学分类建模—与组织学金标准对照』五步框架组织文献，比较不同器官/病变的光谱标志物（脂质、蛋白质二级结构改变）及其诊断效能。亦可在该综述中专辟章节讨论光谱法区分心源性肺水肿与其他死因（溺死、心衰）肺水肿的判别潜力。</t>
         </is>
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>样本量小（共15张大鼠脑干切片，10例DAI对5例对照），统计功效有限；监督神经网络在小样本上易过拟合，缺乏独立测试集与外部验证。仅分析脑干单一区域，未覆盖DAI好发的胼胝体与脑白质；大鼠与人类DAI分子谱存在物种差异，且死后间隔对脂质降解的影响未讨论，向人体外推证据不足。</t>
+          <t>研究性质为初步研究（pilot study），样本量有限，统计功效不足；FTIR对组织含水状态敏感，死后自溶、腐败及固定方式对光谱的影响未系统控制。肺水肿可见于多种死因（心衰、溺死、窒息等），该方法的死因特异性尚需更大样本和多死因对照验证，且未报告与传统组织学诊断的敏感度/特异度定量比较。</t>
         </is>
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
-          <t>PURPOSE: The aim of this study was to identify the diffuse axonal injury (DAI) of rat through screening out differentially expressed proteins which may represent potential biomarkers by MALDI-TOF IMS. METHODS: A total of 15 brainstem sections of rats (10 with and 5 without DAI) were conducted by MALDI-TOF IMS. RESULTS: Applying a Supervised Neural Network algorithm, we were able to distinguish between normal and DAI regions with an overall cross-validation, a sensitivity and specificity of 95.67%, 99.34%, and 92.01%, respectively. CONCLUSIONS: This study reveals the value of MALDI-TOF IMS to classify between normal and injured tissues and identify candidates for DAI biomarkers.</t>
+          <t>FTIR microspectroscopy in combination with chemometrics has the potential to be an effective aid for postmortem diagnosis of SCD.</t>
         </is>
       </c>
       <c r="N57" s="3" t="inlineStr">
         <is>
-          <t>收集DAI案例和对照组脑组织样本，利用MALDI-TOF质谱成像进行原位分子扫描，分析质谱峰差异筛选DAI特异性脂质和蛋白质分子标志物，将分子成像结果与传统HE/银染等进行对比。</t>
+          <t>人尸检肺组织样本(n=)，FTIR显微光谱+主成分分析(PCA)+偏最小二乘判别分析(PLS-DA)</t>
         </is>
       </c>
       <c r="O57" s="3" t="inlineStr">
         <is>
-          <t>MALDI-TOF质谱成像能从分子水平揭示DAI的组织病理变化，鉴定出的特异性分子标志物可有效区分DAI与正常组织，为DAI诊断提供超越传统组织病理学的分子维度信息。</t>
+          <t>FTIR显微光谱可准确鉴定SCD尸检案例中的肺水肿，为传统组织学提供客观、定量的辅助诊断方法。</t>
         </is>
       </c>
       <c r="P57" s="3" t="inlineStr">
         <is>
-          <t>首次将MALDI-TOF质谱成像技术应用于DAI的法医病理学诊断，发现可供鉴别DAI的脂质和蛋白质分子标志物，开辟了分子病理学观察新途径。</t>
+          <t>首次将FTIR显微光谱应用于法医SCD肺水肿鉴定</t>
         </is>
       </c>
       <c r="Q57" s="3" t="inlineStr">
         <is>
-          <t>弥漫性轴索损伤;生物标志物;MALDI-TOF</t>
+          <t>FTIR;肺水肿;心源性猝死</t>
         </is>
       </c>
       <c r="R57" s="3" t="inlineStr">
         <is>
-          <t>American Journal of Forensic Medicine and Pathology</t>
+          <t>Analytical Chemistry</t>
         </is>
       </c>
       <c r="S57" s="3" t="inlineStr">
         <is>
-          <t>10.1097/PAF.0000000000000275</t>
+          <t>10.1021/acs.analchem.7b04642</t>
         </is>
       </c>
     </row>
@@ -5954,38 +5836,37 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Diagnosis of a Cerebral Arteriovenous Malformation Using Isolated Brain Computed Tomography Angiography: Case Report</t>
+          <t>Research Progress of MALDI-TOF-IMS in Biomedicine and Its Application Prospect in Forensic Sciences</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>离体脑CT血管造影诊断脑动静脉畸形：案例报告</t>
+          <t>MALDI-TOF-IMS在生物医学中的研究进展及其在法医学中的应用前景</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>目的：展示离体脑CT血管造影在法医学实践中诊断脑动静脉畸形(AVM)的价值。方法：对一例猝死案例的离体脑进行CT血管造影检查，向脑动脉注入造影剂后行CT扫描，并将影像学结果与尸体解剖进行对比。结果：离体脑CT血管造影清晰显示了AVM及其供血动脉和引流静脉，诊断经尸体解剖证实。结论：离体脑CT血管造影是法医学实践中诊断脑动静脉畸形的有效方法。</t>
+          <t>基质辅助激光解吸/电离飞行时间成像质谱(MALDI-TOF-IMS)是一种强大的分子成像技术。本文综述了MALDI-TOF-IMS在生物医学中的研究进展及其在法医学中的应用前景，介绍了其原理、技术特点和优势，讨论了其在生物标志物发现、药物分布分析和组织表征中的应用，并提出了其在法医病理学、毒理学及微量物证分析中的潜在应用。MALDI-TOF-IMS在法医分子成像方面具有广阔前景。</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>死后影像学
-脑动静脉畸形</t>
+          <t>MALDI-TOF质谱成像</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>影像</t>
+          <t>质谱</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>死因</t>
+          <t>损伤机制</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>2016-09</t>
+          <t>2017-10</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -5995,52 +5876,52 @@
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>中文核心（JCR未收录）</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>可牵引一篇『死后脑血管成像在法医神经病理学中的应用』综述：汇总PMCTA、离体脑灌注CT血管造影与死后MRI在脑动静脉畸形、动脉瘤破裂、蛛网膜下腔出血等猝死案例中的诊断价值，按『成像技术分类—血管病变检出—影像与解剖对照验证』框架组织，讨论离体器官成像作为常规神经病理学检查补充手段的流程与限度。</t>
+          <t>该文本身即综述，可进一步牵引一篇『分子成像质谱技术（MALDI-IMS、DESI、SIMS）在法医学中的应用前景』的比较性综述：按技术原理（电离方式、空间分辨率、是否标记）对比各质谱成像平台的优劣，并围绕法医病理（心肌梗死、脑损伤分子标志物）、法医毒理（体内药物/毒物分布）与微量物证三大应用域组织文献，提出『原位分子病理学』的概念框架与标准化流程建议。</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>为单一案例报告，证据等级低；离体脑操作（取出脑组织后注射对比剂）可能改变血管张力与形态，产生血管塌陷、对比剂外渗等人工假象，注射压力与剂量缺乏标准化。仅证实了较大AVM的检出能力，对隐匿型微血管畸形（毛细血管扩张症、微小AVM）的检出敏感性未知，未与颅内MRI等无创模态做对照。</t>
+          <t>属叙述性综述，未报告系统检索策略、纳入/排除标准与证据分级，存在选择偏倚；对MALDI-TOF-IMS的法医学应用多为前景展望，实证案例与量化数据较少。对空间分辨率、定量能力、样本前处理等关键技术瓶颈的讨论有限，亦未与其他质谱成像技术（DESI、SIMS）做系统优劣比较。</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>Postmortem CT angiography played an important role in diagnosis of the cerebral arteriovenous malformation that was responsible for a massive hemorrhage in the skull.</t>
+          <t>Matrix-assisted laser desorption/ionization time-of-flight imaging mass spectrometry (MALDI-TOF-IMS) can analysis unknown compounds in sections and obtain molecule imaging by scanning biological tissue sections, which has become a powerful tool for the research of biomarker, lipid distribution and drug metabolism, etc. This article reviews the application of this technique in protein identification, clinical application, drug discovery, lipid research and brain injury.</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>对一例猝死案例的离体脑进行CT血管造影：向脑动脉注入造影剂后行CT扫描，将影像学表现与尸体解剖结果进行对比验证。</t>
+          <t>文献综述，系统介绍MALDI-TOF-IMS技术成像原理和工作流程，总结其在生物医学领域（生物标志物发现、药物组织分布、组织分子表征）的研究进展，前瞻性探讨该技术在法医学各分支学科中的潜在应用。</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>离体脑CT血管造影是法医学实践中诊断脑动静脉畸形的有效方法，可清晰显示AVM的供血动脉和引流静脉。</t>
+          <t>MALDI-TOF-IMS作为无需标记的原位分子成像技术，在法医病理学、毒理学和微量物证分析等领域具有巨大应用潜力，有望成为法医分子成像的重要工具。</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>将离体脑CT血管造影技术应用于法医学脑AVM的死后诊断，为猝死案例中脑血管畸形的法医学鉴定提供了新的影像学手段。</t>
+          <t>首次系统性将MALDI-TOF-IMS这一前沿分子成像技术引入法医学领域进行应用前景分析，架起了生物医学先进技术与法医学需求之间的桥梁。</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
         <is>
-          <t>脑AVM;血管造影;PMCT</t>
+          <t>法医学杂志;生物医学;MALDI-TOF-IMS</t>
         </is>
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
-          <t>American Journal of Forensic Medicine and Pathology</t>
+          <t>Fa yi xue za zhi</t>
         </is>
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>10.1097/PAF.0000000000000247</t>
+          <t>10.3969/j.issn.1004-5619.2017.05.016</t>
         </is>
       </c>
     </row>
@@ -6050,92 +5931,93 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Research progress in the estimation of the postmortem interval by Chinese forensic scholars</t>
+          <t>Application of FTIR spectroscopy for traumatic axonal injury: a possible tool for estimating injury interval</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>中国法医学者死后间隔时间推断研究进展</t>
+          <t>FTIR光谱在外伤性轴索损伤中的应用：推断损伤时间的可能工具</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>死后间隔时间(PMI)推断是中国法医病理学的重点研究领域。本文综述了中国法医学者在PMI推断方面的研究进展，涵盖早期死后变化、尸体降温、超生反应、生化标志物、分子生物学技术、法医昆虫学和法医微生物学等方法。总结了中国学者在该领域取得的成果与面临的挑战，并对中国PMI研究的未来方向提出了展望。</t>
+          <t>基于FTIR的PLS算法作为推断外伤性轴索损伤（TAI）损伤时间的客观工具，在法医学和神经学中具有应用价值。</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>死后间隔时间</t>
+          <t>光谱分析
+损伤时间推断</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>综述</t>
+          <t>光谱</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>PMI</t>
+          <t>损伤机制</t>
         </is>
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>2016-01</t>
+          <t>2017-08</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>复旦大学基础医学院法医学系</t>
+          <t>复旦大学基础医学院法医学系/西安交通大学法医学院</t>
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>该文为PMI综述，可进一步牵引若干子领域深度综述：如『分子生物学方法推断PMI：RNA降解、蛋白质组与代谢组学的证据比较』『法医微生物组学与PMI推断』或『法医昆虫学PMI推断的中国实践』，按『方法原理—适用窗口—误差范围—环境影响因素—标准化与验证』框架细化，并以国际方法为参照评估中国方案的优劣与融合路径。</t>
+          <t>可牵引一篇『振动光谱学推断神经损伤时间的研究进展』综述：聚焦外伤性轴索损伤、脑挫伤、缺血缺氧性脑损伤中轴突膜脂质与蛋白质二级结构的时相性生化改变，按『损伤后不同时间点的光谱特征—PLS/机器学习回归—损伤时间预测方程』框架组织，并延伸讨论光谱学方法在损伤时间与死后间隔时间（PMI）双重时间推断中的统一应用前景。</t>
         </is>
       </c>
       <c r="L59" s="3" t="inlineStr">
         <is>
-          <t>属叙述性综述，未提供系统检索策略、纳入排除标准与质量评估，存在选择偏倚；对各方法（死后变化、生化标志物、分子生物学、昆虫学、微生物学）证据成熟度不一却同等论述，缺乏量化比较（如各方法误差区间、适用PMI窗口）。中国人群数据的可重复性与外部验证情况未深入评估，也未讨论各方法在不同温度、湿度与埋葬环境下适用边界。</t>
+          <t>基于实验模型（TAI模型）而非人体组织，动物与人类轴索损伤的分子时相进程存在物种差异，向人体外推需谨慎。PLS预测模型的精度受训练集损伤时间点覆盖密度、损伤严重度分层及个体间变异影响，样本量有限；FTIR对组织含水、固定与切片厚度敏感，跨实验室标准化问题未解决，模型的外部验证亦不足。</t>
         </is>
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
-          <t>The determination of time since death or the postmortem interval (PMI) is one of the most important and frequently asked questions in forensic medicine. We conducted a review of relevant studies published by Chinese forensic scholars in the last few decades, summarizing progress using molecular biology, spectroscopic technology, entomological methods, energy changes, thanatochemistry and other methods.</t>
+          <t>FTIR-based PLS algorithm as an objective tool for estimating injury intervals of traumatic axonal injury (TAI) in forensic science and neurology.</t>
         </is>
       </c>
       <c r="N59" s="3" t="inlineStr">
         <is>
-          <t>文献综述，涵盖早期死后变化、尸体降温、超生反应、生化标志物、分子生物学技术、法医昆虫学和法医微生物学等多种PMI推断方法的原理和研究进展总结。</t>
+          <t>动物实验（大鼠TAI模型），脑组织切片，FTIR光谱+PLS回归</t>
         </is>
       </c>
       <c r="O59" s="3" t="inlineStr">
         <is>
-          <t>系统总结了中国法医学者在PMI推断领域的研究贡献和进展，明确了中国特色研究方向（法医昆虫学、微生物学等）和未来发展路径。</t>
+          <t>FTIR光谱结合PLS回归可准确推断TAI损伤时间，为法医学神经损伤时间推断提供新方法。</t>
         </is>
       </c>
       <c r="P59" s="3" t="inlineStr">
         <is>
-          <t>系统梳理并总结了中国法医学者在死后间隔时间推断领域的独特研究贡献，明确了中国在该领域的特色研究方向。</t>
+          <t>首次将FTIR光谱用于外伤性轴索损伤的时间推断</t>
         </is>
       </c>
       <c r="Q59" s="3" t="inlineStr">
         <is>
-          <t>综述;死亡时间;中国法医学者</t>
+          <t>FTIR;外伤性轴索损伤;损伤时间</t>
         </is>
       </c>
       <c r="R59" s="3" t="inlineStr">
         <is>
-          <t>Forensic Sciences Research</t>
+          <t>Bioscience Reports</t>
         </is>
       </c>
       <c r="S59" s="3" t="inlineStr">
         <is>
-          <t>10.1080/20961790.2016.1229377</t>
+          <t>10.1042/BSR20170720</t>
         </is>
       </c>
     </row>
@@ -6145,23 +6027,23 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Use of 3D reconstruction of emergency and postoperative craniocerebral CT images to explore craniocerebral trauma mechanism</t>
+          <t>Diagnosis of coronary artery disease using targeted post-mortem computed tomography coronary angiography: a case report</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>急诊和术后颅脑CT图像三维重建探索颅脑损伤机制</t>
+          <t>靶向死后CT冠状动脉造影诊断冠心病：案例报告</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>目的：利用急诊和术后CT图像的三维重建探索颅脑损伤机制。方法：收集创伤患者的急诊和术后颅脑CT图像，进行三维重建，分析骨折形态、颅内损伤分布及损伤机制，并分析创伤机制与损伤模式之间的相关性。结果：三维重建清晰显示了颅脑损伤模式，可根据骨折和损伤分布模式推断损伤机制。结论：急诊和术后CT图像三维重建是法医学实践中探索颅脑损伤机制的有用方法。</t>
+          <t>目的：展示靶向死后CT冠状动脉造影在冠心病诊断中的应用。方法：对一例猝死案例进行靶向死后CT冠状动脉造影检查，通过靶向注射对比剂实现冠状动脉可视化，并将CT结果与尸检及组织病理学检查进行对比。结果：靶向死后CT冠状动脉造影清晰显示了冠状动脉狭窄，结果与尸检及组织病理学检查一致。结论：靶向死后CT冠状动脉造影是法医学实践中诊断冠心病的有价值工具，尤其适用于微创检查。</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>影像学
-颅脑损伤</t>
+          <t>死后影像学
+冠心病</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -6171,12 +6053,12 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>损伤机制</t>
+          <t>死因</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>2015-10</t>
+          <t>2017-01</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
@@ -6186,52 +6068,52 @@
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>可牵引一篇『三维重建与虚拟解剖技术在损伤机制分析中的应用』综述：按CT数据采集—三维分割重建—骨折形态与骨折线走向分析—致伤方式（撞击/坠落/钝器）反推的流程组织文献，并可扩展至『影像学-有限元生物力学联合的损伤重建工作流』，讨论急诊与术后多时间节点动态重建在损伤演变分析中的价值。</t>
+          <t>可牵引一篇『死后CT血管造影（PMCTA）在心血管源性猝死死因鉴定中的应用』综述：对比全身灌注、靶向注射、左心室穿刺等不同PMCTA技术的操作流程、显影质量与适用场景，聚焦冠状动脉狭窄程度评估、斑块负荷与钙化评分等影像学征象，并以『影像所见—传统尸检—组织病理学金标准』三对照验证模式组织证据，讨论微创影像学替代传统尸检的可行性边界。</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>属案例报告性质，样本有限，损伤模式与机制的对应关系缺乏大样本统计验证；急诊与术后CT时间点不同，手术干预（内固定、去骨瓣减压）会改变骨折原始形态，重建结果可能偏离原始损伤。三维重建依赖图像质量与分割算法，存在操作者间差异；损伤机制推断为定性分析，未结合量化力学参数验证。</t>
+          <t>为单一案例报告，证据等级低，结论外推性有限；靶向注射依赖操作者经验，对比剂注射压力、剂量与浓度缺乏标准化方案。死后血管塌陷、痉挛及气体伪影可能使CTA所示狭窄程度与解剖所见存在偏差，且该方法难以评估弥漫性小血管病变与心肌缺血的功能学意义，缺乏多中心案例的系统性验证。</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>We report a craniocerebral trauma case in which a man sustained severe skull fractures and cerebral contusions. We reconstructed the original skull fracture features by utilizing digital reconstruction technologies in terms of CT scanning, 3D reconstruction, and virtual surgical tools. The case demonstrated that digital reconstruction technologies can serve as effective approaches for forensic investigation.</t>
+          <t>Targeted post-mortem computed tomography (PMCT) combined with coronary angiography has the potential to play a significant role in the investigation of sudden cardiac death. The authors utilized a targeted PMCT coronary angiography in a case involving a 53-year-old man who died from acute myocardial ischemia. Targeted PMCTA can visualize the arteries and estimate the degree of principal pathological changes.</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>收集创伤患者的急诊和术后颅脑CT图像，进行三维重建，分析骨折形态、颅内损伤分布和损伤机制，并分析创伤机制与损伤模式之间的相关性。</t>
+          <t>对一例可疑心源性猝死案例实施靶向死后CT冠状动脉造影，通过靶向注射碘对比剂后行CT扫描，观察冠脉狭窄程度与分布，将影像学结果与传统尸检及组织病理学检查结果对照验证。</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>急诊和术后CT图像三维重建能够清晰显示颅脑损伤模式，可根据骨折和损伤分布模式推断损伤机制，是探索颅脑损伤机制的有用方法。</t>
+          <t>靶向死后CT冠状动脉造影可清晰显示冠状动脉病变，与传统尸检及组织病理学高度一致，为法医学冠心病微创诊断提供了可靠手段。</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>结合急诊与术后两个时间节点的颅脑CT图像进行三维重建，从损伤演变角度探索颅脑损伤机制，为法医学损伤机制推断提供了动态分析思路。</t>
+          <t>将靶向死后CT冠状动脉造影技术应用于法医学冠心病诊断，实现了微创化尸体血管检查，为拒绝传统尸检的案例提供替代性诊断方案。</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
         <is>
-          <t>CT;3D重建;颅脑损伤</t>
+          <t>PMCTA;案例报告;冠心病</t>
         </is>
       </c>
       <c r="R60" s="2" t="inlineStr">
         <is>
-          <t>Forensic Science International</t>
+          <t>Forensic Sciences Research</t>
         </is>
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>10.1016/j.forsciint.2015.07.012</t>
+          <t>10.1080/20961790.2017.1328795</t>
         </is>
       </c>
     </row>
@@ -6241,27 +6123,28 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Nonfracture-associated pulmonary fat embolism after blunt force fatality: case report and review of the literature</t>
+          <t>Post-mortem computed tomography angiography using left ventricle cardiac puncture: A whole-body, angiographic approach</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>钝力伤致死后无骨折相关肺脂肪栓塞：案例报告与文献综述</t>
+          <t>左心室心脏穿刺死后CT血管造影：全身血管造影方法</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>肺脂肪栓塞通常与骨折相关，然而无骨折相关肺脂肪栓塞十分罕见。本文报告了一例钝力伤后无骨折的致命性肺脂肪栓塞案例，呈现了案例详情、尸体解剖发现和组织病理学检查结果，并对无骨折相关肺脂肪栓塞进行了文献综述。可能的机制包括软组织损伤中脂肪的动员。法医病理学家在处理无骨折的钝力伤致死案例时应了解这一罕见情况。</t>
+          <t>目的：介绍一种通过左心室心脏穿刺实现全身死后CT血管造影的方法。方法：实施左心室心脏穿刺并注射对比剂，随后进行全身CT扫描，在多例案例中对血管造影质量及诊断价值进行评估。结果：左心室心脏穿刺成功实现了全身血管造影，从头至脚的血管系统获得了良好显影，并识别出多种病理状况。结论：经左心室心脏穿刺的死后CT血管造影是一种适用于法医学调查的有效全身血管造影方法。</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>肺脂肪栓塞</t>
+          <t>死后影像学
+全身血管造影</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>形态学</t>
+          <t>影像</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
@@ -6271,7 +6154,7 @@
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t>2015-06</t>
+          <t>2017-01</t>
         </is>
       </c>
       <c r="I61" s="3" t="inlineStr">
@@ -6281,52 +6164,52 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>可牵引一篇『脂肪栓塞的法医学研究进展』综述：系统梳理骨折相关与无骨折（软组织损伤）相关肺脂肪栓塞的流行病学、发病机制（脂肪动员理论、脂质生化介质）、组织学诊断标准（常规HE、油红O特殊染色、定量评估）及作为直接死因的认定标准，并以『栓塞程度与死亡因果关系的判定』争议为论述主线，结合临床脂肪栓塞综合征的转归讨论法医鉴定要点。</t>
+          <t>可牵引一篇『死后血管造影技术演进与微创化趋势』的综述：按技术代际梳理从依赖心肺转流机的全身灌注PMCTA，到手动/泵注的简化全身造影、靶向局部造影与心脏穿刺入路的演变，以显影质量、操作时间、成本、设备依赖性与适用中心条件为比较维度，提出面向基层法医机构的『低门槛死后血管成像方案』选择框架。</t>
         </is>
       </c>
       <c r="L61" s="3" t="inlineStr">
         <is>
-          <t>为单一案例报告，无骨折相关致命性肺脂肪栓塞属罕见情况，结论外推性有限；脂肪栓塞与死亡的因果关系判定缺乏统一量化标准（栓塞程度阈值、是否排除其他并发死因），本文亦未做定量评估。油红O等特殊染色受死后自溶与组织处理影响，对脂肪检出的可靠性未讨论，且未能完全排除其他并存死因。</t>
+          <t>为方法学描述加多例应用，未报告各例的量化评估指标与统计比较，显影质量判断偏主观；左心室穿刺单点注射可能存在部分血管床显影不均、对比剂残留心腔产生伪影等问题，操作失败率与对比剂外渗等并发症未详细说明。与完整尸检/组织病理学的系统对照不足，血管病变检出的敏感度与特异度尚不明确。</t>
         </is>
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
-          <t>This case reminds forensic scientists to consider fat embolism as a cause of death in cases of blunt force injury without fracture, and patients must be closely monitored while still alive, with other relevant clinical factors identified for better therapeutic effect, thereby decreasing the mortality rate.</t>
+          <t>Compared with other existing PMCTA methods for examination of vascular injuries and diseases, this technique involves simple procedures, is less time consuming, has lower associated costs, does not require specialized equipment, provides adequate imaging quality, and is suitable for centres not equipped with cardiopulmonary bypass machines or other specialized equipment.</t>
         </is>
       </c>
       <c r="N61" s="3" t="inlineStr">
         <is>
-          <t>案例报告：呈现钝力伤后无骨折致命性肺脂肪栓塞的案例详情、尸检发现和组织病理学检查结果（脂肪染色等），辅以无骨折相关肺脂肪栓塞的文献综述。</t>
+          <t>采用左心室心脏穿刺途径注入碘对比剂，随后行全身多层螺旋CT扫描，在多个法医案例中评估血管显影质量（动脉、静脉系统及微血管充盈程度），分析其对各类病变的诊断效能。</t>
         </is>
       </c>
       <c r="O61" s="3" t="inlineStr">
         <is>
-          <t>无骨折相关肺脂肪栓塞是钝力伤致死中的罕见情况，可能机制为软组织损伤中脂肪的动员；法医在处理无骨折钝力伤致死案例时应警惕此种可能。</t>
+          <t>经左心室心脏穿刺的全身死后CT血管造影操作简便，可实现从头到下肢的血管系统全面显影，有助于发现血管及实质器官病变，是适用于法医学常规尸体检查的有效影像学手段。</t>
         </is>
       </c>
       <c r="P61" s="3" t="inlineStr">
         <is>
-          <t>报告了钝力伤后无骨折相关肺脂肪栓塞的罕见案例并系统综述文献，提醒法医不应因无骨折而排除脂肪栓塞的可能。</t>
+          <t>首创通过左心室穿刺单次注射实现全身死后CT血管造影的方法，突破了传统多血管插管的繁琐操作，为死后血管系统的全面评估提供了简便高效的解决方案。</t>
         </is>
       </c>
       <c r="Q61" s="3" t="inlineStr">
         <is>
-          <t>脂肪栓塞;案例报告;钝力伤</t>
+          <t>全心造影;左心室穿刺;PMCTA</t>
         </is>
       </c>
       <c r="R61" s="3" t="inlineStr">
         <is>
-          <t>American Journal of Forensic Medicine and Pathology</t>
+          <t>PLoS ONE</t>
         </is>
       </c>
       <c r="S61" s="3" t="inlineStr">
         <is>
-          <t>10.1097/PAF.0000000000000142</t>
+          <t>10.1371/journal.pone.0183408</t>
         </is>
       </c>
     </row>
@@ -6336,27 +6219,27 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Mechanical properties of cranial bones and sutures in 1-2-year-old infants</t>
+          <t>Identifying Diffuse Axonal Injury by Matrix-Assisted Laser Desorption/Ionization Time-of-Flight: A New Method for Pathological Observation</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>1-2岁婴儿颅骨和骨缝的力学性能</t>
+          <t>MALDI-TOF质谱成像鉴定弥漫性轴索损伤：病理观察新方法</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>目的：研究1-2岁婴儿颅骨和骨缝的力学性能。方法：从1-2岁婴儿尸体采集颅骨和骨缝样本，进行拉伸和压缩力学测试，测量弹性模量、极限强度等力学参数。结果：获得了婴儿颅骨和骨缝的力学性能特征，骨与骨缝之间、不同颅骨区域之间存在显著差异。结论：婴儿颅骨和骨缝的力学性能数据为法医学实践中儿童头部创伤的生物力学分析提供了重要参考依据。</t>
+          <t>目的：探索MALDI-TOF质谱成像在弥漫性轴索损伤(DAI)鉴定中的应用。方法：利用MALDI-TOF质谱成像对DAI病例和对照组的脑组织样本进行分析，比较分子谱差异，并鉴定DAI的特异性生物标志物。结果：MALDI-TOF成像显示DAI脑组织与正常组织具有明显不同的分子谱，鉴定出可区分DAI与对照的特异性脂质和蛋白质标志物。结论：MALDI-TOF质谱成像是一种新型且有效的DAI病理观察方法，可提供分子水平的诊断信息，作为传统组织病理学的有力补充。</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>法医生物力学</t>
+          <t>质谱成像</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>生物力学</t>
+          <t>质谱</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -6366,7 +6249,7 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>2014-10</t>
+          <t>2016-12</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -6376,52 +6259,52 @@
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>可牵引一篇『儿童颅骨生物力学与虐待性头部创伤（AHT）鉴别的法医学综述』：汇总不同年龄段颅骨与骨缝的力学参数（弹性模量、极限强度、极限应变），按『年龄依赖性力学数据库—有限元建模—坠落/摇晃等机制致伤可能性评估』框架组织，讨论力学数据在区分意外跌落与虐待性损伤中的证据价值及其不确定性边界。</t>
+          <t>可牵引一篇『质谱成像（MSI）在脑损伤法医病理学中的应用』综述：围绕DAI、脑挫伤、缺血缺氧性脑病的脂质与蛋白质分子标志物鉴定，按『样本制备—MSI采集—分子谱差异分析—监督分类模型（神经网络等）—与传统组织病理学互补』框架组织文献，并可前瞻性讨论分子成像对损伤时间推断与损伤机制认定的增量价值。</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>样本来自1-2岁婴儿尸体，样本量有限且年龄跨度窄，外推至新生儿、幼儿其他年龄段受限；尸体组织力学性能与活体存在差异（死后变化、取材与保存处理）。离体骨缝与骨样本的力学行为不能完全代表完整颅骨结构（忽略脑组织耦合与颅内压），且仅做静态拉伸/压缩测试，缺乏冲击载荷等动态条件下的数据。</t>
+          <t>样本量小（共15张大鼠脑干切片，10例DAI对5例对照），统计功效有限；监督神经网络在小样本上易过拟合，缺乏独立测试集与外部验证。仅分析脑干单一区域，未覆盖DAI好发的胼胝体与脑白质；大鼠与人类DAI分子谱存在物种差异，且死后间隔对脂质降解的影响未讨论，向人体外推证据不足。</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>There was no significant difference in ultimate stress, elastic modulus, or ultimate strain between the sagittal and coronal sutures, however, there were significant differences between the frontal and parietal bones as well as between the cranial bones and suture samples.</t>
+          <t>PURPOSE: The aim of this study was to identify the diffuse axonal injury (DAI) of rat through screening out differentially expressed proteins which may represent potential biomarkers by MALDI-TOF IMS. METHODS: A total of 15 brainstem sections of rats (10 with and 5 without DAI) were conducted by MALDI-TOF IMS. RESULTS: Applying a Supervised Neural Network algorithm, we were able to distinguish between normal and DAI regions with an overall cross-validation, a sensitivity and specificity of 95.67%, 99.34%, and 92.01%, respectively. CONCLUSIONS: This study reveals the value of MALDI-TOF IMS to classify between normal and injured tissues and identify candidates for DAI biomarkers.</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>从1-2岁婴儿尸体采集颅骨和骨缝样本，进行拉伸和压缩力学测试，测量弹性模量、极限强度等力学参数，比较骨与骨缝以及不同颅骨区域之间的差异。</t>
+          <t>收集DAI案例和对照组脑组织样本，利用MALDI-TOF质谱成像进行原位分子扫描，分析质谱峰差异筛选DAI特异性脂质和蛋白质分子标志物，将分子成像结果与传统HE/银染等进行对比。</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>获得了1-2岁婴儿颅骨和骨缝的力学性能参数（弹性模量、极限强度等），为法医学儿童头部创伤的生物力学分析提供了重要基础数据。</t>
+          <t>MALDI-TOF质谱成像能从分子水平揭示DAI的组织病理变化，鉴定出的特异性分子标志物可有效区分DAI与正常组织，为DAI诊断提供超越传统组织病理学的分子维度信息。</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>首次系统测定1-2岁婴儿颅骨和骨缝的力学性能参数，填补了该年龄段颅骨生物力学数据空白。</t>
+          <t>首次将MALDI-TOF质谱成像技术应用于DAI的法医病理学诊断，发现可供鉴别DAI的脂质和蛋白质分子标志物，开辟了分子病理学观察新途径。</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
         <is>
-          <t>生物力学;颅骨;婴儿</t>
+          <t>弥漫性轴索损伤;生物标志物;MALDI-TOF</t>
         </is>
       </c>
       <c r="R62" s="2" t="inlineStr">
         <is>
-          <t>Medical Science Monitor</t>
+          <t>American Journal of Forensic Medicine and Pathology</t>
         </is>
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>10.12659/MSM.892278</t>
+          <t>10.1097/PAF.0000000000000275</t>
         </is>
       </c>
     </row>
@@ -6431,27 +6314,28 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Death due to fulminant neuroleptic malignant syndrome induced by low doses of haloperidol: a rare case</t>
+          <t>Diagnosis of a Cerebral Arteriovenous Malformation Using Isolated Brain Computed Tomography Angiography: Case Report</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>低剂量氟哌啶醇致暴发性神经阻滞剂恶性综合征死亡：罕见案例</t>
+          <t>离体脑CT血管造影诊断脑动静脉畸形：案例报告</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>神经阻滞剂恶性综合征(NMS)是抗精神病药物的一种罕见但危及生命的并发症。本文报告了一例低剂量氟哌啶醇致暴发性NMS死亡的罕见案例。受害者是一名年轻男性，接受低剂量氟哌啶醇后出现快速发作的NMS并导致死亡。讨论了该案例的临床过程、尸检发现和法医学意义，并进行了类似案例的文献综述。即使低剂量氟哌啶醇也可能触发致命的NMS，涉及抗精神病药物的猝死案例应考虑该可能性。</t>
+          <t>目的：展示离体脑CT血管造影在法医学实践中诊断脑动静脉畸形(AVM)的价值。方法：对一例猝死案例的离体脑进行CT血管造影检查，向脑动脉注入造影剂后行CT扫描，并将影像学结果与尸体解剖进行对比。结果：离体脑CT血管造影清晰显示了AVM及其供血动脉和引流静脉，诊断经尸体解剖证实。结论：离体脑CT血管造影是法医学实践中诊断脑动静脉畸形的有效方法。</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>罕见案例</t>
+          <t>死后影像学
+脑动静脉畸形</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>形态学</t>
+          <t>影像</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
@@ -6461,7 +6345,7 @@
       </c>
       <c r="H63" s="3" t="inlineStr">
         <is>
-          <t>2014-05</t>
+          <t>2016-09</t>
         </is>
       </c>
       <c r="I63" s="3" t="inlineStr">
@@ -6471,52 +6355,52 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>可牵引一篇『抗精神病药物相关猝死的法医学鉴别诊断』综述：围绕神经阻滞剂恶性综合征（NMS）、药物性心律失常（QT延长）与其他死因的鉴别，按『药物暴露史评估—临床过程重建—尸检与毒理检测—死因认定逻辑』框架组织文献，重点讨论低剂量触发NMS的机制（多巴胺受体阻断、遗传易感性、脱水等危险因素）及死后诊断缺乏特异性标志物的鉴定困境。</t>
+          <t>可牵引一篇『死后脑血管成像在法医神经病理学中的应用』综述：汇总PMCTA、离体脑灌注CT血管造影与死后MRI在脑动静脉畸形、动脉瘤破裂、蛛网膜下腔出血等猝死案例中的诊断价值，按『成像技术分类—血管病变检出—影像与解剖对照验证』框架组织，讨论离体器官成像作为常规神经病理学检查补充手段的流程与限度。</t>
         </is>
       </c>
       <c r="L63" s="3" t="inlineStr">
         <is>
-          <t>为单一案例报告，低剂量触发暴发性NMS属罕见事件，外推性有限；NMS本质为临床诊断，死后缺乏特异性生物学标志物，尸检无特征性病理改变，死因认定主要依靠排除法，本文无法完全排除心律失常、吸入性肺炎等并发死因。文献综述部分的证据检索与整合不系统，未对同类案例做量化汇总。</t>
+          <t>为单一案例报告，证据等级低；离体脑操作（取出脑组织后注射对比剂）可能改变血管张力与形态，产生血管塌陷、对比剂外渗等人工假象，注射压力与剂量缺乏标准化。仅证实了较大AVM的检出能力，对隐匿型微血管畸形（毛细血管扩张症、微小AVM）的检出敏感性未知，未与颅内MRI等无创模态做对照。</t>
         </is>
       </c>
       <c r="M63" s="3" t="inlineStr">
         <is>
-          <t>The paper reports on a rare case of fulminant neuroleptic malignant syndrome (NMS) with several risk factors, typical manifestation and rapid death induced by low doses of haloperidol. The pathological findings, pathogenesis, clinical manifestations, diagnostic criteria, risk factors and other features of NMS are discussed.</t>
+          <t>Postmortem CT angiography played an important role in diagnosis of the cerebral arteriovenous malformation that was responsible for a massive hemorrhage in the skull.</t>
         </is>
       </c>
       <c r="N63" s="3" t="inlineStr">
         <is>
-          <t>案例报告：详细描述一名年轻男性接受低剂量氟哌啶醇后发生暴发性NMS并死亡的临床过程、尸检发现，并结合类似案例文献综述讨论法医学意义。</t>
+          <t>对一例猝死案例的离体脑进行CT血管造影：向脑动脉注入造影剂后行CT扫描，将影像学表现与尸体解剖结果进行对比验证。</t>
         </is>
       </c>
       <c r="O63" s="3" t="inlineStr">
         <is>
-          <t>即使是低剂量氟哌啶醇也可能触发致命的NMS；在涉及抗精神病药物的猝死案例中，法医学鉴定应考虑NMS的可能性。</t>
+          <t>离体脑CT血管造影是法医学实践中诊断脑动静脉畸形的有效方法，可清晰显示AVM的供血动脉和引流静脉。</t>
         </is>
       </c>
       <c r="P63" s="3" t="inlineStr">
         <is>
-          <t>报告了低剂量氟哌啶醇致暴发性NMS死亡的罕见案例，挑战了NMS通常与高剂量或联合用药相关的传统认识。</t>
+          <t>将离体脑CT血管造影技术应用于法医学脑AVM的死后诊断，为猝死案例中脑血管畸形的法医学鉴定提供了新的影像学手段。</t>
         </is>
       </c>
       <c r="Q63" s="3" t="inlineStr">
         <is>
-          <t>案例报告;神经阻滞剂恶性综合征</t>
+          <t>脑AVM;血管造影;PMCT</t>
         </is>
       </c>
       <c r="R63" s="3" t="inlineStr">
         <is>
-          <t>Journal of Forensic and Legal Medicine</t>
+          <t>American Journal of Forensic Medicine and Pathology</t>
         </is>
       </c>
       <c r="S63" s="3" t="inlineStr">
         <is>
-          <t>10.1016/j.jflm.2014.02.011</t>
+          <t>10.1097/PAF.0000000000000247</t>
         </is>
       </c>
     </row>
@@ -6526,93 +6410,92 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Characteristics of electrically injured skin from human hand tissue samples using Fourier transform infrared microspectroscopy</t>
+          <t>Research progress in the estimation of the postmortem interval by Chinese forensic scholars</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>使用FTIR显微光谱研究人手部组织样本电击伤皮肤的特征</t>
+          <t>中国法医学者死后间隔时间推断研究进展</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>FTIR显微光谱为电击伤的辅助诊断提供了客观光谱标志物。电击伤皮肤组织的角质层和非角质层区域的光谱吸收显著增加。</t>
+          <t>死后间隔时间(PMI)推断是中国法医病理学的重点研究领域。本文综述了中国法医学者在PMI推断方面的研究进展，涵盖早期死后变化、尸体降温、超生反应、生化标志物、分子生物学技术、法医昆虫学和法医微生物学等方法。总结了中国学者在该领域取得的成果与面临的挑战，并对中国PMI研究的未来方向提出了展望。</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>光谱分析
-电击伤</t>
+          <t>死后间隔时间</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>光谱</t>
+          <t>综述</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>死亡方式</t>
+          <t>PMI</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>2014-01</t>
+          <t>2016-01</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>复旦大学基础医学院法医学系/司法鉴定科学研究院</t>
+          <t>复旦大学基础医学院法医学系</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>可牵引一篇『电流斑鉴定的客观化方法研究进展』综述：对比传统形态学指标（表皮/真皮改变、金属化颗粒、SEM-EDX元素分析）与振动光谱（FTIR、拉曼）分子标志物在电击伤鉴定中的价值，按『样本类型—光谱特征—化学计量学判别—与相似损伤（热烧伤、摩擦伤）鉴别』框架组织，讨论多模态联合鉴定流程的构建。</t>
+          <t>该文为PMI综述，可进一步牵引若干子领域深度综述：如『分子生物学方法推断PMI：RNA降解、蛋白质组与代谢组学的证据比较』『法医微生物组学与PMI推断』或『法医昆虫学PMI推断的中国实践』，按『方法原理—适用窗口—误差范围—环境影响因素—标准化与验证』框架细化，并以国际方法为参照评估中国方案的优劣与融合路径。</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>仅采用人手部皮肤组织样本，样本量小，且未与热烧伤、摩擦伤、尸斑等相似外观损伤做光谱对照，特异性存疑；死后变化、腐败与固定处理对皮肤光谱的影响未系统控制。角质层与非角质层区域光谱变化的生物学解释及跨个体可重复性尚需更大样本验证，判别模型亦缺乏独立验证集。</t>
+          <t>属叙述性综述，未提供系统检索策略、纳入排除标准与质量评估，存在选择偏倚；对各方法（死后变化、生化标志物、分子生物学、昆虫学、微生物学）证据成熟度不一却同等论述，缺乏量化比较（如各方法误差区间、适用PMI窗口）。中国人群数据的可重复性与外部验证情况未深入评估，也未讨论各方法在不同温度、湿度与埋葬环境下适用边界。</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>FTIR-MSP presents a useful method to provide objective spectral markers for the assisted diagnosis of electrical marks. Band absorbance increased significantly both in the stratum and non-stratum corneum of electrically injured skin tissues.</t>
+          <t>The determination of time since death or the postmortem interval (PMI) is one of the most important and frequently asked questions in forensic medicine. We conducted a review of relevant studies published by Chinese forensic scholars in the last few decades, summarizing progress using molecular biology, spectroscopic technology, entomological methods, energy changes, thanatochemistry and other methods.</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>人尸检手部电击伤皮肤组织，FTIR显微光谱+组织学对比</t>
+          <t>文献综述，涵盖早期死后变化、尸体降温、超生反应、生化标志物、分子生物学技术、法医昆虫学和法医微生物学等多种PMI推断方法的原理和研究进展总结。</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>FTIR显微光谱可客观检测电击伤皮肤的特异性光谱改变，为法医电击伤鉴定提供辅助手段。</t>
+          <t>系统总结了中国法医学者在PMI推断领域的研究贡献和进展，明确了中国特色研究方向（法医昆虫学、微生物学等）和未来发展路径。</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>首次系统研究电击伤皮肤的FTIR光谱特征</t>
+          <t>系统梳理并总结了中国法医学者在死后间隔时间推断领域的独特研究贡献，明确了中国在该领域的特色研究方向。</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
         <is>
-          <t>FTIR;皮肤;电击伤</t>
+          <t>综述;死亡时间;中国法医学者</t>
         </is>
       </c>
       <c r="R64" s="2" t="inlineStr">
         <is>
-          <t>Science &amp; Justice</t>
+          <t>Forensic Sciences Research</t>
         </is>
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>10.1016/j.scijus.2013.07.005</t>
+          <t>10.1080/20961790.2016.1229377</t>
         </is>
       </c>
     </row>
@@ -6622,93 +6505,93 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>Infrared (IR) spectral markers of bronchial epithelia in victims of fatal burns</t>
+          <t>Use of 3D reconstruction of emergency and postoperative craniocerebral CT images to explore craniocerebral trauma mechanism</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>致命烧伤受害者支气管上皮的红外光谱标志物</t>
+          <t>急诊和术后颅脑CT图像三维重建探索颅脑损伤机制</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>FTIR显微光谱被证明是一种方便可靠的方法，通过同时监测多个特定参数，提供客观光谱标志物以辅助致命烧伤的诊断。</t>
+          <t>目的：利用急诊和术后CT图像的三维重建探索颅脑损伤机制。方法：收集创伤患者的急诊和术后颅脑CT图像，进行三维重建，分析骨折形态、颅内损伤分布及损伤机制，并分析创伤机制与损伤模式之间的相关性。结果：三维重建清晰显示了颅脑损伤模式，可根据骨折和损伤分布模式推断损伤机制。结论：急诊和术后CT图像三维重建是法医学实践中探索颅脑损伤机制的有用方法。</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>光谱分析
-烧伤</t>
+          <t>影像学
+颅脑损伤</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>光谱</t>
+          <t>影像</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>死亡方式</t>
+          <t>损伤机制</t>
         </is>
       </c>
       <c r="H65" s="3" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2015-10</t>
         </is>
       </c>
       <c r="I65" s="3" t="inlineStr">
         <is>
-          <t>复旦大学基础医学院法医学系/司法鉴定科学研究院</t>
+          <t>复旦大学基础医学院法医学系</t>
         </is>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>可牵引一篇『致命烧伤的死因鉴定与生前/死后鉴别综述』：整合体表烧伤面积与深度评估、吸入性损伤组织学改变与FTIR光谱分子标志物（支气管上皮生化改变）三层面证据，按『热损伤死因认定的证据链—生前烧伤与死后焚尸的鉴别—光谱学客观指标的引入』框架组织，讨论多参数联合监测对烧伤死因鉴定的增量价值。</t>
+          <t>可牵引一篇『三维重建与虚拟解剖技术在损伤机制分析中的应用』综述：按CT数据采集—三维分割重建—骨折形态与骨折线走向分析—致伤方式（撞击/坠落/钝器）反推的流程组织文献，并可扩展至『影像学-有限元生物力学联合的损伤重建工作流』，讨论急诊与术后多时间节点动态重建在损伤演变分析中的价值。</t>
         </is>
       </c>
       <c r="L65" s="3" t="inlineStr">
         <is>
-          <t>样本量有限，支气管上皮光谱标志物是否特异于烧伤（相对吸入性毒物损伤、感染性支气管炎等）未充分验证；死后自溶对上皮细胞脂质/蛋白生化组成的影响及固定剂对光谱的干扰未详细讨论。缺乏与常规组织学诊断的敏感度、特异度定量对比，方法标准化与跨实验室可重复性证据不足。</t>
+          <t>属案例报告性质，样本有限，损伤模式与机制的对应关系缺乏大样本统计验证；急诊与术后CT时间点不同，手术干预（内固定、去骨瓣减压）会改变骨折原始形态，重建结果可能偏离原始损伤。三维重建依赖图像质量与分割算法，存在操作者间差异；损伤机制推断为定性分析，未结合量化力学参数验证。</t>
         </is>
       </c>
       <c r="M65" s="3" t="inlineStr">
         <is>
-          <t>FT-IR microspectroscopy was shown to be a convenient and reliable method to provide objective spectral markers to assist the diagnosis of fatal burns by simultaneously monitoring several specific parameters.</t>
+          <t>We report a craniocerebral trauma case in which a man sustained severe skull fractures and cerebral contusions. We reconstructed the original skull fracture features by utilizing digital reconstruction technologies in terms of CT scanning, 3D reconstruction, and virtual surgical tools. The case demonstrated that digital reconstruction technologies can serve as effective approaches for forensic investigation.</t>
         </is>
       </c>
       <c r="N65" s="3" t="inlineStr">
         <is>
-          <t>人尸检支气管上皮组织，FTIR显微光谱+光谱分析</t>
+          <t>收集创伤患者的急诊和术后颅脑CT图像，进行三维重建，分析骨折形态、颅内损伤分布和损伤机制，并分析创伤机制与损伤模式之间的相关性。</t>
         </is>
       </c>
       <c r="O65" s="3" t="inlineStr">
         <is>
-          <t>FTIR显微光谱可检测致命烧伤支气管上皮的特异性光谱改变，为烧伤死因鉴定提供辅助诊断依据。</t>
+          <t>急诊和术后CT图像三维重建能够清晰显示颅脑损伤模式，可根据骨折和损伤分布模式推断损伤机制，是探索颅脑损伤机制的有用方法。</t>
         </is>
       </c>
       <c r="P65" s="3" t="inlineStr">
         <is>
-          <t>首次鉴定致命烧伤支气管上皮的FTIR光谱标志物</t>
+          <t>结合急诊与术后两个时间节点的颅脑CT图像进行三维重建，从损伤演变角度探索颅脑损伤机制，为法医学损伤机制推断提供了动态分析思路。</t>
         </is>
       </c>
       <c r="Q65" s="3" t="inlineStr">
         <is>
-          <t>FTIR;烧伤;支气管上皮</t>
+          <t>CT;3D重建;颅脑损伤</t>
         </is>
       </c>
       <c r="R65" s="3" t="inlineStr">
         <is>
-          <t>Applied Spectroscopy</t>
+          <t>Forensic Science International</t>
         </is>
       </c>
       <c r="S65" s="3" t="inlineStr">
         <is>
-          <t>10.1366/13-07189</t>
+          <t>10.1016/j.forsciint.2015.07.012</t>
         </is>
       </c>
     </row>
@@ -6718,38 +6601,37 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Finite element analysis of pedestrian lower limb fractures by direct force: the result of being run over or impact?</t>
+          <t>Nonfracture-associated pulmonary fat embolism after blunt force fatality: case report and review of the literature</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>行人下肢骨折直接外力有限元分析：碾压还是撞击？</t>
+          <t>钝力伤致死后无骨折相关肺脂肪栓塞：案例报告与文献综述</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>目的：利用有限元分析区分行人交通事故中碾压与撞击所致下肢骨折。方法：构建人体下肢有限元模型，施加模拟碾压和撞击的不同的载荷条件，比较两种机制下的骨折形态、应力分布和损伤特征。结果：碾压和撞击条件下的骨折模式表现出明显不同的特征，两种机制的应力分布和骨折扩展模式存在差异。结论：有限元分析有助于区分行人下肢骨折的碾压和撞击机制，为法医学事故重建提供科学依据。</t>
+          <t>肺脂肪栓塞通常与骨折相关，然而无骨折相关肺脂肪栓塞十分罕见。本文报告了一例钝力伤后无骨折的致命性肺脂肪栓塞案例，呈现了案例详情、尸体解剖发现和组织病理学检查结果，并对无骨折相关肺脂肪栓塞进行了文献综述。可能的机制包括软组织损伤中脂肪的动员。法医病理学家在处理无骨折的钝力伤致死案例时应了解这一罕见情况。</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>法医生物力学
-下肢骨折</t>
+          <t>肺脂肪栓塞</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>生物力学</t>
+          <t>形态学</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>损伤机制</t>
+          <t>死因</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>2013-06</t>
+          <t>2015-06</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
@@ -6759,52 +6641,52 @@
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>可牵引一篇『有限元方法（FEA）在法医损伤生物力学与致伤方式鉴别中的应用』系统综述：按『几何建模（CT个体化/标准化）—材料参数—边界与载荷条件—损伤准则—模型验证（案例对照）』流程框架组织文献，聚焦行人交通事故中碾压与撞击、坠落等致伤方式的力学鉴别，并讨论模型不确定性对法医鉴定结论证据效力的影响。</t>
+          <t>可牵引一篇『脂肪栓塞的法医学研究进展』综述：系统梳理骨折相关与无骨折（软组织损伤）相关肺脂肪栓塞的流行病学、发病机制（脂肪动员理论、脂质生化介质）、组织学诊断标准（常规HE、油红O特殊染色、定量评估）及作为直接死因的认定标准，并以『栓塞程度与死亡因果关系的判定』争议为论述主线，结合临床脂肪栓塞综合征的转归讨论法医鉴定要点。</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>有限元模型对骨骼材料参数与几何来源高度敏感，本文模型仅与单一真实案例对照验证，缺乏多案例统计验证；模型简化了肌肉、皮肤等软组织与边界条件，模拟载荷场景有限。未考虑个体差异（年龄、骨密度、体态），仿真所得应力分布向真实骨折形态的映射存在不确定性，结果的证据强度有限。</t>
+          <t>为单一案例报告，无骨折相关致命性肺脂肪栓塞属罕见情况，结论外推性有限；脂肪栓塞与死亡的因果关系判定缺乏统一量化标准（栓塞程度阈值、是否排除其他并发死因），本文亦未做定量评估。油红O等特殊染色受死后自溶与组织处理影响，对脂肪检出的可靠性未讨论，且未能完全排除其他并存死因。</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>This study developed a novel lower limb FE model and simulated three different loading scenarios and compared the injuries resulting from one actual case with the simulated results in order to explore the possible fracture bio-mechanism.</t>
+          <t>This case reminds forensic scientists to consider fat embolism as a cause of death in cases of blunt force injury without fracture, and patients must be closely monitored while still alive, with other relevant clinical factors identified for better therapeutic effect, thereby decreasing the mortality rate.</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>构建人体下肢有限元模型，分别施加模拟碾压和撞击的载荷条件，比较两种机制下的骨折形态、应力分布和损伤特征。</t>
+          <t>案例报告：呈现钝力伤后无骨折致命性肺脂肪栓塞的案例详情、尸检发现和组织病理学检查结果（脂肪染色等），辅以无骨折相关肺脂肪栓塞的文献综述。</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>碾压和撞击机制下的下肢骨折模式具有明显不同特征，有限元分析可有效区分两者，为法医学交通事故重建提供科学依据。</t>
+          <t>无骨折相关肺脂肪栓塞是钝力伤致死中的罕见情况，可能机制为软组织损伤中脂肪的动员；法医在处理无骨折钝力伤致死案例时应警惕此种可能。</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>将有限元分析方法应用于区分行人下肢骨折的碾压与撞击两种致伤机制，通过生物力学模拟为致伤方式判定提供定量分析手段。</t>
+          <t>报告了钝力伤后无骨折相关肺脂肪栓塞的罕见案例并系统综述文献，提醒法医不应因无骨折而排除脂肪栓塞的可能。</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
         <is>
-          <t>交通事故;下肢骨折;有限元</t>
+          <t>脂肪栓塞;案例报告;钝力伤</t>
         </is>
       </c>
       <c r="R66" s="2" t="inlineStr">
         <is>
-          <t>Forensic Science International</t>
+          <t>American Journal of Forensic Medicine and Pathology</t>
         </is>
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>10.1016/j.forsciint.2013.03.027</t>
+          <t>10.1097/PAF.0000000000000142</t>
         </is>
       </c>
     </row>
@@ -6814,92 +6696,93 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>Sudden twin infant death on the same day: a case report and review of the literature</t>
+          <t>Infrared (IR) spectral markers of bronchial epithelia in victims of fatal burns</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>同日双胞胎婴儿猝死：案例报告与文献综述</t>
+          <t>致命烧伤受害者支气管上皮的红外光谱标志物</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>婴儿猝死综合征(SIDS)是一种毁灭性事件。双胞胎婴儿同日同时猝死极为罕见。本文报告一例同日双胞胎婴儿猝死案例，呈现了案件调查、尸检发现和辅助检查结果，并进行了类似案例的全面文献综述。讨论了可能的机制包括遗传因素、环境因素和感染性原因。本案例强调了对多发婴儿猝死进行彻底法医学调查的重要性，以及同时考虑自然和非自然原因的必要性。</t>
+          <t>FTIR显微光谱被证明是一种方便可靠的方法，通过同时监测多个特定参数，提供客观光谱标志物以辅助致命烧伤的诊断。</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>罕见案例</t>
+          <t>光谱分析
+烧伤</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>形态学</t>
+          <t>光谱</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>死因</t>
+          <t>死亡方式</t>
         </is>
       </c>
       <c r="H67" s="3" t="inlineStr">
         <is>
-          <t>2013-06</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="I67" s="3" t="inlineStr">
         <is>
-          <t>复旦大学基础医学院法医学系</t>
+          <t>复旦大学基础医学院法医学系/司法鉴定科学研究院</t>
         </is>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>可牵引一篇『婴儿猝死（SIDS/SUDI）的法医学综合调查策略』综述：围绕多胞胎同日猝死、遗传性离子通道病（长QT综合征等）、代谢性疾病与虐待/窒息鉴别的鉴别诊断，按『现场勘查—全面尸检—辅助检查—分子尸检（基因panel）—多学科协作』流程框架组织文献，讨论自然与非自然原因在多发婴儿猝死中的证据权重评估方法。</t>
+          <t>可牵引一篇『致命烧伤的死因鉴定与生前/死后鉴别综述』：整合体表烧伤面积与深度评估、吸入性损伤组织学改变与FTIR光谱分子标志物（支气管上皮生化改变）三层面证据，按『热损伤死因认定的证据链—生前烧伤与死后焚尸的鉴别—光谱学客观指标的引入』框架组织，讨论多参数联合监测对烧伤死因鉴定的增量价值。</t>
         </is>
       </c>
       <c r="L67" s="3" t="inlineStr">
         <is>
-          <t>为单一案例报告，双胞胎同日死亡可能受共同环境因素（感染、环境温度、睡眠条件）混杂，难以归因单一机制；文中未报告分子尸检（遗传性心律失常基因检测）结果，遗传假说缺乏直接证据。仅凭尸检常无法区分自然猝死与人为窒息，结论依赖排除法，文献综述亦未对SIDS风险因素做量化系统评价。</t>
+          <t>样本量有限，支气管上皮光谱标志物是否特异于烧伤（相对吸入性毒物损伤、感染性支气管炎等）未充分验证；死后自溶对上皮细胞脂质/蛋白生化组成的影响及固定剂对光谱的干扰未详细讨论。缺乏与常规组织学诊断的敏感度、特异度定量对比，方法标准化与跨实验室可重复性证据不足。</t>
         </is>
       </c>
       <c r="M67" s="3" t="inlineStr">
         <is>
-          <t>Risk factors for SIDS should be considered individually or in combination as possible causes of death, and both 10-week-old male twins who appeared well at the time of their evening feeding yet died while sleeping on their backs have petechial hemorrhages.</t>
+          <t>FT-IR microspectroscopy was shown to be a convenient and reliable method to provide objective spectral markers to assist the diagnosis of fatal burns by simultaneously monitoring several specific parameters.</t>
         </is>
       </c>
       <c r="N67" s="3" t="inlineStr">
         <is>
-          <t>案例报告：呈现同日双胞胎婴儿猝死的案件调查（现场勘查、家庭访谈、病史采集）、系统尸体解剖（大体和组织病理学）、毒理学和微生物学辅助检查结果，并辅以类似双胞胎同日猝死案例的全面文献综述，分析遗传、环境和感染等可能机制。</t>
+          <t>人尸检支气管上皮组织，FTIR显微光谱+光谱分析</t>
         </is>
       </c>
       <c r="O67" s="3" t="inlineStr">
         <is>
-          <t>同日双胞胎婴儿猝死极为罕见，法医学调查应综合现场勘查、全面尸检和辅助检查，同时考虑遗传性离子通道病等自然原因和窒息等非自然原因的可能性，多学科联合调查是关键。</t>
+          <t>FTIR显微光谱可检测致命烧伤支气管上皮的特异性光谱改变，为烧伤死因鉴定提供辅助诊断依据。</t>
         </is>
       </c>
       <c r="P67" s="3" t="inlineStr">
         <is>
-          <t>报告了极为罕见的同日双胞胎婴儿猝死案例，系统综述类似文献，提出遗传因素（如长QT综合征等遗传性心律失常）和环境的综合作用机制，强调了多发婴儿猝死中法医学综合调查策略。</t>
+          <t>首次鉴定致命烧伤支气管上皮的FTIR光谱标志物</t>
         </is>
       </c>
       <c r="Q67" s="3" t="inlineStr">
         <is>
-          <t>案例报告;双胞胎;婴儿猝死</t>
+          <t>FTIR;烧伤;支气管上皮</t>
         </is>
       </c>
       <c r="R67" s="3" t="inlineStr">
         <is>
-          <t>Forensic Science, Medicine, and Pathology</t>
+          <t>Applied Spectroscopy</t>
         </is>
       </c>
       <c r="S67" s="3" t="inlineStr">
         <is>
-          <t>10.1007/s12024-013-9429-3</t>
+          <t>10.1366/13-07189</t>
         </is>
       </c>
     </row>
@@ -6909,38 +6792,37 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Sudden unexpected death due to Chiari type I malformation in a road accident case</t>
+          <t>Mechanical properties of cranial bones and sutures in 1-2-year-old infants</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>道路交通事故中Chiari I型畸形致意外猝死</t>
+          <t>1-2岁婴儿颅骨和骨缝的力学性能</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Chiari I型畸形是一种以小脑扁桃体经枕骨大孔疝出为特征的先天性异常。本文报告一例道路交通事故中因Chiari I型畸形致意外猝死的案例。受害者涉及一起轻微道路交通事故后意外死亡。尸检发现Chiari I型畸形伴脑干压迫。讨论轻微创伤与既往Chiari畸形在致死中的关系。本案例强调了在道路交通事故死亡案例中仔细进行神经病理学检查的重要性。</t>
+          <t>目的：研究1-2岁婴儿颅骨和骨缝的力学性能。方法：从1-2岁婴儿尸体采集颅骨和骨缝样本，进行拉伸和压缩力学测试，测量弹性模量、极限强度等力学参数。结果：获得了婴儿颅骨和骨缝的力学性能特征，骨与骨缝之间、不同颅骨区域之间存在显著差异。结论：婴儿颅骨和骨缝的力学性能数据为法医学实践中儿童头部创伤的生物力学分析提供了重要参考依据。</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>猝死
-Chiari畸形</t>
+          <t>法医生物力学</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>形态学</t>
+          <t>生物力学</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>死因</t>
+          <t>损伤机制</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>2013-03</t>
+          <t>2014-10</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
@@ -6950,52 +6832,52 @@
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>可牵引一篇『隐匿性颅颈交界区病变与轻微创伤致死的法医学因果分析』综述：以Chiari I型畸形、寰枢椎不稳等先天病变为对象，按『解剖脆弱性—创伤与体位因素交互—脑干/延髓受压机制—死因与因果关系（直接死因/诱因）认定』框架组织文献，讨论无症状携带者人群中的意外死亡风险及轻微创伤在死因判定中的法律与医学权重。</t>
+          <t>可牵引一篇『儿童颅骨生物力学与虐待性头部创伤（AHT）鉴别的法医学综述』：汇总不同年龄段颅骨与骨缝的力学参数（弹性模量、极限强度、极限应变），按『年龄依赖性力学数据库—有限元建模—坠落/摇晃等机制致伤可能性评估』框架组织，讨论力学数据在区分意外跌落与虐待性损伤中的证据价值及其不确定性边界。</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>为单一案例报告；Chiari I型畸形在普通人群无症状携带率较高，使『轻微创伤致死的因果关系』认定存在不确定性，本文缺乏流行病学对照支撑。脑干受压致死的机制推断缺少死后MRI、神经电生理等直接证据，且轻微创伤与体位因素各自的相对贡献未量化区分，结论外推需谨慎。</t>
+          <t>样本来自1-2岁婴儿尸体，样本量有限且年龄跨度窄，外推至新生儿、幼儿其他年龄段受限；尸体组织力学性能与活体存在差异（死后变化、取材与保存处理）。离体骨缝与骨样本的力学行为不能完全代表完整颅骨结构（忽略脑组织耦合与颅内压），且仅做静态拉伸/压缩测试，缺乏冲击载荷等动态条件下的数据。</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>The cause and mechanisms of this sudden death are considered as the cardiopulmonary dysfunction and arrest resulted from compression of the medulla and cervical cord, which was induced by both the positional insult and minor head trauma.</t>
+          <t>There was no significant difference in ultimate stress, elastic modulus, or ultimate strain between the sagittal and coronal sutures, however, there were significant differences between the frontal and parietal bones as well as between the cranial bones and suture samples.</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>案例报告：对一例轻微交通事故后意外死亡的受害者进行完整法医学尸体解剖，重点进行神经病理学检查（大体观察小脑扁桃体疝出程度、脑干受压情况，组织病理学检查脑干神经元损伤），分析轻微创伤与既往Chiari I型畸形在致死中的因果关系。</t>
+          <t>从1-2岁婴儿尸体采集颅骨和骨缝样本，进行拉伸和压缩力学测试，测量弹性模量、极限强度等力学参数，比较骨与骨缝以及不同颅骨区域之间的差异。</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>Chiari I型畸形患者在轻微头颈部创伤后可能因脑干受压导致意外猝死，法医在交通事故致死案例中即使创伤轻微也应仔细进行神经病理学检查，以发现潜在的先天性颅颈交界区畸形。</t>
+          <t>获得了1-2岁婴儿颅骨和骨缝的力学性能参数（弹性模量、极限强度等），为法医学儿童头部创伤的生物力学分析提供了重要基础数据。</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>报告了Chiari I型畸形在轻微交通事故中致死的罕见案例，阐明了创伤-先天性畸形相互作用致死的机制：轻微创伤→脑干在狭窄枕骨大孔内进一步受压→呼吸循环中枢功能障碍→猝死，提醒法医关注隐匿性先天性病变在轻微创伤致死中的角色。</t>
+          <t>首次系统测定1-2岁婴儿颅骨和骨缝的力学性能参数，填补了该年龄段颅骨生物力学数据空白。</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
         <is>
-          <t>案例报告;猝死;Chiari畸形</t>
+          <t>生物力学;颅骨;婴儿</t>
         </is>
       </c>
       <c r="R68" s="2" t="inlineStr">
         <is>
-          <t>Journal of Forensic Sciences</t>
+          <t>Medical Science Monitor</t>
         </is>
       </c>
       <c r="S68" s="2" t="inlineStr">
         <is>
-          <t>10.1111/1556-4029.12051</t>
+          <t>10.12659/MSM.892278</t>
         </is>
       </c>
     </row>
@@ -7005,38 +6887,37 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>Blunt liver injury with intact ribs under impacts on the abdomen: a biomechanical investigation</t>
+          <t>Death due to fulminant neuroleptic malignant syndrome induced by low doses of haloperidol: a rare case</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>腹部撞击致肋骨完整情况下的钝性肝损伤：生物力学研究</t>
+          <t>低剂量氟哌啶醇致暴发性神经阻滞剂恶性综合征死亡：罕见案例</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>目的：探讨腹部撞击下肋骨完整情况下钝性肝损伤的生物力学机制。方法：构建包含肝脏和胸廓的人体腹部有限元模型，在不同条件下进行撞击模拟，分析肝脏的应力分布、变形模式和损伤机制。结果：肝脏在肋骨完整的情况下仍可能遭受显著损伤，损伤机制涉及直接力传递和器官变形，某些撞击条件产生的肝损伤模式与临床和法医学观察一致。结论：钝性肝损伤可在肋骨完整的情况下发生，生物力学分析有助于解释损伤机制，对法医学腹部创伤评估具有重要意义。</t>
+          <t>神经阻滞剂恶性综合征(NMS)是抗精神病药物的一种罕见但危及生命的并发症。本文报告了一例低剂量氟哌啶醇致暴发性NMS死亡的罕见案例。受害者是一名年轻男性，接受低剂量氟哌啶醇后出现快速发作的NMS并导致死亡。讨论了该案例的临床过程、尸检发现和法医学意义，并进行了类似案例的文献综述。即使低剂量氟哌啶醇也可能触发致命的NMS，涉及抗精神病药物的猝死案例应考虑该可能性。</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>法医生物力学
-钝性肝损伤</t>
+          <t>罕见案例</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>生物力学</t>
+          <t>形态学</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>损伤机制</t>
+          <t>死因</t>
         </is>
       </c>
       <c r="H69" s="3" t="inlineStr">
         <is>
-          <t>2013-01</t>
+          <t>2014-05</t>
         </is>
       </c>
       <c r="I69" s="3" t="inlineStr">
@@ -7046,52 +6927,52 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>可牵引一篇『腹部实质脏器钝性损伤的生物力学机制综述』：围绕肝、脾损伤的应力/应变损伤阈值、肋骨完整情况下的直接力传导与加速-减速变形机制，按『损伤阈值数据—有限元建模—载荷场景模拟—与临床/法医病理对照』框架组织，重点论证『肋骨不骨折≠内脏无损伤』的力学证据及其对法医学腹部创伤评估与致伤方式判定的指导意义。</t>
+          <t>可牵引一篇『抗精神病药物相关猝死的法医学鉴别诊断』综述：围绕神经阻滞剂恶性综合征（NMS）、药物性心律失常（QT延长）与其他死因的鉴别，按『药物暴露史评估—临床过程重建—尸检与毒理检测—死因认定逻辑』框架组织文献，重点讨论低剂量触发NMS的机制（多巴胺受体阻断、遗传易感性、脱水等危险因素）及死后诊断缺乏特异性标志物的鉴定困境。</t>
         </is>
       </c>
       <c r="L69" s="3" t="inlineStr">
         <is>
-          <t>有限元模型对肝脏材料属性与个体解剖几何做了简化，模拟载荷条件有限，未覆盖全部撞击方向、速度与腹壁状态；结果与临床/法医学观察的一致性仅为定性对照，缺乏定量损伤指标（如应力阈值）与真实案例的系统验证。模型未纳入腹壁肌肉张力、呼吸相位等生理因素，仿真结论外推需谨慎。</t>
+          <t>为单一案例报告，低剂量触发暴发性NMS属罕见事件，外推性有限；NMS本质为临床诊断，死后缺乏特异性生物学标志物，尸检无特征性病理改变，死因认定主要依靠排除法，本文无法完全排除心律失常、吸入性肺炎等并发死因。文献综述部分的证据检索与整合不系统，未对同类案例做量化汇总。</t>
         </is>
       </c>
       <c r="M69" s="3" t="inlineStr">
         <is>
-          <t>Investigating the mechanism underlying hepatic injury following abdominal trauma showed that liver rupture was primarily caused by a direct strike of the ribs induced by blunt impact to the abdomen.</t>
+          <t>The paper reports on a rare case of fulminant neuroleptic malignant syndrome (NMS) with several risk factors, typical manifestation and rapid death induced by low doses of haloperidol. The pathological findings, pathogenesis, clinical manifestations, diagnostic criteria, risk factors and other features of NMS are discussed.</t>
         </is>
       </c>
       <c r="N69" s="3" t="inlineStr">
         <is>
-          <t>构建包含肝脏和胸廓的人体腹部有限元模型（包括肋骨、肝脏、周围软组织的几何和材料属性建模），设置不同撞击速度/方向/部位/能量条件进行有限元仿真模拟，分析肝脏应力分布、最大主应变、变形模式和损伤预测。</t>
+          <t>案例报告：详细描述一名年轻男性接受低剂量氟哌啶醇后发生暴发性NMS并死亡的临床过程、尸检发现，并结合类似案例文献综述讨论法医学意义。</t>
         </is>
       </c>
       <c r="O69" s="3" t="inlineStr">
         <is>
-          <t>钝性肝损伤可在肋骨完整的情况下发生（肋骨不骨折≠内脏无损伤），损伤机制涉及力的直接传导和肝脏加速/减速变形，生物力学分析为法医学腹部创伤评估和致伤方式判定提供了重要力学基础。</t>
+          <t>即使是低剂量氟哌啶醇也可能触发致命的NMS；在涉及抗精神病药物的猝死案例中，法医学鉴定应考虑NMS的可能性。</t>
         </is>
       </c>
       <c r="P69" s="3" t="inlineStr">
         <is>
-          <t>首次通过有限元生物力学模拟系统阐明肋骨完整情况下钝性肝损伤的发生机制，打破了'无骨折即无内脏损伤'的传统法医学认知误区，为法医学腹部钝性伤评估提供了力学理论依据。</t>
+          <t>报告了低剂量氟哌啶醇致暴发性NMS死亡的罕见案例，挑战了NMS通常与高剂量或联合用药相关的传统认识。</t>
         </is>
       </c>
       <c r="Q69" s="3" t="inlineStr">
         <is>
-          <t>有限元;肝损伤;生物力学</t>
+          <t>案例报告;神经阻滞剂恶性综合征</t>
         </is>
       </c>
       <c r="R69" s="3" t="inlineStr">
         <is>
-          <t>PLoS ONE</t>
+          <t>Journal of Forensic and Legal Medicine</t>
         </is>
       </c>
       <c r="S69" s="3" t="inlineStr">
         <is>
-          <t>10.1371/journal.pone.0052366</t>
+          <t>10.1016/j.jflm.2014.02.011</t>
         </is>
       </c>
     </row>
@@ -7101,68 +6982,93 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>A diagnostic strategy for pulmonary fat embolism based on routine H&amp;E staining using computational pathology</t>
+          <t>Characteristics of electrically injured skin from human hand tissue samples using Fourier transform infrared microspectroscopy</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>基于常规HE染色的计算病理学肺脂肪栓塞诊断策略</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr"/>
+          <t>使用FTIR显微光谱研究人手部组织样本电击伤皮肤的特征</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>FTIR显微光谱为电击伤的辅助诊断提供了客观光谱标志物。电击伤皮肤组织的角质层和非角质层区域的光谱吸收显著增加。</t>
+        </is>
+      </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>肺脂肪栓塞</t>
+          <t>光谱分析
+电击伤</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>AI/机器学习; 形态学</t>
+          <t>光谱</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>死因</t>
+          <t>死亡方式</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>2024-05</t>
-        </is>
-      </c>
-      <c r="I70" s="2" t="inlineStr"/>
+          <t>2014-01</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>复旦大学基础医学院法医学系/司法鉴定科学研究院</t>
+        </is>
+      </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>可牵引一篇『计算病理学（数字病理+深度学习）在法医病理学中的应用与挑战』综述：以肺脂肪栓塞的全切片定量分析为范例，扩展到心肌梗死面积、肺水肿、肝脂肪变性等死因相关病变的AI辅助定量诊断，按『数字化全切片—组织学特征工程/深度学习模型—与传统特殊染色及主观半定量法对比—临床转化与标准化』框架组织，讨论AI在提升法医病理客观性与可重复性中的作用。</t>
+          <t>可牵引一篇『电流斑鉴定的客观化方法研究进展』综述：对比传统形态学指标（表皮/真皮改变、金属化颗粒、SEM-EDX元素分析）与振动光谱（FTIR、拉曼）分子标志物在电击伤鉴定中的价值，按『样本类型—光谱特征—化学计量学判别—与相似损伤（热烧伤、摩擦伤）鉴别』框架组织，讨论多模态联合鉴定流程的构建。</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>基于HE染色的深度学习定量高度依赖训练集标注质量与病理医生金标准，PFE栓塞程度与死亡因果关系的判定仍须人工裁决；摘要未报告训练样本量、跨中心泛化性（染色批次、扫描仪差异）与外部验证，与传统油红O特殊染色结果的相关性验证程度不明，方法可重复性证据不足。</t>
+          <t>仅采用人手部皮肤组织样本，样本量小，且未与热烧伤、摩擦伤、尸斑等相似外观损伤做光谱对照，特异性存疑；死后变化、腐败与固定处理对皮肤光谱的影响未系统控制。角质层与非角质层区域光谱变化的生物学解释及跨个体可重复性尚需更大样本验证，判别模型亦缺乏独立验证集。</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>Pulmonary fat embolism (PFE) as a cause of death often occurs in trauma cases such as fractures and soft tissue contusions. Traditional PFE diagnosis relies on subjective methods and special stains like oil red O. This study utilizes computational pathology, combining digital pathology and deep learning algorithms, to precisely quantify fat emboli in whole slide images using conventional hematoxylin-eosin (H&amp;E) staining. The results demonstrate deep learning’s ability to identify fat droplet morphology in lung microvessels, achieving an area under the receiver operating characteristic (ROC) curve (AUC) of 0.98. The AI-quantified fat globules generally matched the Falzi scoring system with oil red O staining. The relative quantity of fat emboli against lung area was calculated by the algorithm, determining a diagnostic threshold of 8.275% for fatal PFE. A diagnostic strategy based on this threshold achieved a high AUC of 0.984, similar to manual identification with special stains but surpassing H&amp;E staining. This demonstrates computational pathology’s potential as an affordable, rapid, and precise method for fatal PFE diagnosis in forensic practice.</t>
-        </is>
-      </c>
-      <c r="N70" s="2" t="inlineStr"/>
-      <c r="O70" s="2" t="inlineStr"/>
-      <c r="P70" s="2" t="inlineStr"/>
-      <c r="Q70" s="2" t="inlineStr"/>
+          <t>FTIR-MSP presents a useful method to provide objective spectral markers for the assisted diagnosis of electrical marks. Band absorbance increased significantly both in the stratum and non-stratum corneum of electrically injured skin tissues.</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>人尸检手部电击伤皮肤组织，FTIR显微光谱+组织学对比</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>FTIR显微光谱可客观检测电击伤皮肤的特异性光谱改变，为法医电击伤鉴定提供辅助手段。</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>首次系统研究电击伤皮肤的FTIR光谱特征</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>FTIR;皮肤;电击伤</t>
+        </is>
+      </c>
       <c r="R70" s="2" t="inlineStr">
         <is>
-          <t>International Journal of Legal Medicine</t>
+          <t>Science &amp; Justice</t>
         </is>
       </c>
       <c r="S70" s="2" t="inlineStr">
         <is>
-          <t>10.1007/s00414-023-03136-5</t>
+          <t>10.1016/j.scijus.2013.07.005</t>
         </is>
       </c>
     </row>
@@ -7172,37 +7078,45 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>Automatic adult age estimation using bone mineral density of proximal femur via deep learning</t>
+          <t>Finite element analysis of pedestrian lower limb fractures by direct force: the result of being run over or impact?</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>基于股骨近端骨密度的深度学习自动成人年龄推断</t>
-        </is>
-      </c>
-      <c r="D71" s="3" t="inlineStr"/>
+          <t>行人下肢骨折直接外力有限元分析：碾压还是撞击？</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>目的：利用有限元分析区分行人交通事故中碾压与撞击所致下肢骨折。方法：构建人体下肢有限元模型，施加模拟碾压和撞击的不同的载荷条件，比较两种机制下的骨折形态、应力分布和损伤特征。结果：碾压和撞击条件下的骨折模式表现出明显不同的特征，两种机制的应力分布和骨折扩展模式存在差异。结论：有限元分析有助于区分行人下肢骨折的碾压和撞击机制，为法医学事故重建提供科学依据。</t>
+        </is>
+      </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>法医人类学
-年龄推断</t>
+          <t>法医生物力学
+下肢骨折</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>AI/机器学习; 影像</t>
+          <t>生物力学</t>
         </is>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>身份</t>
+          <t>损伤机制</t>
         </is>
       </c>
       <c r="H71" s="3" t="inlineStr">
         <is>
-          <t>2025-07</t>
-        </is>
-      </c>
-      <c r="I71" s="3" t="inlineStr"/>
+          <t>2013-06</t>
+        </is>
+      </c>
+      <c r="I71" s="3" t="inlineStr">
+        <is>
+          <t>复旦大学基础医学院法医学系</t>
+        </is>
+      </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
           <t>2.6</t>
@@ -7210,23 +7124,39 @@
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>可牵引一篇『骨密度影像与深度学习在骨骼年龄推断中的技术综述』：以股骨近端BMD的端到端深度学习管线为核心案例，横向比较不同骨骼部位（股骨近端、椎体、锁骨）与成像模态（CT、DXA、QCT）的年龄推断效能，按『数据获取与标注—深度学习架构—误差评估—人群外推性与法医学证据标准』框架组织，讨论自动化年龄推断替代传统人工形态学分级的可行性。</t>
+          <t>可牵引一篇『有限元方法（FEA）在法医损伤生物力学与致伤方式鉴别中的应用』系统综述：按『几何建模（CT个体化/标准化）—材料参数—边界与载荷条件—损伤准则—模型验证（案例对照）』流程框架组织文献，聚焦行人交通事故中碾压与撞击、坠落等致伤方式的力学鉴别，并讨论模型不确定性对法医鉴定结论证据效力的影响。</t>
         </is>
       </c>
       <c r="L71" s="3" t="inlineStr">
         <is>
-          <t>BMD与年龄的关系受骨质疏松、内分泌与代谢疾病显著干扰，且存在种族/地域差异，训练集与目标人群不匹配时外推性受限；端到端深度学习管线可解释性差，缺乏与解剖学特征的可追溯关联。摘要未报告样本量与年龄分布覆盖、独立测试集验证情况，亦未与成熟形态学方法（耻骨联合、肋骨末端分级）的误差范围做定量比较。</t>
+          <t>有限元模型对骨骼材料参数与几何来源高度敏感，本文模型仅与单一真实案例对照验证，缺乏多案例统计验证；模型简化了肌肉、皮肤等软组织与边界条件，模拟载荷场景有限。未考虑个体差异（年龄、骨密度、体态），仿真所得应力分布向真实骨折形态的映射存在不确定性，结果的证据强度有限。</t>
         </is>
       </c>
       <c r="M71" s="3" t="inlineStr">
         <is>
-          <t>Accurate adult age estimation (AAE) is critical for forensic and anthropological applications, yet traditional methods relying on bone mineral density (BMD) face significant challenges due to biological variability and methodological limitations. This study aims to develop an end-to-end Deep Learning (DL) based pipeline for automated AAE using BMD from proximal femoral CT scans. The main objectives are to construct a large-scale dataset of 5151 CT scans from real-world clinical and cadaver cohorts, fine-tune the Segment Anything Model (SAM) for accurate femoral bone segmentation, and evaluate multiple convolutional neural networks (CNNs) for precise age estimation based on segmented BMD data. Model performance was assessed through cross-validation, internal clinical testing, and external post-mortem validation. SAM achieved excellent segmentation performance with a Dice coefficient of 0.928 and an average intersection over union (mIoU) of 0.869. The CNN models achieved an average mean absolute error (MAE) of 5.20 years in cross-validation (male: 5.72; female: 4.51), which improved to 4.98 years in the independent clinical test set (male: 5.32; female: 4.56). External validation on the post-mortem dataset revealed an MAE of 6.91 years, with 6.97 for males and 6.69 for females. Ensemble learning further improved accuracy, reducing MAE to 4.78 years (male: 5.12; female: 4.35) in the internal test set, and 6.58 years (male: 6.64; female: 6.37) in the external validation set. These findings highlight the feasibility of dl-driven AAE and its potential for forensic applications, offering a fully automated framework for robust age estimation.</t>
-        </is>
-      </c>
-      <c r="N71" s="3" t="inlineStr"/>
-      <c r="O71" s="3" t="inlineStr"/>
-      <c r="P71" s="3" t="inlineStr"/>
-      <c r="Q71" s="3" t="inlineStr"/>
+          <t>This study developed a novel lower limb FE model and simulated three different loading scenarios and compared the injuries resulting from one actual case with the simulated results in order to explore the possible fracture bio-mechanism.</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
+          <t>构建人体下肢有限元模型，分别施加模拟碾压和撞击的载荷条件，比较两种机制下的骨折形态、应力分布和损伤特征。</t>
+        </is>
+      </c>
+      <c r="O71" s="3" t="inlineStr">
+        <is>
+          <t>碾压和撞击机制下的下肢骨折模式具有明显不同特征，有限元分析可有效区分两者，为法医学交通事故重建提供科学依据。</t>
+        </is>
+      </c>
+      <c r="P71" s="3" t="inlineStr">
+        <is>
+          <t>将有限元分析方法应用于区分行人下肢骨折的碾压与撞击两种致伤机制，通过生物力学模拟为致伤方式判定提供定量分析手段。</t>
+        </is>
+      </c>
+      <c r="Q71" s="3" t="inlineStr">
+        <is>
+          <t>交通事故;下肢骨折;有限元</t>
+        </is>
+      </c>
       <c r="R71" s="3" t="inlineStr">
         <is>
           <t>Forensic Science International</t>
@@ -7234,7 +7164,7 @@
       </c>
       <c r="S71" s="3" t="inlineStr">
         <is>
-          <t>10.1016/j.forsciint.2025.112511</t>
+          <t>10.1016/j.forsciint.2013.03.027</t>
         </is>
       </c>
     </row>
@@ -7244,68 +7174,92 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Exploring Male-Specific Synaptic Plasticity in Major Depressive Disorder: A Single-Nucleus Transcriptomic Analysis Using Bioinformatics Methods</t>
+          <t>Sudden twin infant death on the same day: a case report and review of the literature</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>男性特异性突触可塑性与抑郁症：单核转录组生物信息学分析</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr"/>
+          <t>同日双胞胎婴儿猝死：案例报告与文献综述</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>婴儿猝死综合征(SIDS)是一种毁灭性事件。双胞胎婴儿同日同时猝死极为罕见。本文报告一例同日双胞胎婴儿猝死案例，呈现了案件调查、尸检发现和辅助检查结果，并进行了类似案例的全面文献综述。讨论了可能的机制包括遗传因素、环境因素和感染性原因。本案例强调了对多发婴儿猝死进行彻底法医学调查的重要性，以及同时考虑自然和非自然原因的必要性。</t>
+        </is>
+      </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>抑郁症</t>
+          <t>罕见案例</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>分子生物学</t>
+          <t>形态学</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>死因</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>2025-03</t>
-        </is>
-      </c>
-      <c r="I72" s="2" t="inlineStr"/>
+          <t>2013-06</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>复旦大学基础医学院法医学系</t>
+        </is>
+      </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>可牵引一篇『单细胞/单核转录组学在精神疾病分子病理研究中的应用』综述：以突触可塑性相关基因为线索，梳理snRNA-seq在MDD等疾病中细胞类型特异性改变的发现，按『数据来源—细胞聚类与差异分析—性别/细胞类型分层—与临床表型关联—功能验证』框架组织；对法医学而言，可延伸讨论分子组学方法在应激相关死亡、自杀及精神药物相关猝死机制研究中的应用前景。</t>
+          <t>可牵引一篇『婴儿猝死（SIDS/SUDI）的法医学综合调查策略』综述：围绕多胞胎同日猝死、遗传性离子通道病（长QT综合征等）、代谢性疾病与虐待/窒息鉴别的鉴别诊断，按『现场勘查—全面尸检—辅助检查—分子尸检（基因panel）—多学科协作』流程框架组织文献，讨论自然与非自然原因在多发婴儿猝死中的证据权重评估方法。</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>为公开数据集（GSE144136）的二次分析，死后脑组织样本受供体药物史、死亡方式、死后间隔等混杂因素影响，样本代表性有限；单核RNA-seq丢失细胞质RNA，存在转录本检测偏好。研究仅聚焦突触可塑性相关基因，通路覆盖不全，男性特异性发现缺乏独立队列验证，且无功能实验证实，结论强度有限。</t>
+          <t>为单一案例报告，双胞胎同日死亡可能受共同环境因素（感染、环境温度、睡眠条件）混杂，难以归因单一机制；文中未报告分子尸检（遗传性心律失常基因检测）结果，遗传假说缺乏直接证据。仅凭尸检常无法区分自然猝死与人为窒息，结论依赖排除法，文献综述亦未对SIDS风险因素做量化系统评价。</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>Major depressive disorder (MDD) is a complex psychiatric illness, with synaptic plasticity playing a key role in its pathology. Our study aims to investigate the molecular basis of MDD by analyzing synaptic plasticity-related gene expression at the single-cell level. Utilizing a published snRNA-seq dataset (GSE144136), we identified Excitatory.neurons_1 as the cell cluster most associated with MDD and synaptic plasticity through cell clustering, gene set enrichment analysis (GSEA), and pseudotime analysis. Integrating the bulk RNA-seq data (GSE38206), we identified CASKIN1 and CSTB as hub genes via differential expression analysis and machine learning methods. Further exploration of the relevant mechanisms was performed via cell–cell communication and ligand-receptor interaction analysis, functional enrichment analysis, and the construction of molecular regulatory networks, highlighting miR-21-5p as a key biomarker. We propose that elevated miR-21-5p in MDD downregulates CASKIN1 in Excitatory.neurons_1 cells, resulting in decreased neural connectivity and altered synaptic plasticity. As our analyzed snRNA-seq dataset consists solely of male samples, these findings may be male-specific. Our findings shed light on potential mechanisms underlying synaptic plasticity in MDD, offering novel insights into the disorder’s cellular and molecular dynamics.</t>
-        </is>
-      </c>
-      <c r="N72" s="2" t="inlineStr"/>
-      <c r="O72" s="2" t="inlineStr"/>
-      <c r="P72" s="2" t="inlineStr"/>
-      <c r="Q72" s="2" t="inlineStr"/>
+          <t>Risk factors for SIDS should be considered individually or in combination as possible causes of death, and both 10-week-old male twins who appeared well at the time of their evening feeding yet died while sleeping on their backs have petechial hemorrhages.</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>案例报告：呈现同日双胞胎婴儿猝死的案件调查（现场勘查、家庭访谈、病史采集）、系统尸体解剖（大体和组织病理学）、毒理学和微生物学辅助检查结果，并辅以类似双胞胎同日猝死案例的全面文献综述，分析遗传、环境和感染等可能机制。</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>同日双胞胎婴儿猝死极为罕见，法医学调查应综合现场勘查、全面尸检和辅助检查，同时考虑遗传性离子通道病等自然原因和窒息等非自然原因的可能性，多学科联合调查是关键。</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>报告了极为罕见的同日双胞胎婴儿猝死案例，系统综述类似文献，提出遗传因素（如长QT综合征等遗传性心律失常）和环境的综合作用机制，强调了多发婴儿猝死中法医学综合调查策略。</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>案例报告;双胞胎;婴儿猝死</t>
+        </is>
+      </c>
       <c r="R72" s="2" t="inlineStr">
         <is>
-          <t>International Journal of Molecular Sciences</t>
+          <t>Forensic Science, Medicine, and Pathology</t>
         </is>
       </c>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>10.3390/ijms26073135</t>
+          <t>10.1007/s12024-013-9429-3</t>
         </is>
       </c>
     </row>
@@ -7315,23 +7269,28 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>FTIR spectroscopy imaging coupled with machine learning reveals biochemical changes in the brains of diabetic mice</t>
+          <t>Sudden unexpected death due to Chiari type I malformation in a road accident case</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>FTIR光谱成像结合机器学习揭示糖尿病小鼠脑生化改变</t>
-        </is>
-      </c>
-      <c r="D73" s="3" t="inlineStr"/>
+          <t>道路交通事故中Chiari I型畸形致意外猝死</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>Chiari I型畸形是一种以小脑扁桃体经枕骨大孔疝出为特征的先天性异常。本文报告一例道路交通事故中因Chiari I型畸形致意外猝死的案例。受害者涉及一起轻微道路交通事故后意外死亡。尸检发现Chiari I型畸形伴脑干压迫。讨论轻微创伤与既往Chiari畸形在致死中的关系。本案例强调了在道路交通事故死亡案例中仔细进行神经病理学检查的重要性。</t>
+        </is>
+      </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>糖尿病脑病</t>
+          <t>猝死
+Chiari畸形</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>AI/机器学习; 光谱</t>
+          <t>形态学</t>
         </is>
       </c>
       <c r="G73" s="3" t="inlineStr">
@@ -7341,42 +7300,62 @@
       </c>
       <c r="H73" s="3" t="inlineStr">
         <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="I73" s="3" t="inlineStr"/>
+          <t>2013-03</t>
+        </is>
+      </c>
+      <c r="I73" s="3" t="inlineStr">
+        <is>
+          <t>复旦大学基础医学院法医学系</t>
+        </is>
+      </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>可牵引一篇『FTIR光谱成像在脑组织区域生化分析中的应用』综述：以糖尿病脑病区域特异性代谢改变为范例，系统梳理FTIRM在皮层、海马、丘脑等不同脑区的脂质与蛋白质二级结构光谱特征，结合机器学习分类方法，按『样本制备—光谱采集与区域定位—峰归属生化注释—分类建模—与生化金标准验证』框架组织；对法医学可延伸至脑缺血、创伤等病理性损伤的分子诊断应用前景。</t>
+          <t>可牵引一篇『隐匿性颅颈交界区病变与轻微创伤致死的法医学因果分析』综述：以Chiari I型畸形、寰枢椎不稳等先天病变为对象，按『解剖脆弱性—创伤与体位因素交互—脑干/延髓受压机制—死因与因果关系（直接死因/诱因）认定』框架组织文献，讨论无症状携带者人群中的意外死亡风险及轻微创伤在死因判定中的法律与医学权重。</t>
         </is>
       </c>
       <c r="L73" s="3" t="inlineStr">
         <is>
-          <t>基于db/db小鼠模型，与人类糖尿病脑病存在物种差异，向人体转化需谨慎；区域间光谱差异的生物学注释主要依靠峰归属推断，缺乏与免疫组化、质谱等生化金标准的定量验证。摘要未报告样本量、死后延迟及固定处理对光谱的影响，研究为描述性分析，区域特异性标志物的稳健性与判别效能证据不足。</t>
+          <t>为单一案例报告；Chiari I型畸形在普通人群无症状携带率较高，使『轻微创伤致死的因果关系』认定存在不确定性，本文缺乏流行病学对照支撑。脑干受压致死的机制推断缺少死后MRI、神经电生理等直接证据，且轻微创伤与体位因素各自的相对贡献未量化区分，结论外推需谨慎。</t>
         </is>
       </c>
       <c r="M73" s="3" t="inlineStr">
         <is>
-          <t>Diabetic encephalopathy is a progressive complication of type 2 diabetes, yet its region-specific biochemical changes remain unclear. In this study, we applied Fourier Transform Infrared Microspectroscopy (FTIRM) to assess metabolic alterations in the anatomical structures of the brains of db/db mice. Spectral data from five anatomically defined regions, cerebral cortex, hippocampus, thalamus, hypothalamus, and striatum, were analyzed in both 12-week and 21-week wild-type and diabetic groups. Marked changes were observed in the spectral regions of glucose, phospholipids, esterified lipids, amide, and nucleic acids across these brain regions. As diabetes progress, the hippocampus exhibited progressive molecular deterioration, while the hypothalamus showed disruptions followed by partial restoration at 21 weeks. Partial least square discriminant analysis (PLS-DA) models based on second-derivative spectra achieved high classification accuracy (area under the curve (AUC) &gt; 0.99), reliably distinguishing between healthy, early (12 weeks), and late (21 weeks) diabetic stages. These results demonstrate the capacity of FTIRM combined with machine learning to reveal region-specific biochemical signatures of diabetic encephalopathy and offer potential for early diagnosis and staging.</t>
-        </is>
-      </c>
-      <c r="N73" s="3" t="inlineStr"/>
-      <c r="O73" s="3" t="inlineStr"/>
-      <c r="P73" s="3" t="inlineStr"/>
-      <c r="Q73" s="3" t="inlineStr"/>
+          <t>The cause and mechanisms of this sudden death are considered as the cardiopulmonary dysfunction and arrest resulted from compression of the medulla and cervical cord, which was induced by both the positional insult and minor head trauma.</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
+          <t>案例报告：对一例轻微交通事故后意外死亡的受害者进行完整法医学尸体解剖，重点进行神经病理学检查（大体观察小脑扁桃体疝出程度、脑干受压情况，组织病理学检查脑干神经元损伤），分析轻微创伤与既往Chiari I型畸形在致死中的因果关系。</t>
+        </is>
+      </c>
+      <c r="O73" s="3" t="inlineStr">
+        <is>
+          <t>Chiari I型畸形患者在轻微头颈部创伤后可能因脑干受压导致意外猝死，法医在交通事故致死案例中即使创伤轻微也应仔细进行神经病理学检查，以发现潜在的先天性颅颈交界区畸形。</t>
+        </is>
+      </c>
+      <c r="P73" s="3" t="inlineStr">
+        <is>
+          <t>报告了Chiari I型畸形在轻微交通事故中致死的罕见案例，阐明了创伤-先天性畸形相互作用致死的机制：轻微创伤→脑干在狭窄枕骨大孔内进一步受压→呼吸循环中枢功能障碍→猝死，提醒法医关注隐匿性先天性病变在轻微创伤致死中的角色。</t>
+        </is>
+      </c>
+      <c r="Q73" s="3" t="inlineStr">
+        <is>
+          <t>案例报告;猝死;Chiari畸形</t>
+        </is>
+      </c>
       <c r="R73" s="3" t="inlineStr">
         <is>
-          <t>Spectrochimica Acta. Part A, Molecular and Biomolecular Spectroscopy</t>
+          <t>Journal of Forensic Sciences</t>
         </is>
       </c>
       <c r="S73" s="3" t="inlineStr">
         <is>
-          <t>10.1016/j.saa.2025.126835</t>
+          <t>10.1111/1556-4029.12051</t>
         </is>
       </c>
     </row>
@@ -7386,72 +7365,93 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>The impact of multi-modality fusion and deep learning on adult age estimation based on bone mineral density</t>
+          <t>Blunt liver injury with intact ribs under impacts on the abdomen: a biomechanical investigation</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>多模态融合与深度学习基于骨密度的成人年龄推断</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr"/>
+          <t>腹部撞击致肋骨完整情况下的钝性肝损伤：生物力学研究</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>目的：探讨腹部撞击下肋骨完整情况下钝性肝损伤的生物力学机制。方法：构建包含肝脏和胸廓的人体腹部有限元模型，在不同条件下进行撞击模拟，分析肝脏的应力分布、变形模式和损伤机制。结果：肝脏在肋骨完整的情况下仍可能遭受显著损伤，损伤机制涉及直接力传递和器官变形，某些撞击条件产生的肝损伤模式与临床和法医学观察一致。结论：钝性肝损伤可在肋骨完整的情况下发生，生物力学分析有助于解释损伤机制，对法医学腹部创伤评估具有重要意义。</t>
+        </is>
+      </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>法医人类学
-年龄推断</t>
+          <t>法医生物力学
+钝性肝损伤</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>AI/机器学习; 影像</t>
+          <t>生物力学</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>身份</t>
+          <t>损伤机制</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>2025-07</t>
-        </is>
-      </c>
-      <c r="I74" s="2" t="inlineStr"/>
+          <t>2013-01</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>复旦大学基础医学院法医学系</t>
+        </is>
+      </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>可牵引一篇『影像组学与深度学习在成人年龄推断中的应用』综述：以骨密度（BMD）多模态融合为切入点，系统比较CT、定量CT、X线等不同模态及传统回归与端到端深度学习方法的年龄推断效能，按『成像模态—特征/模型—人群变异控制—与形态学金标准（耻骨联合、锁骨等）对照—法医人类学应用规范』框架组织文献。</t>
+          <t>可牵引一篇『腹部实质脏器钝性损伤的生物力学机制综述』：围绕肝、脾损伤的应力/应变损伤阈值、肋骨完整情况下的直接力传导与加速-减速变形机制，按『损伤阈值数据—有限元建模—载荷场景模拟—与临床/法医病理对照』框架组织，重点论证『肋骨不骨折≠内脏无损伤』的力学证据及其对法医学腹部创伤评估与致伤方式判定的指导意义。</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>BMD受骨质疏松、代谢疾病、营养、种族与运动等多因素干扰，年龄关联存在较大个体差异；训练数据集的年龄分布与人群来源直接影响模型外推性，摘要未报告样本量、人群构成与独立验证。多模态融合带来的精度增益与计算成本、可解释性下降之间的权衡未充分讨论，亦缺乏与成熟形态学年龄推断方法的系统误差对比。</t>
+          <t>有限元模型对肝脏材料属性与个体解剖几何做了简化，模拟载荷条件有限，未覆盖全部撞击方向、速度与腹壁状态；结果与临床/法医学观察的一致性仅为定性对照，缺乏定量损伤指标（如应力阈值）与真实案例的系统验证。模型未纳入腹壁肌肉张力、呼吸相位等生理因素，仿真结论外推需谨慎。</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>INTRODUCTION: Age estimation, especially in adults, presents substantial challenges in different contexts ranging from forensic to clinical applications. Bone mineral density (BMD), with its distinct age-related variations, has emerged as a critical marker in this domain. This study aims to enhance chronological age estimation accuracy using deep learning (DL) incorporating a multi-modality fusion strategy based on BMD.
-METHODS: We conducted a retrospective analysis of 4296 CT scans from a Chinese population, covering August 2015 to November 2022, encompassing lumbar, femur, and pubis modalities. Our DL approach, integrating multi-modality fusion, was applied to predict chronological age automatically. The model's performance was evaluated using an internal real-world clinical cohort of 644 scans (December 2022 to May 2023) and an external cadaver validation cohort of 351 scans.
-RESULTS: In single-modality assessments, the lumbar modality excelled. However, multi-modality models demonstrated superior performance, evidenced by lower mean absolute errors (MAEs) and higher Pearson's R² values. The optimal multi-modality model exhibited outstanding R² values of 0.89 overall, 0.88 in females, 0.90 in males, with the MAEs of 4.05 overall, 3.69 in females, 4.33 in males in the internal validation cohort. In the external cadaver validation, the model maintained favourable R² values (0.84 overall, 0.89 in females, 0.82 in males) and MAEs (5.01 overall, 4.71 in females, 5.09 in males), highlighting its generalizability across diverse scenarios.
-CONCLUSION: The integration of multi-modalities fusion with DL significantly refines the accuracy of adult age estimation based on BMD. The AI-based system that effectively combines multi-modalities BMD data, presenting a robust and innovative tool for accurate AAE, poised to significantly improve both geriatric diagnostics and forensic investigations.</t>
-        </is>
-      </c>
-      <c r="N74" s="2" t="inlineStr"/>
-      <c r="O74" s="2" t="inlineStr"/>
-      <c r="P74" s="2" t="inlineStr"/>
-      <c r="Q74" s="2" t="inlineStr"/>
+          <t>Investigating the mechanism underlying hepatic injury following abdominal trauma showed that liver rupture was primarily caused by a direct strike of the ribs induced by blunt impact to the abdomen.</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>构建包含肝脏和胸廓的人体腹部有限元模型（包括肋骨、肝脏、周围软组织的几何和材料属性建模），设置不同撞击速度/方向/部位/能量条件进行有限元仿真模拟，分析肝脏应力分布、最大主应变、变形模式和损伤预测。</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>钝性肝损伤可在肋骨完整的情况下发生（肋骨不骨折≠内脏无损伤），损伤机制涉及力的直接传导和肝脏加速/减速变形，生物力学分析为法医学腹部创伤评估和致伤方式判定提供了重要力学基础。</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>首次通过有限元生物力学模拟系统阐明肋骨完整情况下钝性肝损伤的发生机制，打破了'无骨折即无内脏损伤'的传统法医学认知误区，为法医学腹部钝性伤评估提供了力学理论依据。</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>有限元;肝损伤;生物力学</t>
+        </is>
+      </c>
       <c r="R74" s="2" t="inlineStr">
         <is>
-          <t>International Journal of Legal Medicine</t>
+          <t>PLoS ONE</t>
         </is>
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>10.1007/s00414-025-03432-2</t>
+          <t>10.1371/journal.pone.0052366</t>
         </is>
       </c>
     </row>
